--- a/STEPS_data_analysis/data_input/ISO_input_matrix.xlsx
+++ b/STEPS_data_analysis/data_input/ISO_input_matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldhealthorg-my.sharepoint.com/personal/cowanm_who_int/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{D3B2EA46-1EFA-E94C-BBF0-820DB492552A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAC5839C-BA97-4909-81E2-8EB9F215B6F5}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{D3B2EA46-1EFA-E94C-BBF0-820DB492552A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D47D1A38-2CDF-4B1C-B0B2-7CC7D4695D63}"/>
   <bookViews>
-    <workbookView xWindow="30090" yWindow="105" windowWidth="25935" windowHeight="14655" activeTab="1" xr2:uid="{56236E1D-2702-4F2C-A185-C8269303025C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56236E1D-2702-4F2C-A185-C8269303025C}"/>
   </bookViews>
   <sheets>
     <sheet name="indicators" sheetId="1" r:id="rId1"/>
@@ -6157,7 +6157,7 @@
     replace_na(mh9 == 88, TRUE) |
     replace_na(mh10 == 88, TRUE) |
     replace_na(mh11 == 88, TRUE) |
-    replace_na(mh12 == 88, TRUE) |
+    replace_na(mh12 == 88, TRUE)) | (screenpos==1 &amp; symptomcount&gt;=5 &amp; 
     replace_na(mh13 == 88, TRUE))),
     NA,
     deprepisode
@@ -6613,10 +6613,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>

--- a/STEPS_data_analysis/data_input/ISO_input_matrix.xlsx
+++ b/STEPS_data_analysis/data_input/ISO_input_matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\R\GitHub current\data_input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF12619-6A42-40E5-BF92-48944622755C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974A3718-DC62-4245-A0C4-D4A36F9B98AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56236E1D-2702-4F2C-A185-C8269303025C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56236E1D-2702-4F2C-A185-C8269303025C}"/>
   </bookViews>
   <sheets>
     <sheet name="indicators" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4056" uniqueCount="1798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4056" uniqueCount="1807">
   <si>
     <t>Section</t>
   </si>
@@ -3222,15 +3222,9 @@
     <t>Percentage of women with a follow-up visit among those with an abnormal or suspect test result</t>
   </si>
   <si>
-    <t>cx6;cx7</t>
-  </si>
-  <si>
     <t>cxs8:Cervical cancer treatment</t>
   </si>
   <si>
-    <t>cx6;cx8</t>
-  </si>
-  <si>
     <t>cxs11:No cervical cancer screening test</t>
   </si>
   <si>
@@ -3273,9 +3267,6 @@
     <t>oh4:Reason for not using health care services</t>
   </si>
   <si>
-    <t>!is.na(o4)</t>
-  </si>
-  <si>
     <t>oh5:Use of fluoride toothpaste</t>
   </si>
   <si>
@@ -3294,9 +3285,6 @@
     <t>o6</t>
   </si>
   <si>
-    <t>Number of available teeth</t>
-  </si>
-  <si>
     <t>0 teeth;1 to 9 teeth;10 to 19 teeth;20+ teeth</t>
   </si>
   <si>
@@ -3369,9 +3357,6 @@
     <t>Sought medical care</t>
   </si>
   <si>
-    <t>vi1:Seat belt</t>
-  </si>
-  <si>
     <t>Frequency of seat belt use over the past 30 days</t>
   </si>
   <si>
@@ -3379,9 +3364,6 @@
   </si>
   <si>
     <t>Seat belt use frequency</t>
-  </si>
-  <si>
-    <t>vi2:Helmet</t>
   </si>
   <si>
     <t>Frequency of helmet use over the past 30 days</t>
@@ -5601,12 +5583,6 @@
     <t>Percentage of the population by number of teeth</t>
   </si>
   <si>
-    <t>Percentage of the population with untreated dental caries</t>
-  </si>
-  <si>
-    <t>Percentage of the population with severe dental caries</t>
-  </si>
-  <si>
     <t>Percentage of the population with severe pain, swelling, damage or unusual lesion in or around the mouth</t>
   </si>
   <si>
@@ -6028,9 +6004,6 @@
     <t>cx9==1</t>
   </si>
   <si>
-    <t>cx6;cx9</t>
-  </si>
-  <si>
     <t>Received cervical cancer treatment during the same visit when tested</t>
   </si>
   <si>
@@ -6046,9 +6019,6 @@
 CX10: What is the main reason you did not receive treatment?</t>
   </si>
   <si>
-    <t>cx1;cx10</t>
-  </si>
-  <si>
     <t>Reason never received treatment for cervical cancer</t>
   </si>
   <si>
@@ -6062,22 +6032,13 @@
     <t>Reason never screened for cervical cancer screening</t>
   </si>
   <si>
-    <t>cx1==1 &amp; (cx6==3 | cx6==4 | cx6==5)</t>
-  </si>
-  <si>
     <t>cx10==1;cx10==2;cx10==3;cx10==4;cx10==5;cx10==6;cx10==7;cx10==8;cx10==9;cx10==10;is.na(cx10)</t>
   </si>
   <si>
-    <t>cx1==1 &amp; (cx6==3 | cx6==4 | cx6==5) &amp; cx8==2</t>
-  </si>
-  <si>
     <t>not told treatment needed;did not know how/where to get treatment;embarrassment;too expensive;didn't have time;clinic too far away;poor service quality;fear (afraid of procedure, social stigma);cultural beliefs;family member would not allow it;don't know/refused</t>
   </si>
   <si>
     <t>cx11==1;cx11==2;cx11==3;cx11==4;cx11==5;cx11==6;cx11==7;cx11==8;cx11==9;is.na(cx11)</t>
-  </si>
-  <si>
-    <t>cx1==2</t>
   </si>
   <si>
     <t>did not know how/where to get test;embarrassment;too expensive;didn't have time;clinic too far away;poor service quality;fear (afraid of procedure, social stigma);cultural beliefs;family member would not allow it;don't know/refused</t>
@@ -6357,6 +6318,72 @@
   </si>
   <si>
     <t>!is.na(v19)</t>
+  </si>
+  <si>
+    <t>vi1:Seat belt use</t>
+  </si>
+  <si>
+    <t>vi2:Helmet use</t>
+  </si>
+  <si>
+    <t>!is.na(o9)</t>
+  </si>
+  <si>
+    <t>Percentage of the population with untreated dental caries (excluding population with no teeth)</t>
+  </si>
+  <si>
+    <t>Percentage of the population with severe dental caries (excluding population with no teeth)</t>
+  </si>
+  <si>
+    <t>Number of teeth present</t>
+  </si>
+  <si>
+    <t>cx1==1 &amp; !is.na(cx3)</t>
+  </si>
+  <si>
+    <t>cx1==1 &amp; !is.na(cx4)</t>
+  </si>
+  <si>
+    <t>cx1==1 &amp; !is.na(cx5)</t>
+  </si>
+  <si>
+    <t>cx1==1 &amp; !is.na(cx6)</t>
+  </si>
+  <si>
+    <t>cx1==1 &amp; (cx6==3 | cx6==4 | cx6==5) &amp; !is.na(cx7)</t>
+  </si>
+  <si>
+    <t>cx1==1 &amp; (cx6==3 | cx6==4 | cx6==5) &amp; !is.na(cx8)</t>
+  </si>
+  <si>
+    <t>cx1==1 &amp; (cx6==3 | cx6==4 | cx6==5) &amp; !is.na(cx9)</t>
+  </si>
+  <si>
+    <t>cx1==2 &amp; !is.na(cx11)</t>
+  </si>
+  <si>
+    <t>cx1==1 &amp; (cx6==3 | cx6==4 | cx6==5) &amp; cx8==2  &amp; !is.na(cx10)</t>
+  </si>
+  <si>
+    <t>cx1;cx6;cx8;cx10</t>
+  </si>
+  <si>
+    <t>cx1;cx6;cx7</t>
+  </si>
+  <si>
+    <t>cx1;cx6;cx8</t>
+  </si>
+  <si>
+    <t>cx1;cx6;cx9</t>
+  </si>
+  <si>
+    <t>!is.na(o7) &amp; (o6==2 | o6==3 | o6==4)</t>
+  </si>
+  <si>
+    <t>(!is.na(o8) | o7==2)  &amp; (o6==2 | o6==3 | o6==4)</t>
+  </si>
+  <si>
+    <t>!is.na(o4) &amp; o2!=6 &amp; o3==2</t>
   </si>
 </sst>
 </file>
@@ -7203,13 +7230,13 @@
         <v>373</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1649</v>
+        <v>1641</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>1648</v>
+        <v>1640</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>66</v>
@@ -7241,19 +7268,19 @@
         <v>374</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>1650</v>
+        <v>1642</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>316</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>380</v>
@@ -7285,19 +7312,19 @@
         <v>375</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>1651</v>
+        <v>1643</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>317</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>380</v>
@@ -7332,13 +7359,13 @@
         <v>839</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>1464</v>
+        <v>1458</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>1464</v>
+        <v>1458</v>
       </c>
       <c r="I5" s="11" t="s">
         <v>380</v>
@@ -7367,19 +7394,19 @@
         <v>377</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>318</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>1465</v>
+        <v>1459</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>1465</v>
+        <v>1459</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>380</v>
@@ -7419,19 +7446,19 @@
         <v>378</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>1653</v>
+        <v>1645</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>319</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>1466</v>
+        <v>1460</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>1466</v>
+        <v>1460</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>380</v>
@@ -7466,13 +7493,13 @@
         <v>319</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>1467</v>
+        <v>1461</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>1561</v>
+        <v>1555</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>1466</v>
+        <v>1460</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>380</v>
@@ -7510,7 +7537,7 @@
         <v>320</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>1468</v>
+        <v>1462</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>66</v>
@@ -7554,13 +7581,13 @@
         <v>321</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>1469</v>
+        <v>1463</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>1469</v>
+        <v>1463</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>380</v>
@@ -7583,25 +7610,25 @@
         <v>391</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>78</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>1570</v>
+        <v>1564</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>322</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>1470</v>
+        <v>1464</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>1721</v>
+        <v>1708</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>1400</v>
+        <v>1394</v>
       </c>
       <c r="I11" s="11" t="s">
         <v>380</v>
@@ -7628,7 +7655,7 @@
         <v>602</v>
       </c>
       <c r="S11" s="26" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="T11" s="22" t="s">
         <v>840</v>
@@ -7651,25 +7678,25 @@
         <v>391</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1631</v>
+        <v>1623</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>1571</v>
+        <v>1565</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>323</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>1471</v>
+        <v>1465</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>1721</v>
+        <v>1708</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>1714</v>
+        <v>1701</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>380</v>
@@ -7699,7 +7726,7 @@
         <v>602</v>
       </c>
       <c r="S12" s="26" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="T12" s="22" t="s">
         <v>840</v>
@@ -7722,7 +7749,7 @@
         <v>391</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>79</v>
@@ -7734,13 +7761,13 @@
         <v>324</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>1722</v>
+        <v>1709</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>1477</v>
+        <v>1471</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>380</v>
@@ -7771,7 +7798,7 @@
         <v>391</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>395</v>
@@ -7786,10 +7813,10 @@
         <v>67</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>1723</v>
+        <v>1710</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>1612</v>
+        <v>1604</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>380</v>
@@ -7810,7 +7837,7 @@
         <v>602</v>
       </c>
       <c r="S14" s="26" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="T14" s="67" t="s">
         <v>840</v>
@@ -7833,13 +7860,13 @@
         <v>391</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>396</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>1614</v>
+        <v>1606</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>325</v>
@@ -7848,10 +7875,10 @@
         <v>68</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>1723</v>
+        <v>1710</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>1612</v>
+        <v>1604</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>380</v>
@@ -7883,7 +7910,7 @@
         <v>391</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>80</v>
@@ -7895,13 +7922,13 @@
         <v>326</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>1724</v>
+        <v>1711</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>1608</v>
+        <v>1600</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>380</v>
@@ -7938,7 +7965,7 @@
         <v>391</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>81</v>
@@ -7950,13 +7977,13 @@
         <v>326</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>1725</v>
+        <v>1712</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>1609</v>
+        <v>1601</v>
       </c>
       <c r="I17" s="11" t="s">
         <v>380</v>
@@ -7988,7 +8015,7 @@
         <v>391</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>504</v>
@@ -8000,19 +8027,19 @@
         <v>506</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>1474</v>
+        <v>1468</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>1721</v>
+        <v>1708</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>1610</v>
+        <v>1602</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>380</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>1357</v>
+        <v>1351</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>809</v>
@@ -8042,7 +8069,7 @@
         <v>391</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>507</v>
@@ -8054,13 +8081,13 @@
         <v>506</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>1475</v>
+        <v>1469</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>1722</v>
+        <v>1709</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>1611</v>
+        <v>1603</v>
       </c>
       <c r="I19" s="11" t="s">
         <v>380</v>
@@ -8096,7 +8123,7 @@
         <v>391</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>82</v>
@@ -8108,13 +8135,13 @@
         <v>326</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>1476</v>
+        <v>1470</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>1723</v>
+        <v>1710</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>1613</v>
+        <v>1605</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>380</v>
@@ -8152,7 +8179,7 @@
         <v>391</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>83</v>
@@ -8164,13 +8191,13 @@
         <v>326</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>1479</v>
+        <v>1473</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>1732</v>
+        <v>1719</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>1396</v>
+        <v>1390</v>
       </c>
       <c r="I21" s="11" t="s">
         <v>380</v>
@@ -8191,7 +8218,7 @@
         <v>602</v>
       </c>
       <c r="S21" s="26" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="T21" s="67" t="s">
         <v>840</v>
@@ -8214,7 +8241,7 @@
         <v>391</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>84</v>
@@ -8229,10 +8256,10 @@
         <v>494</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>1726</v>
+        <v>1713</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>1397</v>
+        <v>1391</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>380</v>
@@ -8259,31 +8286,31 @@
         <v>391</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>1572</v>
+        <v>1566</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>349</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>1480</v>
+        <v>1474</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>1721</v>
+        <v>1708</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>1398</v>
+        <v>1392</v>
       </c>
       <c r="I23" s="11" t="s">
         <v>380</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>736</v>
@@ -8304,25 +8331,25 @@
         <v>391</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>86</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>1572</v>
+        <v>1566</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>328</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>1481</v>
+        <v>1475</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>1727</v>
+        <v>1714</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>1399</v>
+        <v>1393</v>
       </c>
       <c r="I24" s="11" t="s">
         <v>380</v>
@@ -8349,13 +8376,13 @@
         <v>391</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>87</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>1572</v>
+        <v>1566</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>329</v>
@@ -8364,10 +8391,10 @@
         <v>69</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>1728</v>
+        <v>1715</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="I25" s="11" t="s">
         <v>380</v>
@@ -8394,7 +8421,7 @@
         <v>391</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>88</v>
@@ -8406,13 +8433,13 @@
         <v>330</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>1482</v>
+        <v>1476</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>1722</v>
+        <v>1709</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>1400</v>
+        <v>1394</v>
       </c>
       <c r="I26" s="11" t="s">
         <v>380</v>
@@ -8433,7 +8460,7 @@
         <v>602</v>
       </c>
       <c r="S26" s="26" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="T26" s="22" t="s">
         <v>845</v>
@@ -8456,7 +8483,7 @@
         <v>391</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>89</v>
@@ -8468,19 +8495,19 @@
         <v>331</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>1483</v>
+        <v>1477</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>1729</v>
+        <v>1716</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>1401</v>
+        <v>1395</v>
       </c>
       <c r="I27" s="11" t="s">
         <v>380</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>1672</v>
+        <v>1664</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>733</v>
@@ -8495,7 +8522,7 @@
         <v>602</v>
       </c>
       <c r="S27" s="26" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="T27" s="22" t="s">
         <v>845</v>
@@ -8518,25 +8545,25 @@
         <v>391</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>90</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>1573</v>
+        <v>1567</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>332</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>1484</v>
+        <v>1478</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>1730</v>
+        <v>1717</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>1402</v>
+        <v>1396</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>380</v>
@@ -8563,7 +8590,7 @@
         <v>602</v>
       </c>
       <c r="S28" s="26" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="T28" s="67" t="s">
         <v>840</v>
@@ -8586,25 +8613,25 @@
         <v>391</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>91</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>1574</v>
+        <v>1568</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>333</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>1730</v>
+        <v>1717</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>1403</v>
+        <v>1397</v>
       </c>
       <c r="I29" s="11" t="s">
         <v>380</v>
@@ -8628,7 +8655,7 @@
         <v>602</v>
       </c>
       <c r="S29" s="26" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="T29" s="67" t="s">
         <v>840</v>
@@ -8651,31 +8678,31 @@
         <v>391</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>92</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>1575</v>
+        <v>1569</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>334</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>1730</v>
+        <v>1717</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>1404</v>
+        <v>1398</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>380</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>1576</v>
+        <v>1570</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>731</v>
@@ -8696,25 +8723,25 @@
         <v>391</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>93</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>1575</v>
+        <v>1569</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>334</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>1731</v>
+        <v>1718</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>1405</v>
+        <v>1399</v>
       </c>
       <c r="I31" s="11" t="s">
         <v>380</v>
@@ -8741,7 +8768,7 @@
         <v>391</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>94</v>
@@ -8753,13 +8780,13 @@
         <v>335</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>1673</v>
+        <v>1665</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>1675</v>
+        <v>1667</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>380</v>
@@ -8768,7 +8795,7 @@
         <v>41</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>1677</v>
+        <v>1669</v>
       </c>
       <c r="M32" s="11" t="s">
         <v>66</v>
@@ -8786,7 +8813,7 @@
         <v>391</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>98</v>
@@ -8798,13 +8825,13 @@
         <v>335</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>1488</v>
+        <v>1482</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>1674</v>
+        <v>1666</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>1676</v>
+        <v>1668</v>
       </c>
       <c r="I33" s="11" t="s">
         <v>380</v>
@@ -8813,7 +8840,7 @@
         <v>70</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>1677</v>
+        <v>1669</v>
       </c>
       <c r="M33" s="11" t="s">
         <v>66</v>
@@ -8825,7 +8852,7 @@
         <v>602</v>
       </c>
       <c r="S33" s="26" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="T33" s="67" t="s">
         <v>840</v>
@@ -8848,25 +8875,25 @@
         <v>391</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>1577</v>
+        <v>1571</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>336</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>1489</v>
+        <v>1483</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>1733</v>
+        <v>1720</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>1406</v>
+        <v>1400</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>380</v>
@@ -8893,25 +8920,25 @@
         <v>391</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>96</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>1577</v>
+        <v>1571</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>336</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>1733</v>
+        <v>1720</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>1407</v>
+        <v>1401</v>
       </c>
       <c r="I35" s="11" t="s">
         <v>380</v>
@@ -8938,25 +8965,25 @@
         <v>391</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>767</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>1578</v>
+        <v>1572</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>509</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>1733</v>
+        <v>1720</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>1408</v>
+        <v>1402</v>
       </c>
       <c r="I36" s="11" t="s">
         <v>380</v>
@@ -8980,7 +9007,7 @@
         <v>602</v>
       </c>
       <c r="S36" s="26" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="T36" s="67" t="s">
         <v>840</v>
@@ -9003,7 +9030,7 @@
         <v>391</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>97</v>
@@ -9015,13 +9042,13 @@
         <v>337</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>1492</v>
+        <v>1486</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>1734</v>
+        <v>1721</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>1409</v>
+        <v>1403</v>
       </c>
       <c r="I37" s="11" t="s">
         <v>380</v>
@@ -9042,7 +9069,7 @@
         <v>602</v>
       </c>
       <c r="S37" s="26" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="T37" s="22" t="s">
         <v>849</v>
@@ -9065,7 +9092,7 @@
         <v>391</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C38" s="11" t="s">
         <v>99</v>
@@ -9077,13 +9104,13 @@
         <v>338</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>1493</v>
+        <v>1487</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>1562</v>
+        <v>1556</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="I38" s="11" t="s">
         <v>380</v>
@@ -9104,7 +9131,7 @@
         <v>602</v>
       </c>
       <c r="S38" s="26" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="T38" s="22" t="s">
         <v>849</v>
@@ -9127,25 +9154,25 @@
         <v>391</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C39" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>1358</v>
+        <v>1352</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>339</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>1494</v>
+        <v>1488</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>1735</v>
+        <v>1722</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>1411</v>
+        <v>1405</v>
       </c>
       <c r="I39" s="11" t="s">
         <v>380</v>
@@ -9172,7 +9199,7 @@
         <v>602</v>
       </c>
       <c r="S39" s="26" t="s">
-        <v>1192</v>
+        <v>1186</v>
       </c>
       <c r="T39" s="22" t="s">
         <v>851</v>
@@ -9187,7 +9214,7 @@
         <v>853</v>
       </c>
       <c r="X39" s="25" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="40" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9195,7 +9222,7 @@
         <v>391</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>101</v>
@@ -9207,22 +9234,22 @@
         <v>340</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>1495</v>
+        <v>1489</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>1736</v>
+        <v>1723</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>1412</v>
+        <v>1406</v>
       </c>
       <c r="I40" s="11" t="s">
         <v>380</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>1579</v>
+        <v>1573</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>1580</v>
+        <v>1574</v>
       </c>
       <c r="M40" s="11" t="s">
         <v>66</v>
@@ -9240,7 +9267,7 @@
         <v>391</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>102</v>
@@ -9252,13 +9279,13 @@
         <v>341</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>1496</v>
+        <v>1490</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>1737</v>
+        <v>1724</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>1413</v>
+        <v>1407</v>
       </c>
       <c r="I41" s="11" t="s">
         <v>380</v>
@@ -9284,7 +9311,7 @@
         <v>391</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C42" s="11" t="s">
         <v>103</v>
@@ -9296,13 +9323,13 @@
         <v>342</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>1497</v>
+        <v>1491</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>1738</v>
+        <v>1725</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
       <c r="I42" s="11" t="s">
         <v>380</v>
@@ -9329,7 +9356,7 @@
         <v>391</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C43" s="11" t="s">
         <v>104</v>
@@ -9341,13 +9368,13 @@
         <v>343</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>1498</v>
+        <v>1492</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>1738</v>
+        <v>1725</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
       <c r="I43" s="11" t="s">
         <v>380</v>
@@ -9368,7 +9395,7 @@
         <v>602</v>
       </c>
       <c r="S43" s="26" t="s">
-        <v>1192</v>
+        <v>1186</v>
       </c>
       <c r="T43" s="22" t="s">
         <v>851</v>
@@ -9383,7 +9410,7 @@
         <v>853</v>
       </c>
       <c r="X43" s="25" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="44" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9391,10 +9418,10 @@
         <v>391</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>1581</v>
+        <v>1575</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>577</v>
@@ -9403,19 +9430,19 @@
         <v>343</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>1478</v>
+        <v>1472</v>
       </c>
       <c r="I44" s="11" t="s">
         <v>380</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>1359</v>
+        <v>1353</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>54</v>
@@ -9436,10 +9463,10 @@
         <v>391</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>1582</v>
+        <v>1576</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>577</v>
@@ -9448,19 +9475,19 @@
         <v>343</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>1478</v>
+        <v>1472</v>
       </c>
       <c r="I45" s="11" t="s">
         <v>380</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>1360</v>
+        <v>1354</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>55</v>
@@ -9481,10 +9508,10 @@
         <v>391</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>577</v>
@@ -9493,19 +9520,19 @@
         <v>343</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>1478</v>
+        <v>1472</v>
       </c>
       <c r="I46" s="11" t="s">
         <v>380</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>1361</v>
+        <v>1355</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>56</v>
@@ -9526,7 +9553,7 @@
         <v>391</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C47" s="11" t="s">
         <v>688</v>
@@ -9538,13 +9565,13 @@
         <v>343</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>1739</v>
+        <v>1726</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>1478</v>
+        <v>1472</v>
       </c>
       <c r="I47" s="11" t="s">
         <v>380</v>
@@ -9571,7 +9598,7 @@
         <v>391</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C48" s="11" t="s">
         <v>689</v>
@@ -9583,13 +9610,13 @@
         <v>343</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>1739</v>
+        <v>1726</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>1478</v>
+        <v>1472</v>
       </c>
       <c r="I48" s="11" t="s">
         <v>380</v>
@@ -9616,7 +9643,7 @@
         <v>391</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C49" s="11" t="s">
         <v>690</v>
@@ -9628,13 +9655,13 @@
         <v>343</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>1739</v>
+        <v>1726</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>1478</v>
+        <v>1472</v>
       </c>
       <c r="I49" s="11" t="s">
         <v>380</v>
@@ -9661,7 +9688,7 @@
         <v>391</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>105</v>
@@ -9673,13 +9700,13 @@
         <v>344</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>1499</v>
+        <v>1493</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>1738</v>
+        <v>1725</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>1740</v>
+        <v>1727</v>
       </c>
       <c r="I50" s="11" t="s">
         <v>380</v>
@@ -9706,7 +9733,7 @@
         <v>391</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C51" s="11" t="s">
         <v>106</v>
@@ -9718,19 +9745,19 @@
         <v>791</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>1500</v>
+        <v>1494</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>1741</v>
+        <v>1728</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>1416</v>
+        <v>1410</v>
       </c>
       <c r="I51" s="11" t="s">
         <v>380</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>59</v>
@@ -9751,7 +9778,7 @@
         <v>602</v>
       </c>
       <c r="S51" s="26" t="s">
-        <v>1192</v>
+        <v>1186</v>
       </c>
       <c r="T51" s="22" t="s">
         <v>886</v>
@@ -9774,7 +9801,7 @@
         <v>391</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C52" s="11" t="s">
         <v>107</v>
@@ -9789,10 +9816,10 @@
         <v>411</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>1742</v>
+        <v>1729</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>1416</v>
+        <v>1410</v>
       </c>
       <c r="I52" s="11" t="s">
         <v>380</v>
@@ -9823,7 +9850,7 @@
         <v>391</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C53" s="11" t="s">
         <v>108</v>
@@ -9835,13 +9862,13 @@
         <v>345</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>1743</v>
+        <v>1730</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>1744</v>
+        <v>1731</v>
       </c>
       <c r="I53" s="11" t="s">
         <v>380</v>
@@ -9862,7 +9889,7 @@
         <v>602</v>
       </c>
       <c r="S53" s="26" t="s">
-        <v>1192</v>
+        <v>1186</v>
       </c>
       <c r="T53" s="22" t="s">
         <v>851</v>
@@ -9877,7 +9904,7 @@
         <v>853</v>
       </c>
       <c r="X53" s="25" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="54" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9885,7 +9912,7 @@
         <v>391</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>793</v>
@@ -9900,10 +9927,10 @@
         <v>76</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>1738</v>
+        <v>1725</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>1744</v>
+        <v>1731</v>
       </c>
       <c r="I54" s="11" t="s">
         <v>380</v>
@@ -9929,7 +9956,7 @@
         <v>391</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C55" s="11" t="s">
         <v>109</v>
@@ -9941,19 +9968,19 @@
         <v>794</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>1501</v>
+        <v>1495</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>1738</v>
+        <v>1725</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>1745</v>
+        <v>1732</v>
       </c>
       <c r="I55" s="11" t="s">
         <v>380</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>888</v>
@@ -9973,10 +10000,10 @@
         <v>391</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>1216</v>
+        <v>1210</v>
       </c>
       <c r="D56" s="11" t="s">
         <v>854</v>
@@ -9985,13 +10012,13 @@
         <v>855</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>1746</v>
+        <v>1733</v>
       </c>
       <c r="I56" s="11" t="s">
         <v>380</v>
@@ -10027,7 +10054,7 @@
         <v>391</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C57" s="11" t="s">
         <v>857</v>
@@ -10042,7 +10069,7 @@
         <v>860</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>1237</v>
+        <v>1231</v>
       </c>
       <c r="H57" s="11" t="s">
         <v>861</v>
@@ -10051,7 +10078,7 @@
         <v>380</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>862</v>
@@ -10083,7 +10110,7 @@
         <v>391</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C58" s="11" t="s">
         <v>864</v>
@@ -10098,7 +10125,7 @@
         <v>867</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>1747</v>
+        <v>1734</v>
       </c>
       <c r="H58" s="11" t="s">
         <v>868</v>
@@ -10139,7 +10166,7 @@
         <v>391</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C59" s="11" t="s">
         <v>872</v>
@@ -10151,13 +10178,13 @@
         <v>874</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>1502</v>
+        <v>1496</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>1748</v>
+        <v>1735</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>1417</v>
+        <v>1411</v>
       </c>
       <c r="I59" s="11" t="s">
         <v>380</v>
@@ -10193,7 +10220,7 @@
         <v>391</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C60" s="11" t="s">
         <v>876</v>
@@ -10205,13 +10232,13 @@
         <v>878</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>1503</v>
+        <v>1497</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>1749</v>
+        <v>1736</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>1418</v>
+        <v>1412</v>
       </c>
       <c r="I60" s="11" t="s">
         <v>380</v>
@@ -10247,7 +10274,7 @@
         <v>391</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C61" s="11" t="s">
         <v>880</v>
@@ -10259,13 +10286,13 @@
         <v>882</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>1504</v>
+        <v>1498</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>1750</v>
+        <v>1737</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>1419</v>
+        <v>1413</v>
       </c>
       <c r="I61" s="11" t="s">
         <v>380</v>
@@ -10301,31 +10328,31 @@
         <v>391</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C62" s="11" t="s">
         <v>884</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>1362</v>
+        <v>1356</v>
       </c>
       <c r="E62" s="11" t="s">
         <v>885</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>1505</v>
+        <v>1499</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>1751</v>
+        <v>1738</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>1420</v>
+        <v>1414</v>
       </c>
       <c r="I62" s="11" t="s">
         <v>380</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>875</v>
@@ -10367,13 +10394,13 @@
         <v>350</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>1421</v>
+        <v>1415</v>
       </c>
       <c r="G63" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>1421</v>
+        <v>1415</v>
       </c>
       <c r="I63" s="11" t="s">
         <v>380</v>
@@ -10394,7 +10421,7 @@
         <v>602</v>
       </c>
       <c r="S63" s="26" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="T63" s="22" t="s">
         <v>889</v>
@@ -10429,13 +10456,13 @@
         <v>350</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>1422</v>
+        <v>1416</v>
       </c>
       <c r="G64" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>1422</v>
+        <v>1416</v>
       </c>
       <c r="I64" s="11" t="s">
         <v>380</v>
@@ -10456,7 +10483,7 @@
         <v>602</v>
       </c>
       <c r="S64" s="26" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="T64" s="22" t="s">
         <v>889</v>
@@ -10518,7 +10545,7 @@
         <v>602</v>
       </c>
       <c r="S65" s="26" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="T65" s="22" t="s">
         <v>889</v>
@@ -10580,7 +10607,7 @@
         <v>602</v>
       </c>
       <c r="S66" s="26" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="T66" s="22" t="s">
         <v>889</v>
@@ -10661,7 +10688,7 @@
         <v>351</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>1238</v>
+        <v>1232</v>
       </c>
       <c r="G68" s="11" t="s">
         <v>154</v>
@@ -10688,7 +10715,7 @@
         <v>602</v>
       </c>
       <c r="S68" s="26" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="T68" s="22" t="s">
         <v>889</v>
@@ -10723,7 +10750,7 @@
         <v>351</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="G69" s="11" t="s">
         <v>153</v>
@@ -10756,7 +10783,7 @@
         <v>602</v>
       </c>
       <c r="S69" s="26" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="T69" s="22" t="s">
         <v>889</v>
@@ -10791,13 +10818,13 @@
         <v>352</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>1506</v>
+        <v>1500</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>1563</v>
+        <v>1557</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>1423</v>
+        <v>1417</v>
       </c>
       <c r="I70" s="11" t="s">
         <v>380</v>
@@ -10821,7 +10848,7 @@
         <v>602</v>
       </c>
       <c r="S70" s="26" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="T70" s="22" t="s">
         <v>893</v>
@@ -10856,13 +10883,13 @@
         <v>353</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>1507</v>
+        <v>1501</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>1564</v>
+        <v>1558</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>1424</v>
+        <v>1418</v>
       </c>
       <c r="I71" s="11" t="s">
         <v>380</v>
@@ -10880,7 +10907,7 @@
         <v>602</v>
       </c>
       <c r="S71" s="26" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="T71" s="22" t="s">
         <v>893</v>
@@ -10915,13 +10942,13 @@
         <v>354</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>1508</v>
+        <v>1502</v>
       </c>
       <c r="G72" s="11" t="s">
-        <v>1565</v>
+        <v>1559</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>1425</v>
+        <v>1419</v>
       </c>
       <c r="I72" s="11" t="s">
         <v>380</v>
@@ -10945,7 +10972,7 @@
         <v>602</v>
       </c>
       <c r="S72" s="26" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="T72" s="22" t="s">
         <v>893</v>
@@ -10980,13 +11007,13 @@
         <v>355</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>1509</v>
+        <v>1503</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>1566</v>
+        <v>1560</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>1426</v>
+        <v>1420</v>
       </c>
       <c r="I73" s="11" t="s">
         <v>380</v>
@@ -11021,13 +11048,13 @@
         <v>355</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>1510</v>
+        <v>1504</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>1566</v>
+        <v>1560</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>1426</v>
+        <v>1420</v>
       </c>
       <c r="I74" s="11" t="s">
         <v>380</v>
@@ -11065,13 +11092,13 @@
         <v>356</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>1511</v>
+        <v>1505</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>1759</v>
+        <v>1746</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>1427</v>
+        <v>1421</v>
       </c>
       <c r="I75" s="11" t="s">
         <v>380</v>
@@ -11109,13 +11136,13 @@
         <v>357</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>1512</v>
+        <v>1506</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>1752</v>
+        <v>1739</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>1428</v>
+        <v>1422</v>
       </c>
       <c r="I76" s="11" t="s">
         <v>380</v>
@@ -11150,13 +11177,13 @@
         <v>358</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>1513</v>
+        <v>1507</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>1753</v>
+        <v>1740</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>1429</v>
+        <v>1423</v>
       </c>
       <c r="I77" s="11" t="s">
         <v>380</v>
@@ -11191,13 +11218,13 @@
         <v>358</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>1514</v>
+        <v>1508</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>1754</v>
+        <v>1741</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="I78" s="11" t="s">
         <v>380</v>
@@ -11232,13 +11259,13 @@
         <v>358</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>1515</v>
+        <v>1509</v>
       </c>
       <c r="G79" s="11" t="s">
-        <v>1755</v>
+        <v>1742</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>1431</v>
+        <v>1425</v>
       </c>
       <c r="I79" s="11" t="s">
         <v>380</v>
@@ -11273,13 +11300,13 @@
         <v>358</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>1516</v>
+        <v>1510</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>1756</v>
+        <v>1743</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>1432</v>
+        <v>1426</v>
       </c>
       <c r="I80" s="11" t="s">
         <v>380</v>
@@ -11314,13 +11341,13 @@
         <v>358</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>1517</v>
+        <v>1511</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>1757</v>
+        <v>1744</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>1433</v>
+        <v>1427</v>
       </c>
       <c r="I81" s="11" t="s">
         <v>380</v>
@@ -11355,13 +11382,13 @@
         <v>358</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>1518</v>
+        <v>1512</v>
       </c>
       <c r="G82" s="11" t="s">
-        <v>1758</v>
+        <v>1745</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="I82" s="11" t="s">
         <v>380</v>
@@ -11390,7 +11417,7 @@
         <v>685</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>1363</v>
+        <v>1357</v>
       </c>
       <c r="E83" s="11" t="s">
         <v>372</v>
@@ -11399,7 +11426,7 @@
         <v>308</v>
       </c>
       <c r="G83" s="11" t="s">
-        <v>1240</v>
+        <v>1234</v>
       </c>
       <c r="H83" s="11" t="s">
         <v>436</v>
@@ -11429,7 +11456,7 @@
         <v>602</v>
       </c>
       <c r="S83" s="26" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="T83" s="22" t="s">
         <v>893</v>
@@ -11458,7 +11485,7 @@
         <v>706</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>1363</v>
+        <v>1357</v>
       </c>
       <c r="E84" s="15" t="s">
         <v>372</v>
@@ -11467,7 +11494,7 @@
         <v>707</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>1241</v>
+        <v>1235</v>
       </c>
       <c r="H84" s="11" t="s">
         <v>436</v>
@@ -11502,7 +11529,7 @@
         <v>709</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>1363</v>
+        <v>1357</v>
       </c>
       <c r="E85" s="15" t="s">
         <v>372</v>
@@ -11511,7 +11538,7 @@
         <v>710</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="H85" s="11" t="s">
         <v>436</v>
@@ -11546,7 +11573,7 @@
         <v>712</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>1363</v>
+        <v>1357</v>
       </c>
       <c r="E86" s="15" t="s">
         <v>372</v>
@@ -11555,7 +11582,7 @@
         <v>713</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="H86" s="11" t="s">
         <v>436</v>
@@ -11590,7 +11617,7 @@
         <v>715</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>1363</v>
+        <v>1357</v>
       </c>
       <c r="E87" s="15" t="s">
         <v>372</v>
@@ -11599,7 +11626,7 @@
         <v>716</v>
       </c>
       <c r="G87" s="11" t="s">
-        <v>1244</v>
+        <v>1238</v>
       </c>
       <c r="H87" s="11" t="s">
         <v>436</v>
@@ -11634,7 +11661,7 @@
         <v>746</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>1364</v>
+        <v>1358</v>
       </c>
       <c r="E88" s="15" t="s">
         <v>372</v>
@@ -11643,7 +11670,7 @@
         <v>751</v>
       </c>
       <c r="G88" s="11" t="s">
-        <v>1245</v>
+        <v>1239</v>
       </c>
       <c r="H88" s="11" t="s">
         <v>436</v>
@@ -11678,7 +11705,7 @@
         <v>747</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>1364</v>
+        <v>1358</v>
       </c>
       <c r="E89" s="15" t="s">
         <v>372</v>
@@ -11687,7 +11714,7 @@
         <v>752</v>
       </c>
       <c r="G89" s="11" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
       <c r="H89" s="11" t="s">
         <v>436</v>
@@ -11722,7 +11749,7 @@
         <v>748</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>1364</v>
+        <v>1358</v>
       </c>
       <c r="E90" s="15" t="s">
         <v>372</v>
@@ -11731,7 +11758,7 @@
         <v>753</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>1247</v>
+        <v>1241</v>
       </c>
       <c r="H90" s="11" t="s">
         <v>436</v>
@@ -11766,7 +11793,7 @@
         <v>749</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>1364</v>
+        <v>1358</v>
       </c>
       <c r="E91" s="15" t="s">
         <v>372</v>
@@ -11775,7 +11802,7 @@
         <v>754</v>
       </c>
       <c r="G91" s="11" t="s">
-        <v>1248</v>
+        <v>1242</v>
       </c>
       <c r="H91" s="11" t="s">
         <v>436</v>
@@ -11810,7 +11837,7 @@
         <v>750</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>1364</v>
+        <v>1358</v>
       </c>
       <c r="E92" s="15" t="s">
         <v>372</v>
@@ -11819,7 +11846,7 @@
         <v>755</v>
       </c>
       <c r="G92" s="11" t="s">
-        <v>1249</v>
+        <v>1243</v>
       </c>
       <c r="H92" s="11" t="s">
         <v>436</v>
@@ -11848,7 +11875,7 @@
         <v>391</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C93" s="11" t="s">
         <v>178</v>
@@ -11857,16 +11884,16 @@
         <v>586</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>1250</v>
+        <v>1244</v>
       </c>
       <c r="G93" s="11" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="I93" s="11" t="s">
         <v>380</v>
@@ -11884,7 +11911,7 @@
         <v>6</v>
       </c>
       <c r="P93" s="11" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
       <c r="Q93" s="11">
         <v>1</v>
@@ -11893,7 +11920,7 @@
         <v>602</v>
       </c>
       <c r="S93" s="22" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="T93" s="22" t="s">
         <v>903</v>
@@ -11902,7 +11929,7 @@
         <v>1</v>
       </c>
       <c r="V93" s="22" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="W93" s="22" t="s">
         <v>900</v>
@@ -11916,7 +11943,7 @@
         <v>391</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C94" s="11" t="s">
         <v>179</v>
@@ -11925,16 +11952,16 @@
         <v>587</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>1252</v>
+        <v>1246</v>
       </c>
       <c r="G94" s="11" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="I94" s="11" t="s">
         <v>380</v>
@@ -11961,7 +11988,7 @@
         <v>391</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C95" s="11" t="s">
         <v>183</v>
@@ -11970,16 +11997,16 @@
         <v>161</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="F95" s="11" t="s">
         <v>274</v>
       </c>
       <c r="G95" s="11" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="I95" s="11" t="s">
         <v>380</v>
@@ -12006,7 +12033,7 @@
         <v>391</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C96" s="11" t="s">
         <v>184</v>
@@ -12015,16 +12042,16 @@
         <v>162</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="F96" s="11" t="s">
         <v>274</v>
       </c>
       <c r="G96" s="11" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="I96" s="11" t="s">
         <v>380</v>
@@ -12045,7 +12072,7 @@
         <v>602</v>
       </c>
       <c r="S96" s="22" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="T96" s="22" t="s">
         <v>903</v>
@@ -12054,7 +12081,7 @@
         <v>2</v>
       </c>
       <c r="V96" s="22" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="W96" s="22" t="s">
         <v>900</v>
@@ -12068,7 +12095,7 @@
         <v>391</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C97" s="11" t="s">
         <v>185</v>
@@ -12077,16 +12104,16 @@
         <v>163</v>
       </c>
       <c r="E97" s="11" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="F97" s="11" t="s">
         <v>270</v>
       </c>
       <c r="G97" s="11" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="H97" s="11" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="I97" s="11" t="s">
         <v>380</v>
@@ -12113,7 +12140,7 @@
         <v>391</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C98" s="11" t="s">
         <v>186</v>
@@ -12122,16 +12149,16 @@
         <v>163</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="F98" s="11" t="s">
         <v>198</v>
       </c>
       <c r="G98" s="11" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="H98" s="11" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="I98" s="11" t="s">
         <v>380</v>
@@ -12158,7 +12185,7 @@
         <v>391</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C99" s="11" t="s">
         <v>187</v>
@@ -12167,16 +12194,16 @@
         <v>163</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="F99" s="11" t="s">
         <v>197</v>
       </c>
       <c r="G99" s="11" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="H99" s="11" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="I99" s="11" t="s">
         <v>380</v>
@@ -12203,7 +12230,7 @@
         <v>391</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C100" s="11" t="s">
         <v>188</v>
@@ -12212,16 +12239,16 @@
         <v>167</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="F100" s="11" t="s">
         <v>270</v>
       </c>
       <c r="G100" s="11" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="I100" s="11" t="s">
         <v>380</v>
@@ -12248,7 +12275,7 @@
         <v>391</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C101" s="11" t="s">
         <v>189</v>
@@ -12257,16 +12284,16 @@
         <v>167</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="F101" s="11" t="s">
         <v>198</v>
       </c>
       <c r="G101" s="11" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="H101" s="11" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="I101" s="11" t="s">
         <v>380</v>
@@ -12293,7 +12320,7 @@
         <v>391</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C102" s="11" t="s">
         <v>190</v>
@@ -12302,16 +12329,16 @@
         <v>167</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="F102" s="11" t="s">
         <v>197</v>
       </c>
       <c r="G102" s="11" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="I102" s="11" t="s">
         <v>380</v>
@@ -12338,7 +12365,7 @@
         <v>391</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C103" s="11" t="s">
         <v>191</v>
@@ -12347,16 +12374,16 @@
         <v>588</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>1519</v>
+        <v>1513</v>
       </c>
       <c r="G103" s="11" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="H103" s="11" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="I103" s="11" t="s">
         <v>380</v>
@@ -12377,7 +12404,7 @@
         <v>602</v>
       </c>
       <c r="S103" s="22" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="T103" s="22" t="s">
         <v>903</v>
@@ -12386,7 +12413,7 @@
         <v>3</v>
       </c>
       <c r="V103" s="22" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="W103" s="22" t="s">
         <v>900</v>
@@ -12400,7 +12427,7 @@
         <v>391</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C104" s="11" t="s">
         <v>192</v>
@@ -12409,16 +12436,16 @@
         <v>588</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="F104" s="11" t="s">
-        <v>1520</v>
+        <v>1514</v>
       </c>
       <c r="G104" s="11" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="I104" s="11" t="s">
         <v>380</v>
@@ -12444,7 +12471,7 @@
         <v>391</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C105" s="11" t="s">
         <v>193</v>
@@ -12453,16 +12480,16 @@
         <v>588</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>1521</v>
+        <v>1515</v>
       </c>
       <c r="G105" s="11" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="H105" s="11" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="I105" s="11" t="s">
         <v>380</v>
@@ -12489,7 +12516,7 @@
         <v>602</v>
       </c>
       <c r="S105" s="22" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="T105" s="22" t="s">
         <v>903</v>
@@ -12498,7 +12525,7 @@
         <v>4</v>
       </c>
       <c r="V105" s="22" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="W105" s="22" t="s">
         <v>900</v>
@@ -12512,7 +12539,7 @@
         <v>391</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C106" s="11" t="s">
         <v>194</v>
@@ -12521,16 +12548,16 @@
         <v>172</v>
       </c>
       <c r="E106" s="11" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="F106" s="11" t="s">
         <v>271</v>
       </c>
       <c r="G106" s="11" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="H106" s="11" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="I106" s="11" t="s">
         <v>380</v>
@@ -12556,7 +12583,7 @@
         <v>391</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C107" s="11" t="s">
         <v>195</v>
@@ -12565,16 +12592,16 @@
         <v>589</v>
       </c>
       <c r="E107" s="11" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>1522</v>
+        <v>1516</v>
       </c>
       <c r="G107" s="11" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="H107" s="11" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="I107" s="11" t="s">
         <v>380</v>
@@ -12601,7 +12628,7 @@
         <v>602</v>
       </c>
       <c r="S107" s="22" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="T107" s="22" t="s">
         <v>903</v>
@@ -12610,7 +12637,7 @@
         <v>5</v>
       </c>
       <c r="V107" s="22" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="W107" s="22" t="s">
         <v>900</v>
@@ -12624,7 +12651,7 @@
         <v>391</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C108" s="11" t="s">
         <v>196</v>
@@ -12639,10 +12666,10 @@
         <v>199</v>
       </c>
       <c r="G108" s="11" t="s">
-        <v>1254</v>
+        <v>1248</v>
       </c>
       <c r="H108" s="11" t="s">
-        <v>1633</v>
+        <v>1625</v>
       </c>
       <c r="I108" s="11" t="s">
         <v>380</v>
@@ -12663,7 +12690,7 @@
         <v>602</v>
       </c>
       <c r="S108" s="22" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="T108" s="22" t="s">
         <v>903</v>
@@ -12672,7 +12699,7 @@
         <v>6</v>
       </c>
       <c r="V108" s="22" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="W108" s="22" t="s">
         <v>900</v>
@@ -12686,25 +12713,25 @@
         <v>391</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="C109" s="11" t="s">
         <v>207</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>1585</v>
+        <v>1579</v>
       </c>
       <c r="E109" s="11" t="s">
         <v>902</v>
       </c>
       <c r="F109" s="11" t="s">
-        <v>1523</v>
+        <v>1517</v>
       </c>
       <c r="G109" s="11" t="s">
-        <v>1760</v>
+        <v>1747</v>
       </c>
       <c r="H109" s="11" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="I109" s="11" t="s">
         <v>380</v>
@@ -12730,7 +12757,7 @@
         <v>391</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="C110" s="11" t="s">
         <v>208</v>
@@ -12742,13 +12769,13 @@
         <v>359</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>1524</v>
+        <v>1518</v>
       </c>
       <c r="G110" s="11" t="s">
-        <v>1761</v>
+        <v>1748</v>
       </c>
       <c r="H110" s="11" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="I110" s="11" t="s">
         <v>380</v>
@@ -12774,25 +12801,25 @@
         <v>391</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>1667</v>
+        <v>1659</v>
       </c>
       <c r="E111" s="11" t="s">
         <v>360</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>1525</v>
+        <v>1519</v>
       </c>
       <c r="G111" s="11" t="s">
-        <v>1762</v>
+        <v>1749</v>
       </c>
       <c r="H111" s="11" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="I111" s="11" t="s">
         <v>380</v>
@@ -12818,25 +12845,25 @@
         <v>391</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>1587</v>
+        <v>1581</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>1667</v>
+        <v>1659</v>
       </c>
       <c r="E112" s="11" t="s">
         <v>360</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>1526</v>
+        <v>1520</v>
       </c>
       <c r="G112" s="11" t="s">
-        <v>1763</v>
+        <v>1750</v>
       </c>
       <c r="H112" s="11" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="I112" s="11" t="s">
         <v>380</v>
@@ -12862,25 +12889,25 @@
         <v>391</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="C113" s="11" t="s">
         <v>223</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>1588</v>
+        <v>1582</v>
       </c>
       <c r="E113" s="11" t="s">
         <v>906</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>1527</v>
+        <v>1521</v>
       </c>
       <c r="G113" s="11" t="s">
-        <v>1764</v>
+        <v>1751</v>
       </c>
       <c r="H113" s="11" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="I113" s="11" t="s">
         <v>380</v>
@@ -12901,22 +12928,22 @@
         <v>602</v>
       </c>
       <c r="S113" s="25" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="T113" s="22" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="U113" s="23">
         <v>6</v>
       </c>
       <c r="V113" s="22" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="W113" s="22" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="X113" s="25" t="s">
-        <v>1644</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="114" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12924,7 +12951,7 @@
         <v>391</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="C114" s="11" t="s">
         <v>392</v>
@@ -12936,13 +12963,13 @@
         <v>361</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>1528</v>
+        <v>1522</v>
       </c>
       <c r="G114" s="11" t="s">
-        <v>1765</v>
+        <v>1752</v>
       </c>
       <c r="H114" s="11" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="I114" s="11" t="s">
         <v>380</v>
@@ -12968,7 +12995,7 @@
         <v>391</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="C115" s="11" t="s">
         <v>393</v>
@@ -12980,13 +13007,13 @@
         <v>361</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>1529</v>
+        <v>1523</v>
       </c>
       <c r="G115" s="11" t="s">
-        <v>1766</v>
+        <v>1753</v>
       </c>
       <c r="H115" s="11" t="s">
-        <v>1441</v>
+        <v>1435</v>
       </c>
       <c r="I115" s="11" t="s">
         <v>380</v>
@@ -13012,25 +13039,25 @@
         <v>391</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>1589</v>
+        <v>1583</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="E116" s="11" t="s">
         <v>362</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>1530</v>
+        <v>1524</v>
       </c>
       <c r="G116" s="11" t="s">
-        <v>1767</v>
+        <v>1754</v>
       </c>
       <c r="H116" s="11" t="s">
-        <v>1442</v>
+        <v>1436</v>
       </c>
       <c r="I116" s="11" t="s">
         <v>380</v>
@@ -13056,25 +13083,25 @@
         <v>391</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>1590</v>
+        <v>1584</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="E117" s="11" t="s">
         <v>362</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
       <c r="G117" s="11" t="s">
-        <v>1768</v>
+        <v>1755</v>
       </c>
       <c r="H117" s="11" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="I117" s="11" t="s">
         <v>380</v>
@@ -13100,25 +13127,25 @@
         <v>391</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="C118" s="11" t="s">
         <v>224</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>1591</v>
+        <v>1585</v>
       </c>
       <c r="E118" s="11" t="s">
         <v>901</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
       <c r="G118" s="11" t="s">
-        <v>1769</v>
+        <v>1756</v>
       </c>
       <c r="H118" s="11" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="I118" s="11" t="s">
         <v>380</v>
@@ -13144,7 +13171,7 @@
         <v>391</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="C119" s="11" t="s">
         <v>225</v>
@@ -13156,13 +13183,13 @@
         <v>363</v>
       </c>
       <c r="F119" s="11" t="s">
-        <v>1533</v>
+        <v>1527</v>
       </c>
       <c r="G119" s="11" t="s">
-        <v>1770</v>
+        <v>1757</v>
       </c>
       <c r="H119" s="11" t="s">
-        <v>1445</v>
+        <v>1439</v>
       </c>
       <c r="I119" s="11" t="s">
         <v>380</v>
@@ -13188,25 +13215,25 @@
         <v>391</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="E120" s="11" t="s">
         <v>364</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
       <c r="G120" s="11" t="s">
-        <v>1771</v>
+        <v>1758</v>
       </c>
       <c r="H120" s="11" t="s">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="I120" s="11" t="s">
         <v>380</v>
@@ -13232,25 +13259,25 @@
         <v>391</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="C121" s="36" t="s">
-        <v>1593</v>
+        <v>1587</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="E121" s="36" t="s">
         <v>364</v>
       </c>
       <c r="F121" s="11" t="s">
-        <v>1535</v>
+        <v>1529</v>
       </c>
       <c r="G121" s="11" t="s">
-        <v>1772</v>
+        <v>1759</v>
       </c>
       <c r="H121" s="11" t="s">
-        <v>1447</v>
+        <v>1441</v>
       </c>
       <c r="I121" s="36" t="s">
         <v>380</v>
@@ -13276,25 +13303,25 @@
         <v>391</v>
       </c>
       <c r="B122" s="36" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="C122" s="36" t="s">
         <v>231</v>
       </c>
       <c r="D122" s="36" t="s">
-        <v>1350</v>
+        <v>1344</v>
       </c>
       <c r="E122" s="36" t="s">
         <v>365</v>
       </c>
       <c r="F122" s="11" t="s">
-        <v>1536</v>
+        <v>1530</v>
       </c>
       <c r="G122" s="11" t="s">
-        <v>1773</v>
+        <v>1760</v>
       </c>
       <c r="H122" s="11" t="s">
-        <v>1448</v>
+        <v>1442</v>
       </c>
       <c r="I122" s="36" t="s">
         <v>380</v>
@@ -13318,19 +13345,19 @@
         <v>309</v>
       </c>
       <c r="T122" s="25" t="s">
-        <v>1159</v>
+        <v>1153</v>
       </c>
       <c r="U122" s="38">
         <v>1</v>
       </c>
       <c r="V122" s="37" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
       <c r="W122" s="37" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
       <c r="X122" s="37" t="s">
-        <v>1160</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="123" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -13338,7 +13365,7 @@
         <v>391</v>
       </c>
       <c r="B123" s="36" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="C123" s="11" t="s">
         <v>232</v>
@@ -13350,13 +13377,13 @@
         <v>528</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>1537</v>
+        <v>1531</v>
       </c>
       <c r="G123" s="11" t="s">
-        <v>1774</v>
+        <v>1761</v>
       </c>
       <c r="H123" s="11" t="s">
-        <v>1449</v>
+        <v>1443</v>
       </c>
       <c r="I123" s="11" t="s">
         <v>380</v>
@@ -13382,7 +13409,7 @@
         <v>391</v>
       </c>
       <c r="B124" s="36" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="C124" s="11" t="s">
         <v>233</v>
@@ -13394,13 +13421,13 @@
         <v>528</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>1538</v>
+        <v>1532</v>
       </c>
       <c r="G124" s="11" t="s">
-        <v>1775</v>
+        <v>1762</v>
       </c>
       <c r="H124" s="11" t="s">
-        <v>1450</v>
+        <v>1444</v>
       </c>
       <c r="I124" s="11" t="s">
         <v>380</v>
@@ -13426,25 +13453,25 @@
         <v>391</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="C125" s="11" t="s">
         <v>241</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="E125" s="11" t="s">
-        <v>1346</v>
+        <v>1340</v>
       </c>
       <c r="F125" s="11" t="s">
-        <v>1539</v>
+        <v>1533</v>
       </c>
       <c r="G125" s="11" t="s">
-        <v>1776</v>
+        <v>1763</v>
       </c>
       <c r="H125" s="11" t="s">
-        <v>1451</v>
+        <v>1445</v>
       </c>
       <c r="I125" s="11" t="s">
         <v>380</v>
@@ -13465,22 +13492,22 @@
         <v>602</v>
       </c>
       <c r="S125" s="37" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="T125" s="37" t="s">
-        <v>1169</v>
+        <v>1163</v>
       </c>
       <c r="U125" s="38">
         <v>1</v>
       </c>
       <c r="V125" s="37" t="s">
-        <v>1167</v>
+        <v>1161</v>
       </c>
       <c r="W125" s="37" t="s">
+        <v>1162</v>
+      </c>
+      <c r="X125" s="37" t="s">
         <v>1168</v>
-      </c>
-      <c r="X125" s="37" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="126" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -13488,25 +13515,25 @@
         <v>391</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="C126" s="11" t="s">
         <v>242</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="E126" s="11" t="s">
-        <v>1346</v>
+        <v>1340</v>
       </c>
       <c r="F126" s="11" t="s">
-        <v>1540</v>
+        <v>1534</v>
       </c>
       <c r="G126" s="11" t="s">
-        <v>1777</v>
+        <v>1764</v>
       </c>
       <c r="H126" s="11" t="s">
-        <v>1452</v>
+        <v>1446</v>
       </c>
       <c r="I126" s="11" t="s">
         <v>380</v>
@@ -13527,22 +13554,22 @@
         <v>602</v>
       </c>
       <c r="S126" s="37" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="T126" s="37" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="U126" s="38">
         <v>1</v>
       </c>
       <c r="V126" s="37" t="s">
+        <v>1161</v>
+      </c>
+      <c r="W126" s="37" t="s">
+        <v>1162</v>
+      </c>
+      <c r="X126" s="37" t="s">
         <v>1167</v>
-      </c>
-      <c r="W126" s="37" t="s">
-        <v>1168</v>
-      </c>
-      <c r="X126" s="37" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="127" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -13550,25 +13577,25 @@
         <v>391</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="C127" s="11" t="s">
         <v>243</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="E127" s="11" t="s">
-        <v>1346</v>
+        <v>1340</v>
       </c>
       <c r="F127" s="11" t="s">
-        <v>1541</v>
+        <v>1535</v>
       </c>
       <c r="G127" s="11" t="s">
-        <v>1778</v>
+        <v>1765</v>
       </c>
       <c r="H127" s="11" t="s">
-        <v>1453</v>
+        <v>1447</v>
       </c>
       <c r="I127" s="11" t="s">
         <v>380</v>
@@ -13589,22 +13616,22 @@
         <v>602</v>
       </c>
       <c r="S127" s="37" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="T127" s="37" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="U127" s="38">
         <v>2</v>
       </c>
       <c r="V127" s="37" t="s">
+        <v>1161</v>
+      </c>
+      <c r="W127" s="37" t="s">
+        <v>1162</v>
+      </c>
+      <c r="X127" s="37" t="s">
         <v>1167</v>
-      </c>
-      <c r="W127" s="37" t="s">
-        <v>1168</v>
-      </c>
-      <c r="X127" s="37" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="128" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -13612,25 +13639,25 @@
         <v>391</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="C128" s="11" t="s">
         <v>244</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="E128" s="11" t="s">
-        <v>1346</v>
+        <v>1340</v>
       </c>
       <c r="F128" s="11" t="s">
-        <v>1542</v>
+        <v>1536</v>
       </c>
       <c r="G128" s="11" t="s">
-        <v>1779</v>
+        <v>1766</v>
       </c>
       <c r="H128" s="11" t="s">
-        <v>1454</v>
+        <v>1448</v>
       </c>
       <c r="I128" s="11" t="s">
         <v>380</v>
@@ -13651,22 +13678,22 @@
         <v>602</v>
       </c>
       <c r="S128" s="37" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="T128" s="37" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="U128" s="38">
         <v>3</v>
       </c>
       <c r="V128" s="37" t="s">
+        <v>1161</v>
+      </c>
+      <c r="W128" s="37" t="s">
+        <v>1162</v>
+      </c>
+      <c r="X128" s="37" t="s">
         <v>1167</v>
-      </c>
-      <c r="W128" s="37" t="s">
-        <v>1168</v>
-      </c>
-      <c r="X128" s="37" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="129" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -13674,25 +13701,25 @@
         <v>391</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="C129" s="11" t="s">
         <v>245</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="E129" s="11" t="s">
-        <v>1346</v>
+        <v>1340</v>
       </c>
       <c r="F129" s="11" t="s">
-        <v>1543</v>
+        <v>1537</v>
       </c>
       <c r="G129" s="11" t="s">
-        <v>1780</v>
+        <v>1767</v>
       </c>
       <c r="H129" s="11" t="s">
-        <v>1455</v>
+        <v>1449</v>
       </c>
       <c r="I129" s="11" t="s">
         <v>380</v>
@@ -13713,22 +13740,22 @@
         <v>602</v>
       </c>
       <c r="S129" s="37" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="T129" s="37" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="U129" s="38">
         <v>1</v>
       </c>
       <c r="V129" s="37" t="s">
-        <v>1167</v>
+        <v>1161</v>
       </c>
       <c r="W129" s="37" t="s">
-        <v>1168</v>
+        <v>1162</v>
       </c>
       <c r="X129" s="37" t="s">
-        <v>1175</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="130" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -13736,25 +13763,25 @@
         <v>391</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="C130" s="11" t="s">
         <v>246</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="E130" s="11" t="s">
-        <v>1346</v>
+        <v>1340</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>1544</v>
+        <v>1538</v>
       </c>
       <c r="G130" s="11" t="s">
-        <v>1781</v>
+        <v>1768</v>
       </c>
       <c r="H130" s="11" t="s">
-        <v>1456</v>
+        <v>1450</v>
       </c>
       <c r="I130" s="11" t="s">
         <v>380</v>
@@ -13775,22 +13802,22 @@
         <v>602</v>
       </c>
       <c r="S130" s="37" t="s">
+        <v>1160</v>
+      </c>
+      <c r="T130" s="37" t="s">
         <v>1166</v>
-      </c>
-      <c r="T130" s="37" t="s">
-        <v>1172</v>
       </c>
       <c r="U130" s="38">
         <v>1</v>
       </c>
       <c r="V130" s="37" t="s">
-        <v>1167</v>
+        <v>1161</v>
       </c>
       <c r="W130" s="37" t="s">
-        <v>1168</v>
+        <v>1162</v>
       </c>
       <c r="X130" s="37" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="131" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -13798,25 +13825,25 @@
         <v>391</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="C131" s="11" t="s">
         <v>272</v>
       </c>
       <c r="D131" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="E131" s="11" t="s">
-        <v>1346</v>
+        <v>1340</v>
       </c>
       <c r="F131" s="11" t="s">
-        <v>1545</v>
+        <v>1539</v>
       </c>
       <c r="G131" s="11" t="s">
-        <v>1782</v>
+        <v>1769</v>
       </c>
       <c r="H131" s="11" t="s">
-        <v>1457</v>
+        <v>1451</v>
       </c>
       <c r="I131" s="11" t="s">
         <v>380</v>
@@ -13837,22 +13864,22 @@
         <v>602</v>
       </c>
       <c r="S131" s="37" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="T131" s="37" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="U131" s="38">
         <v>4</v>
       </c>
       <c r="V131" s="37" t="s">
+        <v>1161</v>
+      </c>
+      <c r="W131" s="37" t="s">
+        <v>1162</v>
+      </c>
+      <c r="X131" s="37" t="s">
         <v>1167</v>
-      </c>
-      <c r="W131" s="37" t="s">
-        <v>1168</v>
-      </c>
-      <c r="X131" s="37" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="132" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
@@ -13860,7 +13887,7 @@
         <v>391</v>
       </c>
       <c r="B132" s="16" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C132" s="16" t="s">
         <v>532</v>
@@ -13872,13 +13899,13 @@
         <v>908</v>
       </c>
       <c r="F132" s="16" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="G132" s="16" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
       <c r="H132" s="16" t="s">
-        <v>1458</v>
+        <v>1452</v>
       </c>
       <c r="I132" s="16" t="s">
         <v>380</v>
@@ -13903,22 +13930,22 @@
         <v>602</v>
       </c>
       <c r="S132" s="37" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="T132" s="37" t="s">
-        <v>1183</v>
+        <v>1177</v>
       </c>
       <c r="U132" s="38">
         <v>1</v>
       </c>
       <c r="V132" s="37" t="s">
+        <v>1175</v>
+      </c>
+      <c r="W132" s="37" t="s">
+        <v>1176</v>
+      </c>
+      <c r="X132" s="37" t="s">
         <v>1181</v>
-      </c>
-      <c r="W132" s="37" t="s">
-        <v>1182</v>
-      </c>
-      <c r="X132" s="37" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="133" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
@@ -13926,10 +13953,10 @@
         <v>391</v>
       </c>
       <c r="B133" s="16" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C133" s="16" t="s">
-        <v>1594</v>
+        <v>1588</v>
       </c>
       <c r="D133" s="16" t="s">
         <v>533</v>
@@ -13938,13 +13965,13 @@
         <v>908</v>
       </c>
       <c r="F133" s="16" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="G133" s="16" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="H133" s="16" t="s">
-        <v>1459</v>
+        <v>1453</v>
       </c>
       <c r="I133" s="16" t="s">
         <v>380</v>
@@ -13978,22 +14005,22 @@
         <v>391</v>
       </c>
       <c r="B134" s="16" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C134" s="16" t="s">
         <v>909</v>
       </c>
       <c r="D134" s="16" t="s">
-        <v>1678</v>
+        <v>1670</v>
       </c>
       <c r="E134" s="16" t="s">
-        <v>1679</v>
+        <v>1671</v>
       </c>
       <c r="F134" s="16" t="s">
         <v>910</v>
       </c>
       <c r="G134" s="16" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="H134" s="16" t="s">
         <v>911</v>
@@ -14032,7 +14059,7 @@
         <v>391</v>
       </c>
       <c r="B135" s="16" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C135" s="16" t="s">
         <v>913</v>
@@ -14041,13 +14068,13 @@
         <v>914</v>
       </c>
       <c r="E135" s="16" t="s">
-        <v>1680</v>
+        <v>1672</v>
       </c>
       <c r="F135" s="16" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
       <c r="G135" s="16" t="s">
-        <v>1256</v>
+        <v>1791</v>
       </c>
       <c r="H135" s="16" t="s">
         <v>915</v>
@@ -14059,7 +14086,7 @@
         <v>916</v>
       </c>
       <c r="K135" s="16" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
       <c r="L135" s="16"/>
       <c r="M135" s="16" t="s">
@@ -14086,22 +14113,22 @@
         <v>391</v>
       </c>
       <c r="B136" s="16" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C136" s="16" t="s">
-        <v>1669</v>
+        <v>1661</v>
       </c>
       <c r="D136" s="16" t="s">
         <v>917</v>
       </c>
       <c r="E136" s="16" t="s">
-        <v>1681</v>
+        <v>1673</v>
       </c>
       <c r="F136" s="16" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="G136" s="16" t="s">
-        <v>1256</v>
+        <v>1792</v>
       </c>
       <c r="H136" s="16" t="s">
         <v>918</v>
@@ -14113,7 +14140,7 @@
         <v>919</v>
       </c>
       <c r="K136" s="16" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="L136" s="16"/>
       <c r="M136" s="16" t="s">
@@ -14140,22 +14167,22 @@
         <v>391</v>
       </c>
       <c r="B137" s="16" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C137" s="16" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
       <c r="D137" s="16" t="s">
-        <v>1683</v>
+        <v>1675</v>
       </c>
       <c r="E137" s="16" t="s">
-        <v>1684</v>
+        <v>1676</v>
       </c>
       <c r="F137" s="16" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
       <c r="G137" s="16" t="s">
-        <v>1256</v>
+        <v>1793</v>
       </c>
       <c r="H137" s="16" t="s">
         <v>920</v>
@@ -14164,10 +14191,10 @@
         <v>380</v>
       </c>
       <c r="J137" s="16" t="s">
-        <v>1685</v>
+        <v>1677</v>
       </c>
       <c r="K137" s="16" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
       <c r="L137" s="16"/>
       <c r="M137" s="16" t="s">
@@ -14194,7 +14221,7 @@
         <v>391</v>
       </c>
       <c r="B138" s="16" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C138" s="16" t="s">
         <v>921</v>
@@ -14203,13 +14230,13 @@
         <v>922</v>
       </c>
       <c r="E138" s="16" t="s">
-        <v>1686</v>
+        <v>1678</v>
       </c>
       <c r="F138" s="16" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="G138" s="16" t="s">
-        <v>1256</v>
+        <v>1794</v>
       </c>
       <c r="H138" s="16" t="s">
         <v>923</v>
@@ -14221,7 +14248,7 @@
         <v>924</v>
       </c>
       <c r="K138" s="16" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
       <c r="L138" s="16"/>
       <c r="M138" s="16" t="s">
@@ -14248,7 +14275,7 @@
         <v>391</v>
       </c>
       <c r="B139" s="16" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C139" s="16" t="s">
         <v>925</v>
@@ -14257,25 +14284,25 @@
         <v>926</v>
       </c>
       <c r="E139" s="16" t="s">
-        <v>1687</v>
+        <v>1679</v>
       </c>
       <c r="F139" s="16" t="s">
-        <v>1261</v>
+        <v>1255</v>
       </c>
       <c r="G139" s="16" t="s">
-        <v>1705</v>
+        <v>1795</v>
       </c>
       <c r="H139" s="16" t="s">
-        <v>927</v>
+        <v>1801</v>
       </c>
       <c r="I139" s="16" t="s">
         <v>380</v>
       </c>
       <c r="J139" s="16" t="s">
-        <v>1688</v>
+        <v>1680</v>
       </c>
       <c r="K139" s="16" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="L139" s="16"/>
       <c r="M139" s="16" t="s">
@@ -14302,34 +14329,34 @@
         <v>391</v>
       </c>
       <c r="B140" s="16" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C140" s="16" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>1689</v>
+        <v>1681</v>
       </c>
       <c r="E140" s="16" t="s">
-        <v>1690</v>
+        <v>1682</v>
       </c>
       <c r="F140" s="16" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="G140" s="16" t="s">
-        <v>1705</v>
+        <v>1796</v>
       </c>
       <c r="H140" s="16" t="s">
-        <v>929</v>
+        <v>1802</v>
       </c>
       <c r="I140" s="16" t="s">
         <v>380</v>
       </c>
       <c r="J140" s="16" t="s">
-        <v>1691</v>
+        <v>1683</v>
       </c>
       <c r="K140" s="16" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="L140" s="16"/>
       <c r="M140" s="16" t="s">
@@ -14356,31 +14383,31 @@
         <v>391</v>
       </c>
       <c r="B141" s="16" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C141" s="16" t="s">
-        <v>1692</v>
+        <v>1684</v>
       </c>
       <c r="D141" s="16" t="s">
-        <v>1689</v>
+        <v>1681</v>
       </c>
       <c r="E141" s="16" t="s">
-        <v>1693</v>
+        <v>1685</v>
       </c>
       <c r="F141" s="16" t="s">
-        <v>1694</v>
+        <v>1686</v>
       </c>
       <c r="G141" s="16" t="s">
-        <v>1705</v>
+        <v>1797</v>
       </c>
       <c r="H141" s="16" t="s">
-        <v>1695</v>
+        <v>1803</v>
       </c>
       <c r="I141" s="16" t="s">
         <v>380</v>
       </c>
       <c r="J141" s="16" t="s">
-        <v>1696</v>
+        <v>1687</v>
       </c>
       <c r="K141" s="16"/>
       <c r="L141" s="16"/>
@@ -14402,34 +14429,34 @@
         <v>391</v>
       </c>
       <c r="B142" s="16" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C142" s="16" t="s">
-        <v>1697</v>
+        <v>1688</v>
       </c>
       <c r="D142" s="16" t="s">
-        <v>1698</v>
+        <v>1689</v>
       </c>
       <c r="E142" s="16" t="s">
-        <v>1699</v>
+        <v>1690</v>
       </c>
       <c r="F142" s="16" t="s">
-        <v>1706</v>
+        <v>1695</v>
       </c>
       <c r="G142" s="16" t="s">
-        <v>1707</v>
+        <v>1799</v>
       </c>
       <c r="H142" s="16" t="s">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="I142" s="16" t="s">
         <v>380</v>
       </c>
       <c r="J142" s="16" t="s">
-        <v>1701</v>
+        <v>1691</v>
       </c>
       <c r="K142" s="16" t="s">
-        <v>1708</v>
+        <v>1696</v>
       </c>
       <c r="L142" s="16"/>
       <c r="M142" s="16" t="s">
@@ -14456,34 +14483,34 @@
         <v>391</v>
       </c>
       <c r="B143" s="16" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C143" s="16" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="D143" s="16" t="s">
-        <v>1702</v>
+        <v>1692</v>
       </c>
       <c r="E143" s="16" t="s">
-        <v>1703</v>
+        <v>1693</v>
       </c>
       <c r="F143" s="16" t="s">
-        <v>1709</v>
+        <v>1697</v>
       </c>
       <c r="G143" s="16" t="s">
-        <v>1710</v>
+        <v>1798</v>
       </c>
       <c r="H143" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="I143" s="16" t="s">
         <v>380</v>
       </c>
       <c r="J143" s="16" t="s">
-        <v>1704</v>
+        <v>1694</v>
       </c>
       <c r="K143" s="16" t="s">
-        <v>1711</v>
+        <v>1698</v>
       </c>
       <c r="L143" s="16"/>
       <c r="M143" s="16" t="s">
@@ -14510,19 +14537,19 @@
         <v>391</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="C144" s="17" t="s">
-        <v>1658</v>
+        <v>1650</v>
       </c>
       <c r="D144" s="17" t="s">
         <v>606</v>
       </c>
       <c r="E144" s="17" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="F144" s="17" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="G144" s="17" t="s">
         <v>607</v>
@@ -14556,22 +14583,22 @@
         <v>391</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="C145" s="17" t="s">
-        <v>1659</v>
+        <v>1651</v>
       </c>
       <c r="D145" s="17" t="s">
         <v>610</v>
       </c>
       <c r="E145" s="17" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="F145" s="17" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
       <c r="G145" s="17" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>611</v>
@@ -14602,19 +14629,19 @@
         <v>391</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="C146" s="17" t="s">
-        <v>1660</v>
+        <v>1652</v>
       </c>
       <c r="D146" s="17" t="s">
         <v>613</v>
       </c>
       <c r="E146" s="17" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="F146" s="17" t="s">
-        <v>1265</v>
+        <v>1259</v>
       </c>
       <c r="G146" s="17" t="s">
         <v>614</v>
@@ -14650,22 +14677,22 @@
         <v>391</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="C147" s="17" t="s">
-        <v>1661</v>
+        <v>1653</v>
       </c>
       <c r="D147" s="17" t="s">
         <v>821</v>
       </c>
       <c r="E147" s="17" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="F147" s="17" t="s">
-        <v>1265</v>
+        <v>1259</v>
       </c>
       <c r="G147" s="17" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>618</v>
@@ -14698,22 +14725,22 @@
         <v>391</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="C148" s="17" t="s">
-        <v>1662</v>
+        <v>1654</v>
       </c>
       <c r="D148" s="17" t="s">
         <v>822</v>
       </c>
       <c r="E148" s="17" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="F148" s="17" t="s">
-        <v>1265</v>
+        <v>1259</v>
       </c>
       <c r="G148" s="17" t="s">
-        <v>1267</v>
+        <v>1261</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>618</v>
@@ -14746,7 +14773,7 @@
         <v>391</v>
       </c>
       <c r="B149" s="17" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="C149" s="17" t="s">
         <v>621</v>
@@ -14755,13 +14782,13 @@
         <v>820</v>
       </c>
       <c r="E149" s="17" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="F149" s="17" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="G149" s="17" t="s">
-        <v>1269</v>
+        <v>1263</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>622</v>
@@ -14792,7 +14819,7 @@
         <v>391</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="C150" s="17" t="s">
         <v>624</v>
@@ -14801,13 +14828,13 @@
         <v>820</v>
       </c>
       <c r="E150" s="17" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="F150" s="17" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="G150" s="17" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>625</v>
@@ -14838,22 +14865,22 @@
         <v>391</v>
       </c>
       <c r="B151" s="17" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="C151" s="17" t="s">
-        <v>1664</v>
+        <v>1656</v>
       </c>
       <c r="D151" s="17" t="s">
         <v>627</v>
       </c>
       <c r="E151" s="17" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="F151" s="17" t="s">
-        <v>1270</v>
+        <v>1264</v>
       </c>
       <c r="G151" s="17" t="s">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>628</v>
@@ -14884,22 +14911,22 @@
         <v>391</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="C152" s="17" t="s">
-        <v>1663</v>
+        <v>1655</v>
       </c>
       <c r="D152" s="17" t="s">
         <v>629</v>
       </c>
       <c r="E152" s="17" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="F152" s="17" t="s">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="G152" s="17" t="s">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>630</v>
@@ -14930,7 +14957,7 @@
         <v>391</v>
       </c>
       <c r="B153" s="17" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="C153" s="17" t="s">
         <v>795</v>
@@ -14939,16 +14966,16 @@
         <v>823</v>
       </c>
       <c r="E153" s="17" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="F153" s="17" t="s">
         <v>796</v>
       </c>
       <c r="G153" s="17" t="s">
-        <v>1273</v>
+        <v>1267</v>
       </c>
       <c r="H153" s="17" t="s">
-        <v>1228</v>
+        <v>1222</v>
       </c>
       <c r="I153" s="17" t="s">
         <v>385</v>
@@ -14976,34 +15003,34 @@
         <v>391</v>
       </c>
       <c r="B154" s="28" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="C154" s="28" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="D154" s="28" t="s">
-        <v>1595</v>
+        <v>1589</v>
       </c>
       <c r="E154" s="28" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="F154" s="28" t="s">
-        <v>1274</v>
+        <v>1268</v>
       </c>
       <c r="G154" s="28" t="s">
-        <v>1783</v>
+        <v>1770</v>
       </c>
       <c r="H154" s="28" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="I154" s="28" t="s">
         <v>380</v>
       </c>
       <c r="J154" s="28" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="K154" s="28" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="L154" s="28"/>
       <c r="M154" s="28" t="s">
@@ -15024,22 +15051,22 @@
         <v>391</v>
       </c>
       <c r="B155" s="28" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="C155" s="28" t="s">
+        <v>933</v>
+      </c>
+      <c r="D155" s="28" t="s">
+        <v>934</v>
+      </c>
+      <c r="E155" s="28" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F155" s="28" t="s">
+        <v>1269</v>
+      </c>
+      <c r="G155" s="28" t="s">
         <v>935</v>
-      </c>
-      <c r="D155" s="28" t="s">
-        <v>936</v>
-      </c>
-      <c r="E155" s="28" t="s">
-        <v>1050</v>
-      </c>
-      <c r="F155" s="28" t="s">
-        <v>1275</v>
-      </c>
-      <c r="G155" s="28" t="s">
-        <v>937</v>
       </c>
       <c r="H155" s="28" t="s">
         <v>634</v>
@@ -15048,10 +15075,10 @@
         <v>380</v>
       </c>
       <c r="J155" s="28" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="K155" s="28" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="L155" s="28"/>
       <c r="M155" s="28" t="s">
@@ -15067,22 +15094,22 @@
         <v>602</v>
       </c>
       <c r="S155" s="37" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="T155" s="37" t="s">
-        <v>1191</v>
+        <v>1185</v>
       </c>
       <c r="U155" s="38">
         <v>1</v>
       </c>
       <c r="V155" s="37" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="W155" s="37" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
       <c r="X155" s="37" t="s">
-        <v>1190</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="156" spans="1:24" s="65" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -15090,22 +15117,22 @@
         <v>391</v>
       </c>
       <c r="B156" s="28" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="C156" s="28" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D156" s="28" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="E156" s="28" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="F156" s="28" t="s">
-        <v>1344</v>
+        <v>1338</v>
       </c>
       <c r="G156" s="28" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="H156" s="28" t="s">
         <v>634</v>
@@ -15114,7 +15141,7 @@
         <v>380</v>
       </c>
       <c r="J156" s="28" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="K156" s="28"/>
       <c r="L156" s="28"/>
@@ -15131,22 +15158,22 @@
         <v>602</v>
       </c>
       <c r="S156" s="37" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="T156" s="37" t="s">
-        <v>1191</v>
+        <v>1185</v>
       </c>
       <c r="U156" s="38">
         <v>2</v>
       </c>
       <c r="V156" s="37" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="W156" s="37" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
       <c r="X156" s="37" t="s">
-        <v>1190</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="157" spans="1:24" s="65" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -15154,31 +15181,31 @@
         <v>391</v>
       </c>
       <c r="B157" s="28" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="C157" s="28" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="D157" s="28" t="s">
-        <v>1656</v>
+        <v>1648</v>
       </c>
       <c r="E157" s="28" t="s">
-        <v>1596</v>
+        <v>1590</v>
       </c>
       <c r="F157" s="28" t="s">
-        <v>1276</v>
+        <v>1270</v>
       </c>
       <c r="G157" s="28" t="s">
-        <v>1784</v>
+        <v>1771</v>
       </c>
       <c r="H157" s="28" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="I157" s="28" t="s">
         <v>380</v>
       </c>
       <c r="J157" s="28" t="s">
-        <v>1597</v>
+        <v>1591</v>
       </c>
       <c r="K157" s="28"/>
       <c r="L157" s="28"/>
@@ -15195,22 +15222,22 @@
         <v>602</v>
       </c>
       <c r="S157" s="37" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="T157" s="37" t="s">
-        <v>1191</v>
+        <v>1185</v>
       </c>
       <c r="U157" s="38">
         <v>3</v>
       </c>
       <c r="V157" s="37" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="W157" s="37" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
       <c r="X157" s="37" t="s">
-        <v>1190</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="158" spans="1:24" s="65" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -15218,22 +15245,22 @@
         <v>391</v>
       </c>
       <c r="B158" s="28" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="C158" s="28" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="D158" s="28" t="s">
-        <v>1657</v>
+        <v>1649</v>
       </c>
       <c r="E158" s="28" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="F158" s="28" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="G158" s="28" t="s">
-        <v>944</v>
+        <v>1806</v>
       </c>
       <c r="H158" s="28" t="s">
         <v>635</v>
@@ -15242,10 +15269,10 @@
         <v>380</v>
       </c>
       <c r="J158" s="28" t="s">
-        <v>1598</v>
+        <v>1592</v>
       </c>
       <c r="K158" s="28" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="L158" s="28"/>
       <c r="M158" s="28" t="s">
@@ -15272,34 +15299,34 @@
         <v>391</v>
       </c>
       <c r="B159" s="28" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="C159" s="28" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="D159" s="28" t="s">
-        <v>1599</v>
+        <v>1593</v>
       </c>
       <c r="E159" s="28" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="F159" s="28" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="G159" s="28" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="H159" s="28" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="I159" s="28" t="s">
         <v>380</v>
       </c>
       <c r="J159" s="28" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="K159" s="28" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="L159" s="28"/>
       <c r="M159" s="28" t="s">
@@ -15326,34 +15353,34 @@
         <v>391</v>
       </c>
       <c r="B160" s="28" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="C160" s="28" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="D160" s="28" t="s">
-        <v>1600</v>
+        <v>1594</v>
       </c>
       <c r="E160" s="28" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="F160" s="28" t="s">
-        <v>1279</v>
+        <v>1273</v>
       </c>
       <c r="G160" s="28" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="H160" s="28" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="I160" s="28" t="s">
         <v>380</v>
       </c>
       <c r="J160" s="28" t="s">
-        <v>951</v>
+        <v>1790</v>
       </c>
       <c r="K160" s="28" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="L160" s="28"/>
       <c r="M160" s="28" t="s">
@@ -15380,31 +15407,31 @@
         <v>391</v>
       </c>
       <c r="B161" s="28" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="C161" s="28" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="D161" s="28" t="s">
-        <v>1601</v>
+        <v>1788</v>
       </c>
       <c r="E161" s="28" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="F161" s="28" t="s">
-        <v>1280</v>
+        <v>1274</v>
       </c>
       <c r="G161" s="28" t="s">
+        <v>1804</v>
+      </c>
+      <c r="H161" s="28" t="s">
         <v>949</v>
-      </c>
-      <c r="H161" s="28" t="s">
-        <v>953</v>
       </c>
       <c r="I161" s="28" t="s">
         <v>380</v>
       </c>
       <c r="J161" s="28" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="K161" s="28"/>
       <c r="L161" s="28"/>
@@ -15432,31 +15459,31 @@
         <v>391</v>
       </c>
       <c r="B162" s="28" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="C162" s="28" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="D162" s="28" t="s">
-        <v>1602</v>
+        <v>1789</v>
       </c>
       <c r="E162" s="28" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="F162" s="28" t="s">
-        <v>1281</v>
+        <v>1275</v>
       </c>
       <c r="G162" s="28" t="s">
-        <v>949</v>
+        <v>1805</v>
       </c>
       <c r="H162" s="28" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="I162" s="28" t="s">
         <v>380</v>
       </c>
       <c r="J162" s="28" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="K162" s="28"/>
       <c r="L162" s="28"/>
@@ -15484,31 +15511,31 @@
         <v>391</v>
       </c>
       <c r="B163" s="28" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="C163" s="28" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="D163" s="28" t="s">
-        <v>1603</v>
+        <v>1595</v>
       </c>
       <c r="E163" s="28" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="F163" s="28" t="s">
-        <v>1282</v>
+        <v>1276</v>
       </c>
       <c r="G163" s="28" t="s">
-        <v>949</v>
+        <v>1787</v>
       </c>
       <c r="H163" s="28" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="I163" s="28" t="s">
         <v>380</v>
       </c>
       <c r="J163" s="28" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="K163" s="28"/>
       <c r="L163" s="28"/>
@@ -15536,7 +15563,7 @@
         <v>391</v>
       </c>
       <c r="B164" s="34" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="C164" s="34" t="s">
         <v>559</v>
@@ -15545,13 +15572,13 @@
         <v>591</v>
       </c>
       <c r="E164" s="34" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="F164" s="34" t="s">
-        <v>1283</v>
+        <v>1277</v>
       </c>
       <c r="G164" s="34" t="s">
-        <v>1284</v>
+        <v>1278</v>
       </c>
       <c r="H164" s="34" t="s">
         <v>500</v>
@@ -15582,7 +15609,7 @@
         <v>391</v>
       </c>
       <c r="B165" s="34" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="C165" s="34" t="s">
         <v>561</v>
@@ -15591,13 +15618,13 @@
         <v>784</v>
       </c>
       <c r="E165" s="34" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="F165" s="34" t="s">
-        <v>1285</v>
+        <v>1279</v>
       </c>
       <c r="G165" s="34" t="s">
-        <v>1367</v>
+        <v>1361</v>
       </c>
       <c r="H165" s="34" t="s">
         <v>562</v>
@@ -15630,7 +15657,7 @@
         <v>391</v>
       </c>
       <c r="B166" s="34" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="C166" s="34" t="s">
         <v>695</v>
@@ -15639,13 +15666,13 @@
         <v>784</v>
       </c>
       <c r="E166" s="34" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="F166" s="34" t="s">
-        <v>1286</v>
+        <v>1280</v>
       </c>
       <c r="G166" s="34" t="s">
-        <v>1368</v>
+        <v>1362</v>
       </c>
       <c r="H166" s="34" t="s">
         <v>562</v>
@@ -15678,7 +15705,7 @@
         <v>391</v>
       </c>
       <c r="B167" s="34" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="C167" s="34" t="s">
         <v>563</v>
@@ -15687,13 +15714,13 @@
         <v>787</v>
       </c>
       <c r="E167" s="34" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="F167" s="34" t="s">
-        <v>1287</v>
+        <v>1281</v>
       </c>
       <c r="G167" s="34" t="s">
-        <v>1369</v>
+        <v>1363</v>
       </c>
       <c r="H167" s="34" t="s">
         <v>564</v>
@@ -15726,7 +15753,7 @@
         <v>391</v>
       </c>
       <c r="B168" s="34" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="C168" s="34" t="s">
         <v>696</v>
@@ -15735,13 +15762,13 @@
         <v>787</v>
       </c>
       <c r="E168" s="34" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="F168" s="34" t="s">
-        <v>1288</v>
+        <v>1282</v>
       </c>
       <c r="G168" s="34" t="s">
-        <v>1370</v>
+        <v>1364</v>
       </c>
       <c r="H168" s="34" t="s">
         <v>564</v>
@@ -15774,31 +15801,31 @@
         <v>391</v>
       </c>
       <c r="B169" s="33" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="C169" s="33" t="s">
-        <v>1617</v>
+        <v>1609</v>
       </c>
       <c r="D169" s="33" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="E169" s="33" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="F169" s="33" t="s">
-        <v>1289</v>
+        <v>1283</v>
       </c>
       <c r="G169" s="33" t="s">
-        <v>1290</v>
+        <v>1284</v>
       </c>
       <c r="H169" s="33" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="I169" s="33" t="s">
         <v>380</v>
       </c>
       <c r="J169" s="33" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="K169" s="33"/>
       <c r="L169" s="33"/>
@@ -15826,31 +15853,31 @@
         <v>391</v>
       </c>
       <c r="B170" s="33" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="C170" s="33" t="s">
-        <v>1618</v>
+        <v>1610</v>
       </c>
       <c r="D170" s="33" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="E170" s="33" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="F170" s="33" t="s">
-        <v>1291</v>
+        <v>1285</v>
       </c>
       <c r="G170" s="33" t="s">
-        <v>1292</v>
+        <v>1286</v>
       </c>
       <c r="H170" s="33" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="I170" s="33" t="s">
         <v>380</v>
       </c>
       <c r="J170" s="33" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="K170" s="33"/>
       <c r="L170" s="33"/>
@@ -15878,31 +15905,31 @@
         <v>391</v>
       </c>
       <c r="B171" s="33" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="C171" s="33" t="s">
-        <v>1619</v>
+        <v>1611</v>
       </c>
       <c r="D171" s="33" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="E171" s="33" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="F171" s="33" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="G171" s="33" t="s">
-        <v>1294</v>
+        <v>1288</v>
       </c>
       <c r="H171" s="33" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="I171" s="33" t="s">
         <v>380</v>
       </c>
       <c r="J171" s="33" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="K171" s="33"/>
       <c r="L171" s="33"/>
@@ -15930,31 +15957,31 @@
         <v>391</v>
       </c>
       <c r="B172" s="33" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="C172" s="33" t="s">
-        <v>1620</v>
+        <v>1612</v>
       </c>
       <c r="D172" s="33" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="E172" s="33" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="F172" s="33" t="s">
-        <v>1295</v>
+        <v>1289</v>
       </c>
       <c r="G172" s="33" t="s">
-        <v>1296</v>
+        <v>1290</v>
       </c>
       <c r="H172" s="33" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="I172" s="33" t="s">
         <v>380</v>
       </c>
       <c r="J172" s="33" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="K172" s="33"/>
       <c r="L172" s="33"/>
@@ -15982,31 +16009,31 @@
         <v>391</v>
       </c>
       <c r="B173" s="33" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="C173" s="33" t="s">
-        <v>1621</v>
+        <v>1613</v>
       </c>
       <c r="D173" s="33" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="E173" s="33" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="F173" s="33" t="s">
-        <v>1297</v>
+        <v>1291</v>
       </c>
       <c r="G173" s="33" t="s">
-        <v>1298</v>
+        <v>1292</v>
       </c>
       <c r="H173" s="33" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="I173" s="33" t="s">
         <v>380</v>
       </c>
       <c r="J173" s="33" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="K173" s="33"/>
       <c r="L173" s="33"/>
@@ -16034,31 +16061,31 @@
         <v>391</v>
       </c>
       <c r="B174" s="33" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="C174" s="33" t="s">
-        <v>1622</v>
+        <v>1614</v>
       </c>
       <c r="D174" s="33" t="s">
-        <v>1615</v>
+        <v>1607</v>
       </c>
       <c r="E174" s="33" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="F174" s="33" t="s">
-        <v>1299</v>
+        <v>1293</v>
       </c>
       <c r="G174" s="33" t="s">
-        <v>1300</v>
+        <v>1294</v>
       </c>
       <c r="H174" s="33" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="I174" s="33" t="s">
         <v>380</v>
       </c>
       <c r="J174" s="33" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="K174" s="33"/>
       <c r="L174" s="33"/>
@@ -16086,34 +16113,34 @@
         <v>391</v>
       </c>
       <c r="B175" s="32" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C175" s="32" t="s">
-        <v>976</v>
+        <v>1785</v>
       </c>
       <c r="D175" s="32" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="E175" s="32" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="F175" s="32" t="s">
-        <v>1301</v>
+        <v>1295</v>
       </c>
       <c r="G175" s="32" t="s">
-        <v>1785</v>
+        <v>1772</v>
       </c>
       <c r="H175" s="32" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="I175" s="32" t="s">
         <v>380</v>
       </c>
       <c r="J175" s="32" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="K175" s="32" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="L175" s="32"/>
       <c r="M175" s="32" t="s">
@@ -16140,34 +16167,34 @@
         <v>391</v>
       </c>
       <c r="B176" s="32" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C176" s="32" t="s">
-        <v>980</v>
+        <v>1786</v>
       </c>
       <c r="D176" s="32" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="E176" s="32" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="F176" s="32" t="s">
-        <v>1302</v>
+        <v>1296</v>
       </c>
       <c r="G176" s="32" t="s">
-        <v>1786</v>
+        <v>1773</v>
       </c>
       <c r="H176" s="32" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="I176" s="32" t="s">
         <v>380</v>
       </c>
       <c r="J176" s="32" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="K176" s="32" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="L176" s="32"/>
       <c r="M176" s="32" t="s">
@@ -16194,34 +16221,34 @@
         <v>391</v>
       </c>
       <c r="B177" s="32" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C177" s="32" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="D177" s="32" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="E177" s="32" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="F177" s="32" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="G177" s="32" t="s">
-        <v>1787</v>
+        <v>1774</v>
       </c>
       <c r="H177" s="32" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="I177" s="32" t="s">
         <v>380</v>
       </c>
       <c r="J177" s="32" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="K177" s="32" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="L177" s="32"/>
       <c r="M177" s="32" t="s">
@@ -16248,31 +16275,31 @@
         <v>391</v>
       </c>
       <c r="B178" s="32" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C178" s="32" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="D178" s="32" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="E178" s="32" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="F178" s="32" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="G178" s="32" t="s">
-        <v>1788</v>
+        <v>1775</v>
       </c>
       <c r="H178" s="32" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="I178" s="32" t="s">
         <v>380</v>
       </c>
       <c r="J178" s="32" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="K178" s="32"/>
       <c r="L178" s="32"/>
@@ -16300,31 +16327,31 @@
         <v>391</v>
       </c>
       <c r="B179" s="32" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C179" s="32" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="D179" s="32" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="E179" s="32" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="F179" s="32" t="s">
-        <v>1305</v>
+        <v>1299</v>
       </c>
       <c r="G179" s="32" t="s">
-        <v>1789</v>
+        <v>1776</v>
       </c>
       <c r="H179" s="32" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="I179" s="32" t="s">
         <v>380</v>
       </c>
       <c r="J179" s="32" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="K179" s="32"/>
       <c r="L179" s="32"/>
@@ -16352,34 +16379,34 @@
         <v>391</v>
       </c>
       <c r="B180" s="32" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C180" s="32" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="D180" s="32" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="E180" s="32" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="F180" s="32" t="s">
-        <v>1306</v>
+        <v>1300</v>
       </c>
       <c r="G180" s="32" t="s">
-        <v>1790</v>
+        <v>1777</v>
       </c>
       <c r="H180" s="32" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="I180" s="32" t="s">
         <v>380</v>
       </c>
       <c r="J180" s="32" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="K180" s="32" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="L180" s="32"/>
       <c r="M180" s="32" t="s">
@@ -16406,34 +16433,34 @@
         <v>391</v>
       </c>
       <c r="B181" s="32" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C181" s="32" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="D181" s="32" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="E181" s="32" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="F181" s="32" t="s">
-        <v>1307</v>
+        <v>1301</v>
       </c>
       <c r="G181" s="32" t="s">
-        <v>1791</v>
+        <v>1778</v>
       </c>
       <c r="H181" s="32" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="I181" s="32" t="s">
         <v>380</v>
       </c>
       <c r="J181" s="32" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="K181" s="32" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="L181" s="32"/>
       <c r="M181" s="32" t="s">
@@ -16460,34 +16487,34 @@
         <v>391</v>
       </c>
       <c r="B182" s="32" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C182" s="32" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="D182" s="32" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="E182" s="32" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="F182" s="32" t="s">
-        <v>1308</v>
+        <v>1302</v>
       </c>
       <c r="G182" s="32" t="s">
-        <v>1792</v>
+        <v>1779</v>
       </c>
       <c r="H182" s="32" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="I182" s="32" t="s">
         <v>380</v>
       </c>
       <c r="J182" s="32" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="K182" s="32" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="L182" s="32"/>
       <c r="M182" s="32" t="s">
@@ -16514,34 +16541,34 @@
         <v>391</v>
       </c>
       <c r="B183" s="32" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C183" s="32" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="D183" s="32" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="E183" s="32" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="F183" s="32" t="s">
-        <v>1309</v>
+        <v>1303</v>
       </c>
       <c r="G183" s="32" t="s">
-        <v>1793</v>
+        <v>1780</v>
       </c>
       <c r="H183" s="32" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="I183" s="32" t="s">
         <v>380</v>
       </c>
       <c r="J183" s="32" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="K183" s="32" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="L183" s="32"/>
       <c r="M183" s="32" t="s">
@@ -16568,34 +16595,34 @@
         <v>391</v>
       </c>
       <c r="B184" s="32" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C184" s="32" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="D184" s="32" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="E184" s="32" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="F184" s="32" t="s">
-        <v>1310</v>
+        <v>1304</v>
       </c>
       <c r="G184" s="32" t="s">
-        <v>1794</v>
+        <v>1781</v>
       </c>
       <c r="H184" s="32" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="I184" s="32" t="s">
         <v>380</v>
       </c>
       <c r="J184" s="32" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="K184" s="32" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="L184" s="32"/>
       <c r="M184" s="32" t="s">
@@ -16622,34 +16649,34 @@
         <v>391</v>
       </c>
       <c r="B185" s="32" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C185" s="32" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="D185" s="32" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="E185" s="32" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="F185" s="32" t="s">
-        <v>1311</v>
+        <v>1305</v>
       </c>
       <c r="G185" s="32" t="s">
-        <v>1795</v>
+        <v>1782</v>
       </c>
       <c r="H185" s="32" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="I185" s="32" t="s">
         <v>380</v>
       </c>
       <c r="J185" s="32" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="K185" s="32" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="L185" s="32"/>
       <c r="M185" s="32" t="s">
@@ -16676,34 +16703,34 @@
         <v>391</v>
       </c>
       <c r="B186" s="32" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C186" s="32" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="D186" s="32" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="E186" s="32" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="F186" s="32" t="s">
-        <v>1312</v>
+        <v>1306</v>
       </c>
       <c r="G186" s="32" t="s">
-        <v>1796</v>
+        <v>1783</v>
       </c>
       <c r="H186" s="32" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="I186" s="32" t="s">
         <v>380</v>
       </c>
       <c r="J186" s="32" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="K186" s="32" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="L186" s="32"/>
       <c r="M186" s="32" t="s">
@@ -16730,34 +16757,34 @@
         <v>391</v>
       </c>
       <c r="B187" s="32" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C187" s="32" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="D187" s="32" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="E187" s="32" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="F187" s="32" t="s">
-        <v>1313</v>
+        <v>1307</v>
       </c>
       <c r="G187" s="32" t="s">
-        <v>1797</v>
+        <v>1784</v>
       </c>
       <c r="H187" s="32" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="I187" s="32" t="s">
         <v>380</v>
       </c>
       <c r="J187" s="32" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="K187" s="32" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="L187" s="32"/>
       <c r="M187" s="32" t="s">
@@ -16784,13 +16811,13 @@
         <v>391</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C188" s="11" t="s">
         <v>263</v>
       </c>
       <c r="D188" s="11" t="s">
-        <v>1351</v>
+        <v>1345</v>
       </c>
       <c r="E188" s="11" t="s">
         <v>366</v>
@@ -16823,10 +16850,10 @@
         <v>602</v>
       </c>
       <c r="S188" s="25" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="T188" s="22" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="U188" s="23">
         <v>1</v>
@@ -16835,10 +16862,10 @@
         <v>905</v>
       </c>
       <c r="W188" s="22" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="X188" s="25" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="189" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16846,13 +16873,13 @@
         <v>391</v>
       </c>
       <c r="B189" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C189" s="11" t="s">
         <v>264</v>
       </c>
       <c r="D189" s="11" t="s">
-        <v>1351</v>
+        <v>1345</v>
       </c>
       <c r="E189" s="11" t="s">
         <v>366</v>
@@ -16885,10 +16912,10 @@
         <v>602</v>
       </c>
       <c r="S189" s="25" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="T189" s="22" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="U189" s="23">
         <v>2</v>
@@ -16897,10 +16924,10 @@
         <v>905</v>
       </c>
       <c r="W189" s="22" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="X189" s="25" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="190" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16908,7 +16935,7 @@
         <v>391</v>
       </c>
       <c r="B190" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C190" s="11" t="s">
         <v>265</v>
@@ -16923,7 +16950,7 @@
         <v>496</v>
       </c>
       <c r="G190" s="11" t="s">
-        <v>1314</v>
+        <v>1308</v>
       </c>
       <c r="H190" s="11" t="s">
         <v>491</v>
@@ -16955,7 +16982,7 @@
         <v>391</v>
       </c>
       <c r="B191" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C191" s="11" t="s">
         <v>266</v>
@@ -16967,10 +16994,10 @@
         <v>346</v>
       </c>
       <c r="F191" s="11" t="s">
-        <v>1315</v>
+        <v>1309</v>
       </c>
       <c r="G191" s="11" t="s">
-        <v>1314</v>
+        <v>1308</v>
       </c>
       <c r="H191" s="11" t="s">
         <v>491</v>
@@ -16996,7 +17023,7 @@
         <v>391</v>
       </c>
       <c r="B192" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C192" s="11" t="s">
         <v>267</v>
@@ -17008,10 +17035,10 @@
         <v>346</v>
       </c>
       <c r="F192" s="11" t="s">
-        <v>1316</v>
+        <v>1310</v>
       </c>
       <c r="G192" s="11" t="s">
-        <v>1314</v>
+        <v>1308</v>
       </c>
       <c r="H192" s="11" t="s">
         <v>491</v>
@@ -17038,10 +17065,10 @@
         <v>602</v>
       </c>
       <c r="S192" s="25" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="T192" s="22" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="U192" s="23">
         <v>3</v>
@@ -17050,10 +17077,10 @@
         <v>905</v>
       </c>
       <c r="W192" s="22" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="X192" s="25" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="193" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17061,7 +17088,7 @@
         <v>391</v>
       </c>
       <c r="B193" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C193" s="11" t="s">
         <v>268</v>
@@ -17073,10 +17100,10 @@
         <v>346</v>
       </c>
       <c r="F193" s="11" t="s">
-        <v>1317</v>
+        <v>1311</v>
       </c>
       <c r="G193" s="11" t="s">
-        <v>1314</v>
+        <v>1308</v>
       </c>
       <c r="H193" s="11" t="s">
         <v>491</v>
@@ -17102,22 +17129,22 @@
         <v>391</v>
       </c>
       <c r="B194" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C194" s="11" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D194" s="11" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="E194" s="11" t="s">
         <v>516</v>
       </c>
       <c r="F194" s="11" t="s">
-        <v>1318</v>
+        <v>1312</v>
       </c>
       <c r="G194" s="11" t="s">
-        <v>1316</v>
+        <v>1310</v>
       </c>
       <c r="H194" s="11" t="s">
         <v>517</v>
@@ -17147,10 +17174,10 @@
         <v>602</v>
       </c>
       <c r="S194" s="25" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="T194" s="22" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="U194" s="23">
         <v>1</v>
@@ -17159,10 +17186,10 @@
         <v>905</v>
       </c>
       <c r="W194" s="22" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="X194" s="22" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="195" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17170,22 +17197,22 @@
         <v>391</v>
       </c>
       <c r="B195" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
       <c r="D195" s="11" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="E195" s="11" t="s">
         <v>347</v>
       </c>
       <c r="F195" s="11" t="s">
-        <v>1319</v>
+        <v>1313</v>
       </c>
       <c r="G195" s="11" t="s">
-        <v>1316</v>
+        <v>1310</v>
       </c>
       <c r="H195" s="11" t="s">
         <v>491</v>
@@ -17194,7 +17221,7 @@
         <v>385</v>
       </c>
       <c r="J195" s="11" t="s">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="K195" s="11" t="s">
         <v>525</v>
@@ -17215,10 +17242,10 @@
         <v>602</v>
       </c>
       <c r="S195" s="25" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="T195" s="22" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="U195" s="23">
         <v>2</v>
@@ -17227,10 +17254,10 @@
         <v>905</v>
       </c>
       <c r="W195" s="22" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="X195" s="22" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="196" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17238,22 +17265,22 @@
         <v>391</v>
       </c>
       <c r="B196" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C196" s="11" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="D196" s="11" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="E196" s="11" t="s">
         <v>347</v>
       </c>
       <c r="F196" s="11" t="s">
-        <v>1320</v>
+        <v>1314</v>
       </c>
       <c r="G196" s="11" t="s">
-        <v>1316</v>
+        <v>1310</v>
       </c>
       <c r="H196" s="11" t="s">
         <v>491</v>
@@ -17262,7 +17289,7 @@
         <v>385</v>
       </c>
       <c r="J196" s="11" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
       <c r="K196" s="11" t="s">
         <v>520</v>
@@ -17283,10 +17310,10 @@
         <v>602</v>
       </c>
       <c r="S196" s="25" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="T196" s="22" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="U196" s="23">
         <v>3</v>
@@ -17295,10 +17322,10 @@
         <v>905</v>
       </c>
       <c r="W196" s="22" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="X196" s="22" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="197" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17306,7 +17333,7 @@
         <v>391</v>
       </c>
       <c r="B197" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C197" s="11" t="s">
         <v>283</v>
@@ -17321,7 +17348,7 @@
         <v>279</v>
       </c>
       <c r="G197" s="11" t="s">
-        <v>1321</v>
+        <v>1315</v>
       </c>
       <c r="H197" s="11" t="s">
         <v>422</v>
@@ -17350,13 +17377,13 @@
         <v>391</v>
       </c>
       <c r="B198" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C198" s="11" t="s">
         <v>269</v>
       </c>
       <c r="D198" s="11" t="s">
-        <v>1352</v>
+        <v>1346</v>
       </c>
       <c r="E198" s="11" t="s">
         <v>368</v>
@@ -17394,13 +17421,13 @@
         <v>391</v>
       </c>
       <c r="B199" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C199" s="11" t="s">
         <v>284</v>
       </c>
       <c r="D199" s="11" t="s">
-        <v>1352</v>
+        <v>1346</v>
       </c>
       <c r="E199" s="11" t="s">
         <v>368</v>
@@ -17438,13 +17465,13 @@
         <v>391</v>
       </c>
       <c r="B200" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C200" s="11" t="s">
         <v>285</v>
       </c>
       <c r="D200" s="11" t="s">
-        <v>1352</v>
+        <v>1346</v>
       </c>
       <c r="E200" s="11" t="s">
         <v>368</v>
@@ -17453,10 +17480,10 @@
         <v>282</v>
       </c>
       <c r="G200" s="11" t="s">
-        <v>1322</v>
+        <v>1316</v>
       </c>
       <c r="H200" s="11" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="I200" s="11" t="s">
         <v>385</v>
@@ -17477,22 +17504,22 @@
         <v>602</v>
       </c>
       <c r="S200" s="22" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="T200" s="26" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="U200" s="35">
         <v>1</v>
       </c>
       <c r="V200" s="26" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="W200" s="26" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="X200" s="26" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="201" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17500,7 +17527,7 @@
         <v>391</v>
       </c>
       <c r="B201" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C201" s="11" t="s">
         <v>287</v>
@@ -17512,13 +17539,13 @@
         <v>368</v>
       </c>
       <c r="F201" s="11" t="s">
-        <v>1323</v>
+        <v>1317</v>
       </c>
       <c r="G201" s="11" t="s">
-        <v>1324</v>
+        <v>1318</v>
       </c>
       <c r="H201" s="11" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="I201" s="11" t="s">
         <v>385</v>
@@ -17545,22 +17572,22 @@
         <v>602</v>
       </c>
       <c r="S201" s="22" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="T201" s="26" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="U201" s="35">
         <v>2</v>
       </c>
       <c r="V201" s="26" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="W201" s="26" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="X201" s="26" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="202" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17568,7 +17595,7 @@
         <v>391</v>
       </c>
       <c r="B202" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C202" s="11" t="s">
         <v>288</v>
@@ -17583,10 +17610,10 @@
         <v>286</v>
       </c>
       <c r="G202" s="11" t="s">
-        <v>1322</v>
+        <v>1316</v>
       </c>
       <c r="H202" s="11" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="I202" s="11" t="s">
         <v>385</v>
@@ -17613,22 +17640,22 @@
         <v>602</v>
       </c>
       <c r="S202" s="22" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="T202" s="26" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="U202" s="35">
         <v>3</v>
       </c>
       <c r="V202" s="26" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="W202" s="26" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="X202" s="26" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="203" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17636,13 +17663,13 @@
         <v>391</v>
       </c>
       <c r="B203" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C203" s="11" t="s">
         <v>289</v>
       </c>
       <c r="D203" s="11" t="s">
-        <v>1353</v>
+        <v>1347</v>
       </c>
       <c r="E203" s="11" t="s">
         <v>369</v>
@@ -17675,22 +17702,22 @@
         <v>602</v>
       </c>
       <c r="S203" s="22" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="T203" s="26" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="U203" s="35">
         <v>1</v>
       </c>
       <c r="V203" s="26" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="W203" s="26" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="X203" s="26" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="204" spans="1:24" s="65" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -17698,31 +17725,31 @@
         <v>391</v>
       </c>
       <c r="B204" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C204" s="11" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="D204" s="11" t="s">
-        <v>1354</v>
+        <v>1348</v>
       </c>
       <c r="E204" s="11" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="F204" s="11" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="G204" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H204" s="11" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="I204" s="11" t="s">
         <v>385</v>
       </c>
       <c r="J204" s="11" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="K204" s="11" t="s">
         <v>256</v>
@@ -17752,16 +17779,16 @@
         <v>391</v>
       </c>
       <c r="B205" s="11" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C205" s="11" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="D205" s="11" t="s">
-        <v>1355</v>
+        <v>1349</v>
       </c>
       <c r="E205" s="11" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="F205" s="11" t="s">
         <v>291</v>
@@ -17776,7 +17803,7 @@
         <v>385</v>
       </c>
       <c r="J205" s="11" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
       <c r="K205" s="11" t="s">
         <v>256</v>
@@ -17795,22 +17822,22 @@
         <v>602</v>
       </c>
       <c r="S205" s="22" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="T205" s="26" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="U205" s="35">
         <v>2</v>
       </c>
       <c r="V205" s="26" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="W205" s="26" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="X205" s="26" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="206" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17818,7 +17845,7 @@
         <v>391</v>
       </c>
       <c r="B206" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C206" s="11" t="s">
         <v>299</v>
@@ -17833,7 +17860,7 @@
         <v>305</v>
       </c>
       <c r="G206" s="11" t="s">
-        <v>1325</v>
+        <v>1319</v>
       </c>
       <c r="H206" s="11" t="s">
         <v>426</v>
@@ -17862,7 +17889,7 @@
         <v>391</v>
       </c>
       <c r="B207" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C207" s="11" t="s">
         <v>300</v>
@@ -17877,7 +17904,7 @@
         <v>306</v>
       </c>
       <c r="G207" s="11" t="s">
-        <v>1325</v>
+        <v>1319</v>
       </c>
       <c r="H207" s="11" t="s">
         <v>426</v>
@@ -17901,22 +17928,22 @@
         <v>602</v>
       </c>
       <c r="S207" s="25" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="T207" s="22" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="U207" s="23">
         <v>1</v>
       </c>
       <c r="V207" s="22" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="W207" s="22" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="X207" s="25" t="s">
-        <v>1121</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="208" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17924,7 +17951,7 @@
         <v>391</v>
       </c>
       <c r="B208" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C208" s="15" t="s">
         <v>301</v>
@@ -17936,10 +17963,10 @@
         <v>524</v>
       </c>
       <c r="F208" s="11" t="s">
-        <v>1326</v>
+        <v>1320</v>
       </c>
       <c r="G208" s="11" t="s">
-        <v>1325</v>
+        <v>1319</v>
       </c>
       <c r="H208" s="11" t="s">
         <v>426</v>
@@ -17948,7 +17975,7 @@
         <v>384</v>
       </c>
       <c r="J208" s="11" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
       <c r="M208" s="11" t="s">
         <v>66</v>
@@ -17957,7 +17984,7 @@
         <v>6</v>
       </c>
       <c r="P208" s="11" t="s">
-        <v>1712</v>
+        <v>1699</v>
       </c>
       <c r="Q208" s="11">
         <v>1</v>
@@ -17966,22 +17993,22 @@
         <v>602</v>
       </c>
       <c r="S208" s="25" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="T208" s="22" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="U208" s="23">
         <v>2</v>
       </c>
       <c r="V208" s="22" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="W208" s="22" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="X208" s="25" t="s">
-        <v>1121</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="209" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17989,7 +18016,7 @@
         <v>391</v>
       </c>
       <c r="B209" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C209" s="15" t="s">
         <v>302</v>
@@ -18001,10 +18028,10 @@
         <v>524</v>
       </c>
       <c r="F209" s="11" t="s">
-        <v>1327</v>
+        <v>1321</v>
       </c>
       <c r="G209" s="11" t="s">
-        <v>1328</v>
+        <v>1322</v>
       </c>
       <c r="H209" s="11" t="s">
         <v>426</v>
@@ -18031,22 +18058,22 @@
         <v>602</v>
       </c>
       <c r="S209" s="25" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="T209" s="22" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="U209" s="23">
         <v>3</v>
       </c>
       <c r="V209" s="22" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="W209" s="22" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="X209" s="25" t="s">
-        <v>1121</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="210" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -18054,10 +18081,10 @@
         <v>391</v>
       </c>
       <c r="B210" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C210" s="15" t="s">
-        <v>1148</v>
+        <v>1142</v>
       </c>
       <c r="D210" s="11" t="s">
         <v>692</v>
@@ -18066,10 +18093,10 @@
         <v>524</v>
       </c>
       <c r="F210" s="11" t="s">
-        <v>1329</v>
+        <v>1323</v>
       </c>
       <c r="G210" s="11" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="H210" s="11" t="s">
         <v>512</v>
@@ -18078,7 +18105,7 @@
         <v>384</v>
       </c>
       <c r="J210" s="11" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="K210" s="11" t="s">
         <v>518</v>
@@ -18099,22 +18126,22 @@
         <v>602</v>
       </c>
       <c r="S210" s="25" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="T210" s="22" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="U210" s="35">
         <v>1</v>
       </c>
       <c r="V210" s="26" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="W210" s="26" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="X210" s="26" t="s">
-        <v>1117</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="211" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -18122,10 +18149,10 @@
         <v>391</v>
       </c>
       <c r="B211" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C211" s="15" t="s">
-        <v>1149</v>
+        <v>1143</v>
       </c>
       <c r="D211" s="11" t="s">
         <v>692</v>
@@ -18134,10 +18161,10 @@
         <v>524</v>
       </c>
       <c r="F211" s="11" t="s">
-        <v>1331</v>
+        <v>1325</v>
       </c>
       <c r="G211" s="11" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="H211" s="11" t="s">
         <v>512</v>
@@ -18146,7 +18173,7 @@
         <v>384</v>
       </c>
       <c r="J211" s="11" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
       <c r="K211" s="11" t="s">
         <v>525</v>
@@ -18167,22 +18194,22 @@
         <v>602</v>
       </c>
       <c r="S211" s="25" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="T211" s="22" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="U211" s="35">
         <v>2</v>
       </c>
       <c r="V211" s="26" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="W211" s="26" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="X211" s="26" t="s">
-        <v>1117</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="212" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -18190,10 +18217,10 @@
         <v>391</v>
       </c>
       <c r="B212" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C212" s="15" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="D212" s="11" t="s">
         <v>692</v>
@@ -18202,10 +18229,10 @@
         <v>524</v>
       </c>
       <c r="F212" s="11" t="s">
-        <v>1332</v>
+        <v>1326</v>
       </c>
       <c r="G212" s="11" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="H212" s="11" t="s">
         <v>680</v>
@@ -18214,7 +18241,7 @@
         <v>384</v>
       </c>
       <c r="J212" s="11" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="K212" s="11" t="s">
         <v>520</v>
@@ -18235,22 +18262,22 @@
         <v>602</v>
       </c>
       <c r="S212" s="25" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="T212" s="22" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="U212" s="35">
         <v>3</v>
       </c>
       <c r="V212" s="26" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="W212" s="26" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="X212" s="26" t="s">
-        <v>1117</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="213" spans="1:24" s="15" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -18258,7 +18285,7 @@
         <v>391</v>
       </c>
       <c r="B213" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C213" s="15" t="s">
         <v>740</v>
@@ -18273,7 +18300,7 @@
         <v>698</v>
       </c>
       <c r="G213" s="11" t="s">
-        <v>1333</v>
+        <v>1327</v>
       </c>
       <c r="H213" s="11" t="s">
         <v>699</v>
@@ -18314,16 +18341,16 @@
         <v>391</v>
       </c>
       <c r="B214" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C214" s="11" t="s">
-        <v>1627</v>
+        <v>1619</v>
       </c>
       <c r="D214" s="11" t="s">
-        <v>1624</v>
+        <v>1616</v>
       </c>
       <c r="E214" s="11" t="s">
-        <v>1625</v>
+        <v>1617</v>
       </c>
       <c r="F214" s="11" t="s">
         <v>643</v>
@@ -18353,22 +18380,22 @@
         <v>602</v>
       </c>
       <c r="S214" s="25" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="T214" s="22" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="U214" s="23">
         <v>4</v>
       </c>
       <c r="V214" s="22" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="W214" s="22" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="X214" s="25" t="s">
-        <v>1644</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="215" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -18376,19 +18403,19 @@
         <v>391</v>
       </c>
       <c r="B215" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C215" s="11" t="s">
-        <v>1628</v>
+        <v>1620</v>
       </c>
       <c r="D215" s="11" t="s">
-        <v>1629</v>
+        <v>1621</v>
       </c>
       <c r="E215" s="11" t="s">
-        <v>1626</v>
+        <v>1618</v>
       </c>
       <c r="F215" s="11" t="s">
-        <v>1118</v>
+        <v>1112</v>
       </c>
       <c r="G215" s="11" t="s">
         <v>646</v>
@@ -18400,10 +18427,10 @@
         <v>384</v>
       </c>
       <c r="J215" s="11" t="s">
-        <v>1630</v>
+        <v>1622</v>
       </c>
       <c r="K215" s="11" t="s">
-        <v>1119</v>
+        <v>1113</v>
       </c>
       <c r="M215" s="11" t="s">
         <v>66</v>
@@ -18415,22 +18442,22 @@
         <v>602</v>
       </c>
       <c r="S215" s="25" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="T215" s="22" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="U215" s="23">
         <v>5</v>
       </c>
       <c r="V215" s="22" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="W215" s="22" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="X215" s="25" t="s">
-        <v>1644</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="216" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -18438,13 +18465,13 @@
         <v>391</v>
       </c>
       <c r="B216" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C216" s="11" t="s">
         <v>303</v>
       </c>
       <c r="D216" s="11" t="s">
-        <v>1356</v>
+        <v>1350</v>
       </c>
       <c r="E216" s="11" t="s">
         <v>371</v>
@@ -18453,7 +18480,7 @@
         <v>434</v>
       </c>
       <c r="G216" s="11" t="s">
-        <v>1334</v>
+        <v>1328</v>
       </c>
       <c r="H216" s="11" t="s">
         <v>434</v>
@@ -18482,13 +18509,13 @@
         <v>391</v>
       </c>
       <c r="B217" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C217" s="11" t="s">
         <v>682</v>
       </c>
       <c r="D217" s="11" t="s">
-        <v>1356</v>
+        <v>1350</v>
       </c>
       <c r="E217" s="11" t="s">
         <v>371</v>
@@ -18497,7 +18524,7 @@
         <v>307</v>
       </c>
       <c r="G217" s="11" t="s">
-        <v>1334</v>
+        <v>1328</v>
       </c>
       <c r="H217" s="11" t="s">
         <v>434</v>
@@ -18526,7 +18553,7 @@
         <v>391</v>
       </c>
       <c r="B218" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C218" s="11" t="s">
         <v>304</v>
@@ -18538,10 +18565,10 @@
         <v>371</v>
       </c>
       <c r="F218" s="11" t="s">
-        <v>1546</v>
+        <v>1540</v>
       </c>
       <c r="G218" s="11" t="s">
-        <v>1334</v>
+        <v>1328</v>
       </c>
       <c r="H218" s="11" t="s">
         <v>434</v>
@@ -18562,10 +18589,10 @@
         <v>602</v>
       </c>
       <c r="S218" s="25" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="T218" s="22" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="U218" s="23">
         <v>1</v>
@@ -18574,10 +18601,10 @@
         <v>907</v>
       </c>
       <c r="W218" s="22" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="X218" s="26" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="219" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -18585,7 +18612,7 @@
         <v>391</v>
       </c>
       <c r="B219" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C219" s="11" t="s">
         <v>683</v>
@@ -18597,10 +18624,10 @@
         <v>371</v>
       </c>
       <c r="F219" s="11" t="s">
-        <v>1547</v>
+        <v>1541</v>
       </c>
       <c r="G219" s="11" t="s">
-        <v>1334</v>
+        <v>1328</v>
       </c>
       <c r="H219" s="11" t="s">
         <v>434</v>
@@ -18621,10 +18648,10 @@
         <v>602</v>
       </c>
       <c r="S219" s="25" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="T219" s="22" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="U219" s="23">
         <v>2</v>
@@ -18633,10 +18660,10 @@
         <v>907</v>
       </c>
       <c r="W219" s="22" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="X219" s="26" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="220" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -18644,7 +18671,7 @@
         <v>391</v>
       </c>
       <c r="B220" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C220" s="11" t="s">
         <v>766</v>
@@ -18653,16 +18680,16 @@
         <v>595</v>
       </c>
       <c r="E220" s="11" t="s">
-        <v>1128</v>
+        <v>1122</v>
       </c>
       <c r="F220" s="11" t="s">
-        <v>1548</v>
+        <v>1542</v>
       </c>
       <c r="G220" s="11" t="s">
-        <v>1334</v>
+        <v>1328</v>
       </c>
       <c r="H220" s="11" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="I220" s="11" t="s">
         <v>384</v>
@@ -18686,10 +18713,10 @@
         <v>602</v>
       </c>
       <c r="S220" s="25" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="T220" s="22" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="U220" s="23">
         <v>3</v>
@@ -18698,10 +18725,10 @@
         <v>907</v>
       </c>
       <c r="W220" s="22" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="X220" s="26" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="221" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -18709,7 +18736,7 @@
         <v>391</v>
       </c>
       <c r="B221" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C221" s="11" t="s">
         <v>684</v>
@@ -18718,16 +18745,16 @@
         <v>595</v>
       </c>
       <c r="E221" s="11" t="s">
-        <v>1128</v>
+        <v>1122</v>
       </c>
       <c r="F221" s="11" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="G221" s="11" t="s">
-        <v>1334</v>
+        <v>1328</v>
       </c>
       <c r="H221" s="11" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="I221" s="11" t="s">
         <v>384</v>
@@ -18745,10 +18772,10 @@
         <v>602</v>
       </c>
       <c r="S221" s="25" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="T221" s="22" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="U221" s="23">
         <v>4</v>
@@ -18757,10 +18784,10 @@
         <v>907</v>
       </c>
       <c r="W221" s="22" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="X221" s="26" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="222" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -18768,31 +18795,31 @@
         <v>391</v>
       </c>
       <c r="B222" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C222" s="15" t="s">
-        <v>1145</v>
+        <v>1139</v>
       </c>
       <c r="D222" s="11" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
       <c r="E222" s="11" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="F222" s="11" t="s">
-        <v>1335</v>
+        <v>1329</v>
       </c>
       <c r="G222" s="11" t="s">
-        <v>1336</v>
+        <v>1330</v>
       </c>
       <c r="H222" s="11" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="I222" s="11" t="s">
         <v>384</v>
       </c>
       <c r="J222" s="11" t="s">
-        <v>1141</v>
+        <v>1135</v>
       </c>
       <c r="K222" s="11" t="s">
         <v>519</v>
@@ -18807,10 +18834,10 @@
         <v>602</v>
       </c>
       <c r="S222" s="25" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="T222" s="22" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="U222" s="23">
         <v>5</v>
@@ -18819,10 +18846,10 @@
         <v>907</v>
       </c>
       <c r="W222" s="22" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="X222" s="26" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="223" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -18830,31 +18857,31 @@
         <v>391</v>
       </c>
       <c r="B223" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C223" s="15" t="s">
-        <v>1146</v>
+        <v>1140</v>
       </c>
       <c r="D223" s="11" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
       <c r="E223" s="11" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="F223" s="11" t="s">
-        <v>1337</v>
+        <v>1331</v>
       </c>
       <c r="G223" s="11" t="s">
-        <v>1336</v>
+        <v>1330</v>
       </c>
       <c r="H223" s="11" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="I223" s="11" t="s">
         <v>384</v>
       </c>
       <c r="J223" s="11" t="s">
-        <v>1142</v>
+        <v>1136</v>
       </c>
       <c r="K223" s="11" t="s">
         <v>525</v>
@@ -18869,10 +18896,10 @@
         <v>602</v>
       </c>
       <c r="S223" s="25" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="T223" s="22" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="U223" s="23">
         <v>6</v>
@@ -18881,10 +18908,10 @@
         <v>907</v>
       </c>
       <c r="W223" s="22" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="X223" s="26" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="224" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -18892,31 +18919,31 @@
         <v>391</v>
       </c>
       <c r="B224" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C224" s="15" t="s">
-        <v>1147</v>
+        <v>1141</v>
       </c>
       <c r="D224" s="11" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
       <c r="E224" s="11" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="F224" s="11" t="s">
-        <v>1550</v>
+        <v>1544</v>
       </c>
       <c r="G224" s="11" t="s">
-        <v>1336</v>
+        <v>1330</v>
       </c>
       <c r="H224" s="11" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="I224" s="11" t="s">
         <v>384</v>
       </c>
       <c r="J224" s="11" t="s">
-        <v>1143</v>
+        <v>1137</v>
       </c>
       <c r="K224" s="11" t="s">
         <v>520</v>
@@ -18931,10 +18958,10 @@
         <v>602</v>
       </c>
       <c r="S224" s="25" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="T224" s="22" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="U224" s="23">
         <v>7</v>
@@ -18943,10 +18970,10 @@
         <v>907</v>
       </c>
       <c r="W224" s="22" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="X224" s="26" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="225" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -18954,13 +18981,13 @@
         <v>391</v>
       </c>
       <c r="B225" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C225" s="11" t="s">
         <v>647</v>
       </c>
       <c r="D225" s="11" t="s">
-        <v>1604</v>
+        <v>1596</v>
       </c>
       <c r="E225" s="11" t="s">
         <v>648</v>
@@ -18999,19 +19026,19 @@
         <v>391</v>
       </c>
       <c r="B226" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C226" s="11" t="s">
         <v>651</v>
       </c>
       <c r="D226" s="11" t="s">
-        <v>1604</v>
+        <v>1596</v>
       </c>
       <c r="E226" s="11" t="s">
         <v>648</v>
       </c>
       <c r="F226" s="11" t="s">
-        <v>1551</v>
+        <v>1545</v>
       </c>
       <c r="G226" s="11" t="s">
         <v>652</v>
@@ -19038,10 +19065,10 @@
         <v>602</v>
       </c>
       <c r="S226" s="25" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="T226" s="67" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="U226" s="23">
         <v>1</v>
@@ -19050,10 +19077,10 @@
         <v>907</v>
       </c>
       <c r="W226" s="22" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="X226" s="26" t="s">
-        <v>1152</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="227" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19061,19 +19088,19 @@
         <v>391</v>
       </c>
       <c r="B227" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C227" s="11" t="s">
         <v>654</v>
       </c>
       <c r="D227" s="11" t="s">
-        <v>1604</v>
+        <v>1596</v>
       </c>
       <c r="E227" s="11" t="s">
         <v>648</v>
       </c>
       <c r="F227" s="11" t="s">
-        <v>1552</v>
+        <v>1546</v>
       </c>
       <c r="G227" s="11" t="s">
         <v>649</v>
@@ -19097,10 +19124,10 @@
         <v>602</v>
       </c>
       <c r="S227" s="25" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="T227" s="67" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="U227" s="23">
         <v>2</v>
@@ -19109,10 +19136,10 @@
         <v>907</v>
       </c>
       <c r="W227" s="22" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="X227" s="26" t="s">
-        <v>1152</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="228" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19120,19 +19147,19 @@
         <v>391</v>
       </c>
       <c r="B228" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C228" s="11" t="s">
         <v>657</v>
       </c>
       <c r="D228" s="11" t="s">
-        <v>1604</v>
+        <v>1596</v>
       </c>
       <c r="E228" s="11" t="s">
         <v>648</v>
       </c>
       <c r="F228" s="11" t="s">
-        <v>1553</v>
+        <v>1547</v>
       </c>
       <c r="G228" s="11" t="s">
         <v>649</v>
@@ -19156,10 +19183,10 @@
         <v>602</v>
       </c>
       <c r="S228" s="25" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="T228" s="67" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="U228" s="23">
         <v>3</v>
@@ -19168,10 +19195,10 @@
         <v>907</v>
       </c>
       <c r="W228" s="22" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="X228" s="26" t="s">
-        <v>1152</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="229" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19179,13 +19206,13 @@
         <v>391</v>
       </c>
       <c r="B229" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C229" s="11" t="s">
         <v>659</v>
       </c>
       <c r="D229" s="11" t="s">
-        <v>1605</v>
+        <v>1597</v>
       </c>
       <c r="E229" s="11" t="s">
         <v>660</v>
@@ -19224,19 +19251,19 @@
         <v>391</v>
       </c>
       <c r="B230" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C230" s="11" t="s">
         <v>663</v>
       </c>
       <c r="D230" s="11" t="s">
-        <v>1605</v>
+        <v>1597</v>
       </c>
       <c r="E230" s="11" t="s">
         <v>660</v>
       </c>
       <c r="F230" s="11" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G230" s="11" t="s">
         <v>664</v>
@@ -19263,10 +19290,10 @@
         <v>602</v>
       </c>
       <c r="S230" s="25" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="T230" s="67" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="U230" s="23">
         <v>1</v>
@@ -19275,10 +19302,10 @@
         <v>907</v>
       </c>
       <c r="W230" s="22" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="X230" s="26" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="231" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19286,19 +19313,19 @@
         <v>391</v>
       </c>
       <c r="B231" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C231" s="11" t="s">
         <v>666</v>
       </c>
       <c r="D231" s="11" t="s">
-        <v>1605</v>
+        <v>1597</v>
       </c>
       <c r="E231" s="11" t="s">
         <v>660</v>
       </c>
       <c r="F231" s="11" t="s">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="G231" s="11" t="s">
         <v>661</v>
@@ -19322,10 +19349,10 @@
         <v>602</v>
       </c>
       <c r="S231" s="25" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="T231" s="67" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="U231" s="23">
         <v>2</v>
@@ -19334,10 +19361,10 @@
         <v>907</v>
       </c>
       <c r="W231" s="22" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="X231" s="26" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="232" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19345,19 +19372,19 @@
         <v>391</v>
       </c>
       <c r="B232" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C232" s="11" t="s">
         <v>668</v>
       </c>
       <c r="D232" s="11" t="s">
-        <v>1605</v>
+        <v>1597</v>
       </c>
       <c r="E232" s="11" t="s">
         <v>660</v>
       </c>
       <c r="F232" s="11" t="s">
-        <v>1556</v>
+        <v>1550</v>
       </c>
       <c r="G232" s="11" t="s">
         <v>661</v>
@@ -19381,10 +19408,10 @@
         <v>602</v>
       </c>
       <c r="S232" s="25" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="T232" s="67" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="U232" s="23">
         <v>3</v>
@@ -19393,10 +19420,10 @@
         <v>907</v>
       </c>
       <c r="W232" s="22" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="X232" s="26" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="233" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19404,13 +19431,13 @@
         <v>391</v>
       </c>
       <c r="B233" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C233" s="11" t="s">
         <v>670</v>
       </c>
       <c r="D233" s="11" t="s">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="E233" s="11" t="s">
         <v>671</v>
@@ -19419,10 +19446,10 @@
         <v>567</v>
       </c>
       <c r="G233" s="11" t="s">
-        <v>1338</v>
+        <v>1332</v>
       </c>
       <c r="H233" s="11" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
       <c r="I233" s="11" t="s">
         <v>384</v>
@@ -19449,25 +19476,25 @@
         <v>391</v>
       </c>
       <c r="B234" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C234" s="11" t="s">
         <v>673</v>
       </c>
       <c r="D234" s="11" t="s">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="E234" s="11" t="s">
         <v>671</v>
       </c>
       <c r="F234" s="11" t="s">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="G234" s="11" t="s">
-        <v>1339</v>
+        <v>1333</v>
       </c>
       <c r="H234" s="11" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
       <c r="I234" s="11" t="s">
         <v>384</v>
@@ -19488,10 +19515,10 @@
         <v>602</v>
       </c>
       <c r="S234" s="25" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="T234" s="67" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="U234" s="23">
         <v>1</v>
@@ -19500,10 +19527,10 @@
         <v>907</v>
       </c>
       <c r="W234" s="22" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="X234" s="26" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="235" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19511,25 +19538,25 @@
         <v>391</v>
       </c>
       <c r="B235" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C235" s="11" t="s">
         <v>675</v>
       </c>
       <c r="D235" s="11" t="s">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="E235" s="11" t="s">
         <v>671</v>
       </c>
       <c r="F235" s="11" t="s">
-        <v>1558</v>
+        <v>1552</v>
       </c>
       <c r="G235" s="11" t="s">
-        <v>1338</v>
+        <v>1332</v>
       </c>
       <c r="H235" s="11" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
       <c r="I235" s="11" t="s">
         <v>384</v>
@@ -19547,10 +19574,10 @@
         <v>602</v>
       </c>
       <c r="S235" s="25" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="T235" s="67" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="U235" s="23">
         <v>2</v>
@@ -19559,10 +19586,10 @@
         <v>907</v>
       </c>
       <c r="W235" s="22" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="X235" s="26" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="236" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19570,25 +19597,25 @@
         <v>391</v>
       </c>
       <c r="B236" s="11" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C236" s="11" t="s">
         <v>677</v>
       </c>
       <c r="D236" s="11" t="s">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="E236" s="11" t="s">
         <v>671</v>
       </c>
       <c r="F236" s="11" t="s">
-        <v>1559</v>
+        <v>1553</v>
       </c>
       <c r="G236" s="11" t="s">
-        <v>1338</v>
+        <v>1332</v>
       </c>
       <c r="H236" s="11" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
       <c r="I236" s="11" t="s">
         <v>384</v>
@@ -19620,7 +19647,7 @@
         <v>531</v>
       </c>
       <c r="E237" s="11" t="s">
-        <v>1623</v>
+        <v>1615</v>
       </c>
       <c r="F237" s="11" t="s">
         <v>495</v>
@@ -19629,7 +19656,7 @@
         <v>497</v>
       </c>
       <c r="H237" s="15" t="s">
-        <v>1638</v>
+        <v>1630</v>
       </c>
       <c r="I237" s="11" t="s">
         <v>384</v>
@@ -19653,19 +19680,19 @@
         <v>309</v>
       </c>
       <c r="T237" s="67" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
       <c r="U237" s="23">
         <v>1</v>
       </c>
       <c r="V237" s="22" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
       <c r="W237" s="22" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="X237" s="22" t="s">
-        <v>1163</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="238" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19682,16 +19709,16 @@
         <v>597</v>
       </c>
       <c r="E238" s="11" t="s">
-        <v>1623</v>
+        <v>1615</v>
       </c>
       <c r="F238" s="11" t="s">
-        <v>1560</v>
+        <v>1554</v>
       </c>
       <c r="G238" s="11" t="s">
         <v>801</v>
       </c>
       <c r="H238" s="15" t="s">
-        <v>1645</v>
+        <v>1637</v>
       </c>
       <c r="I238" s="11" t="s">
         <v>384</v>
@@ -19706,7 +19733,7 @@
         <v>6</v>
       </c>
       <c r="P238" s="11" t="s">
-        <v>1607</v>
+        <v>1599</v>
       </c>
       <c r="Q238" s="11">
         <v>1</v>
@@ -19718,19 +19745,19 @@
         <v>309</v>
       </c>
       <c r="T238" s="67" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
       <c r="U238" s="23">
         <v>2</v>
       </c>
       <c r="V238" s="22" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
       <c r="W238" s="22" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="X238" s="22" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="239" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19747,16 +19774,16 @@
         <v>827</v>
       </c>
       <c r="E239" s="11" t="s">
-        <v>1623</v>
+        <v>1615</v>
       </c>
       <c r="F239" s="11" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="G239" s="11" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="H239" s="11" t="s">
-        <v>1448</v>
+        <v>1442</v>
       </c>
       <c r="I239" s="11" t="s">
         <v>384</v>
@@ -19777,19 +19804,19 @@
         <v>309</v>
       </c>
       <c r="T239" s="67" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
       <c r="U239" s="23">
         <v>3</v>
       </c>
       <c r="V239" s="22" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
       <c r="W239" s="22" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="X239" s="22" t="s">
-        <v>1164</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="240" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19797,7 +19824,7 @@
         <v>391</v>
       </c>
       <c r="B240" s="11" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C240" s="11" t="s">
         <v>314</v>
@@ -19809,13 +19836,13 @@
         <v>348</v>
       </c>
       <c r="F240" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="G240" s="11" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="H240" s="11" t="s">
-        <v>1647</v>
+        <v>1639</v>
       </c>
       <c r="I240" s="11" t="s">
         <v>385</v>
@@ -19836,22 +19863,22 @@
         <v>605</v>
       </c>
       <c r="S240" s="22" t="s">
-        <v>1177</v>
+        <v>1171</v>
       </c>
       <c r="T240" s="67" t="s">
-        <v>1180</v>
+        <v>1174</v>
       </c>
       <c r="U240" s="23">
         <v>1</v>
       </c>
       <c r="V240" s="22" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="W240" s="22" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
       <c r="X240" s="22" t="s">
-        <v>1179</v>
+        <v>1173</v>
       </c>
     </row>
   </sheetData>
@@ -19907,16 +19934,16 @@
     </row>
     <row r="3" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>1713</v>
+        <v>1700</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>1714</v>
+        <v>1701</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>1715</v>
+        <v>1702</v>
       </c>
       <c r="G3" s="39"/>
       <c r="H3" s="40"/>
@@ -19925,16 +19952,16 @@
     </row>
     <row r="4" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>1716</v>
+        <v>1703</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>1403</v>
+        <v>1397</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>1717</v>
+        <v>1704</v>
       </c>
       <c r="G4" s="39"/>
       <c r="H4" s="40"/>
@@ -19949,7 +19976,7 @@
         <v>405</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>1641</v>
+        <v>1633</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>631</v>
@@ -19967,7 +19994,7 @@
         <v>69</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>1642</v>
+        <v>1634</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>632</v>
@@ -19982,7 +20009,7 @@
         <v>15</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>1476</v>
+        <v>1470</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>899</v>
@@ -20018,7 +20045,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>897</v>
@@ -20033,16 +20060,16 @@
     </row>
     <row r="10" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1718</v>
+        <v>1705</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>1719</v>
+        <v>1706</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>1720</v>
+        <v>1707</v>
       </c>
       <c r="G10" s="40"/>
       <c r="H10" s="40"/>
@@ -20060,7 +20087,7 @@
         <v>409</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20074,7 +20101,7 @@
         <v>411</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>1220</v>
+        <v>1214</v>
       </c>
       <c r="I12" s="2"/>
     </row>
@@ -20089,7 +20116,7 @@
         <v>413</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="42" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -20097,13 +20124,13 @@
         <v>47</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>868</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>1223</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20129,7 +20156,7 @@
         <v>423</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>1639</v>
+        <v>1631</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>443</v>
@@ -20144,7 +20171,7 @@
         <v>435</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>1640</v>
+        <v>1632</v>
       </c>
       <c r="D17" s="46" t="s">
         <v>741</v>
@@ -20155,10 +20182,10 @@
         <v>110</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>1665</v>
+        <v>1657</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1640</v>
+        <v>1632</v>
       </c>
       <c r="D18" s="46" t="s">
         <v>742</v>
@@ -20172,7 +20199,7 @@
         <v>702</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1640</v>
+        <v>1632</v>
       </c>
       <c r="D19" s="46" t="s">
         <v>743</v>
@@ -20186,7 +20213,7 @@
         <v>703</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>1640</v>
+        <v>1632</v>
       </c>
       <c r="D20" s="46" t="s">
         <v>744</v>
@@ -20200,7 +20227,7 @@
         <v>704</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>1640</v>
+        <v>1632</v>
       </c>
       <c r="D21" s="46" t="s">
         <v>745</v>
@@ -20214,7 +20241,7 @@
         <v>756</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>1640</v>
+        <v>1632</v>
       </c>
       <c r="D22" s="51" t="s">
         <v>760</v>
@@ -20225,10 +20252,10 @@
         <v>110</v>
       </c>
       <c r="B23" s="50" t="s">
-        <v>1666</v>
+        <v>1658</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>1640</v>
+        <v>1632</v>
       </c>
       <c r="D23" s="51" t="s">
         <v>761</v>
@@ -20242,7 +20269,7 @@
         <v>757</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>1640</v>
+        <v>1632</v>
       </c>
       <c r="D24" s="51" t="s">
         <v>762</v>
@@ -20256,7 +20283,7 @@
         <v>758</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>1640</v>
+        <v>1632</v>
       </c>
       <c r="D25" s="51" t="s">
         <v>763</v>
@@ -20270,7 +20297,7 @@
         <v>759</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>1640</v>
+        <v>1632</v>
       </c>
       <c r="D26" s="51" t="s">
         <v>764</v>
@@ -20284,10 +20311,10 @@
         <v>403</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1634</v>
+        <v>1626</v>
       </c>
       <c r="F27" s="40"/>
     </row>
@@ -20297,23 +20324,23 @@
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="11" t="s">
-        <v>1633</v>
+        <v>1625</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>1635</v>
+        <v>1627</v>
       </c>
       <c r="F28" s="40"/>
     </row>
     <row r="29" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="15" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="D29" s="46" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20372,13 +20399,13 @@
         <v>248</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>1197</v>
+        <v>1191</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>527</v>
       </c>
       <c r="D33" s="46" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
       <c r="F33" s="40"/>
       <c r="G33" s="40"/>
@@ -20446,7 +20473,7 @@
         <v>426</v>
       </c>
       <c r="D37" s="46" t="s">
-        <v>1138</v>
+        <v>1132</v>
       </c>
       <c r="F37" s="44"/>
       <c r="G37" s="40"/>
@@ -20569,13 +20596,13 @@
         <v>292</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="D44" s="46" t="s">
-        <v>1137</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20583,13 +20610,13 @@
         <v>292</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20642,10 +20669,10 @@
         <v>437</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>1638</v>
+        <v>1630</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>1637</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20656,7 +20683,7 @@
         <v>438</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>1643</v>
+        <v>1635</v>
       </c>
       <c r="D50" s="46" t="s">
         <v>448</v>
@@ -20670,7 +20697,7 @@
         <v>439</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>1646</v>
+        <v>1638</v>
       </c>
       <c r="D51" s="46" t="s">
         <v>449</v>
@@ -20734,30 +20761,30 @@
     </row>
     <row r="56" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="17" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>1226</v>
+        <v>1220</v>
       </c>
       <c r="D56" s="56" t="s">
-        <v>1227</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="15" t="s">
-        <v>1371</v>
+        <v>1365</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>1372</v>
+        <v>1366</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>1373</v>
+        <v>1367</v>
       </c>
       <c r="D57" s="46" t="s">
-        <v>1374</v>
+        <v>1368</v>
       </c>
     </row>
   </sheetData>
@@ -20806,7 +20833,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="60" t="s">
-        <v>1393</v>
+        <v>1387</v>
       </c>
       <c r="C2" s="61" t="s">
         <v>459</v>
@@ -20827,7 +20854,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="60" t="s">
-        <v>1394</v>
+        <v>1388</v>
       </c>
       <c r="C3" s="61" t="s">
         <v>463</v>
@@ -20848,10 +20875,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>1671</v>
+        <v>1663</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>1389</v>
+        <v>1383</v>
       </c>
       <c r="D4" s="62" t="s">
         <v>467</v>
@@ -20893,13 +20920,13 @@
         <v>473</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>1390</v>
+        <v>1384</v>
       </c>
       <c r="D6" s="62" t="s">
         <v>474</v>
       </c>
       <c r="E6" s="61" t="s">
-        <v>1390</v>
+        <v>1384</v>
       </c>
       <c r="F6" s="61" t="s">
         <v>475</v>
@@ -20932,16 +20959,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="60" t="s">
-        <v>1384</v>
+        <v>1378</v>
       </c>
       <c r="C8" s="61" t="s">
-        <v>1385</v>
+        <v>1379</v>
       </c>
       <c r="D8" s="62" t="s">
-        <v>1387</v>
+        <v>1381</v>
       </c>
       <c r="E8" s="61" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F8" s="61" t="s">
         <v>480</v>
@@ -20953,16 +20980,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="60" t="s">
-        <v>1670</v>
+        <v>1662</v>
       </c>
       <c r="C9" s="61" t="s">
-        <v>1388</v>
+        <v>1382</v>
       </c>
       <c r="D9" s="62" t="s">
         <v>481</v>
       </c>
       <c r="E9" s="61" t="s">
-        <v>1391</v>
+        <v>1385</v>
       </c>
       <c r="F9" s="61" t="s">
         <v>482</v>
@@ -20983,7 +21010,7 @@
         <v>484</v>
       </c>
       <c r="E10" s="61" t="s">
-        <v>1392</v>
+        <v>1386</v>
       </c>
       <c r="F10" s="61" t="s">
         <v>485</v>
@@ -21016,19 +21043,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1375</v>
+        <v>1369</v>
       </c>
       <c r="D12" s="64" t="s">
-        <v>1376</v>
+        <v>1370</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>1377</v>
+        <v>1371</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>1378</v>
+        <v>1372</v>
       </c>
       <c r="G12" s="59"/>
     </row>
@@ -21037,19 +21064,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="59" t="s">
-        <v>1379</v>
+        <v>1373</v>
       </c>
       <c r="C13" s="59" t="s">
-        <v>1380</v>
+        <v>1374</v>
       </c>
       <c r="D13" s="64" t="s">
-        <v>1381</v>
+        <v>1375</v>
       </c>
       <c r="E13" s="59" t="s">
-        <v>1382</v>
+        <v>1376</v>
       </c>
       <c r="F13" s="59" t="s">
-        <v>1383</v>
+        <v>1377</v>
       </c>
       <c r="G13" s="59"/>
     </row>

--- a/STEPS_data_analysis/data_input/ISO_input_matrix.xlsx
+++ b/STEPS_data_analysis/data_input/ISO_input_matrix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasmalla/Documents/Transferred files/Data/data part 4/WHO/Task order 3/infographic report generation v3/data_input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasmalla/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28338705-3915-394C-A755-402A89830DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF25AC27-C71A-5F4D-9100-398BCED22291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="400" yWindow="600" windowWidth="24520" windowHeight="15220" activeTab="1" xr2:uid="{56236E1D-2702-4F2C-A185-C8269303025C}"/>
+    <workbookView xWindow="400" yWindow="600" windowWidth="24520" windowHeight="15220" activeTab="2" xr2:uid="{56236E1D-2702-4F2C-A185-C8269303025C}"/>
   </bookViews>
   <sheets>
     <sheet name="indicators" sheetId="1" r:id="rId1"/>
@@ -4766,12 +4766,6 @@
     <t>media</t>
   </si>
   <si>
-    <t>Males</t>
-  </si>
-  <si>
-    <t>Females</t>
-  </si>
-  <si>
     <t>m11;m12;m8</t>
   </si>
   <si>
@@ -6383,6 +6377,12 @@
                                 labels = c('Men 15 - 44','Men 45 - 69','Women 15 - 44','Women 45 - 69')),
                bin_age = case_when(age&gt;=18 &amp; age &lt; 45 ~ 1,age&gt;=45 &amp; age &lt; 70 ~ 2),
                bin_age = factor(bin_age,levels = 1:2, labels = c('18-44','45-69')))</t>
+  </si>
+  <si>
+    <t>Men</t>
+  </si>
+  <si>
+    <t>Women</t>
   </si>
 </sst>
 </file>
@@ -7226,13 +7226,13 @@
         <v>373</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>66</v>
@@ -7264,19 +7264,19 @@
         <v>374</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>316</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>380</v>
@@ -7308,19 +7308,19 @@
         <v>375</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>317</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>380</v>
@@ -7355,13 +7355,13 @@
         <v>822</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="I5" s="11" t="s">
         <v>380</v>
@@ -7390,19 +7390,19 @@
         <v>377</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>318</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>380</v>
@@ -7442,19 +7442,19 @@
         <v>378</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>319</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>380</v>
@@ -7489,13 +7489,13 @@
         <v>319</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>380</v>
@@ -7533,7 +7533,7 @@
         <v>320</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>66</v>
@@ -7577,13 +7577,13 @@
         <v>321</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>380</v>
@@ -7612,19 +7612,19 @@
         <v>78</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>322</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="I11" s="11" t="s">
         <v>380</v>
@@ -7677,22 +7677,22 @@
         <v>1171</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>323</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>380</v>
@@ -7757,13 +7757,13 @@
         <v>324</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>380</v>
@@ -7809,10 +7809,10 @@
         <v>67</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>380</v>
@@ -7862,7 +7862,7 @@
         <v>396</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>325</v>
@@ -7871,10 +7871,10 @@
         <v>68</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>380</v>
@@ -7918,13 +7918,13 @@
         <v>326</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>380</v>
@@ -7973,13 +7973,13 @@
         <v>326</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="I17" s="11" t="s">
         <v>380</v>
@@ -8023,13 +8023,13 @@
         <v>506</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>380</v>
@@ -8077,13 +8077,13 @@
         <v>506</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="I19" s="11" t="s">
         <v>380</v>
@@ -8131,13 +8131,13 @@
         <v>326</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>380</v>
@@ -8187,13 +8187,13 @@
         <v>326</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="I21" s="11" t="s">
         <v>380</v>
@@ -8252,10 +8252,10 @@
         <v>494</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>380</v>
@@ -8288,19 +8288,19 @@
         <v>85</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>349</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="I23" s="11" t="s">
         <v>380</v>
@@ -8333,19 +8333,19 @@
         <v>86</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>328</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="I24" s="11" t="s">
         <v>380</v>
@@ -8378,7 +8378,7 @@
         <v>87</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>329</v>
@@ -8387,10 +8387,10 @@
         <v>69</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="I25" s="11" t="s">
         <v>380</v>
@@ -8429,13 +8429,13 @@
         <v>330</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="I26" s="11" t="s">
         <v>380</v>
@@ -8491,19 +8491,19 @@
         <v>331</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="I27" s="11" t="s">
         <v>380</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>726</v>
@@ -8547,19 +8547,19 @@
         <v>90</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>332</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>380</v>
@@ -8615,19 +8615,19 @@
         <v>91</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>333</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="I29" s="11" t="s">
         <v>380</v>
@@ -8680,25 +8680,25 @@
         <v>92</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>334</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>380</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>724</v>
@@ -8725,19 +8725,19 @@
         <v>93</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>334</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="I31" s="11" t="s">
         <v>380</v>
@@ -8776,13 +8776,13 @@
         <v>335</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="G32" s="11" t="s">
+        <v>1645</v>
+      </c>
+      <c r="H32" s="11" t="s">
         <v>1647</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>1649</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>380</v>
@@ -8791,7 +8791,7 @@
         <v>41</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="M32" s="11" t="s">
         <v>66</v>
@@ -8821,13 +8821,13 @@
         <v>335</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="G33" s="11" t="s">
+        <v>1646</v>
+      </c>
+      <c r="H33" s="11" t="s">
         <v>1648</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>1650</v>
       </c>
       <c r="I33" s="11" t="s">
         <v>380</v>
@@ -8836,7 +8836,7 @@
         <v>70</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="M33" s="11" t="s">
         <v>66</v>
@@ -8877,19 +8877,19 @@
         <v>95</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>336</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>380</v>
@@ -8922,19 +8922,19 @@
         <v>96</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>336</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="I35" s="11" t="s">
         <v>380</v>
@@ -8967,19 +8967,19 @@
         <v>750</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>509</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="I36" s="11" t="s">
         <v>380</v>
@@ -9038,13 +9038,13 @@
         <v>337</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="I37" s="11" t="s">
         <v>380</v>
@@ -9100,13 +9100,13 @@
         <v>338</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="I38" s="11" t="s">
         <v>380</v>
@@ -9162,13 +9162,13 @@
         <v>339</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="I39" s="11" t="s">
         <v>380</v>
@@ -9210,7 +9210,7 @@
         <v>836</v>
       </c>
       <c r="X39" s="25" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="40" spans="1:24" ht="17.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9230,22 +9230,22 @@
         <v>340</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="I40" s="11" t="s">
         <v>380</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="M40" s="11" t="s">
         <v>66</v>
@@ -9275,13 +9275,13 @@
         <v>341</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="I41" s="11" t="s">
         <v>380</v>
@@ -9319,13 +9319,13 @@
         <v>342</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="I42" s="11" t="s">
         <v>380</v>
@@ -9364,13 +9364,13 @@
         <v>343</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="I43" s="11" t="s">
         <v>380</v>
@@ -9406,7 +9406,7 @@
         <v>836</v>
       </c>
       <c r="X43" s="25" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="44" spans="1:24" ht="17.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9417,7 +9417,7 @@
         <v>1175</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>574</v>
@@ -9432,7 +9432,7 @@
         <v>1207</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="I44" s="11" t="s">
         <v>380</v>
@@ -9462,7 +9462,7 @@
         <v>1175</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>574</v>
@@ -9477,7 +9477,7 @@
         <v>1207</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="I45" s="11" t="s">
         <v>380</v>
@@ -9507,7 +9507,7 @@
         <v>1175</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>574</v>
@@ -9522,7 +9522,7 @@
         <v>1207</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="I46" s="11" t="s">
         <v>380</v>
@@ -9564,10 +9564,10 @@
         <v>1210</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="I47" s="11" t="s">
         <v>380</v>
@@ -9609,10 +9609,10 @@
         <v>1211</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="I48" s="11" t="s">
         <v>380</v>
@@ -9654,10 +9654,10 @@
         <v>1212</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="I49" s="11" t="s">
         <v>380</v>
@@ -9696,13 +9696,13 @@
         <v>344</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="G50" s="11" t="s">
+        <v>1702</v>
+      </c>
+      <c r="H50" s="11" t="s">
         <v>1704</v>
-      </c>
-      <c r="H50" s="11" t="s">
-        <v>1706</v>
       </c>
       <c r="I50" s="11" t="s">
         <v>380</v>
@@ -9741,19 +9741,19 @@
         <v>774</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="I51" s="11" t="s">
         <v>380</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>59</v>
@@ -9812,10 +9812,10 @@
         <v>411</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="I52" s="11" t="s">
         <v>380</v>
@@ -9861,10 +9861,10 @@
         <v>1319</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="I53" s="11" t="s">
         <v>380</v>
@@ -9900,7 +9900,7 @@
         <v>836</v>
       </c>
       <c r="X53" s="25" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="54" spans="1:24" ht="17.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9923,10 +9923,10 @@
         <v>76</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="I54" s="11" t="s">
         <v>380</v>
@@ -9964,13 +9964,13 @@
         <v>777</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="I55" s="11" t="s">
         <v>380</v>
@@ -10014,7 +10014,7 @@
         <v>1213</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="I56" s="11" t="s">
         <v>380</v>
@@ -10121,7 +10121,7 @@
         <v>850</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="H58" s="11" t="s">
         <v>851</v>
@@ -10174,13 +10174,13 @@
         <v>857</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="I59" s="11" t="s">
         <v>380</v>
@@ -10228,13 +10228,13 @@
         <v>861</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="I60" s="11" t="s">
         <v>380</v>
@@ -10282,13 +10282,13 @@
         <v>865</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="I61" s="11" t="s">
         <v>380</v>
@@ -10336,13 +10336,13 @@
         <v>868</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="I62" s="11" t="s">
         <v>380</v>
@@ -10390,13 +10390,13 @@
         <v>350</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="G63" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="I63" s="11" t="s">
         <v>380</v>
@@ -10452,13 +10452,13 @@
         <v>350</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="G64" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="I64" s="11" t="s">
         <v>380</v>
@@ -10814,13 +10814,13 @@
         <v>352</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="I70" s="11" t="s">
         <v>380</v>
@@ -10879,13 +10879,13 @@
         <v>353</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="I71" s="11" t="s">
         <v>380</v>
@@ -10938,13 +10938,13 @@
         <v>354</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="G72" s="11" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="I72" s="11" t="s">
         <v>380</v>
@@ -11003,13 +11003,13 @@
         <v>355</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="I73" s="11" t="s">
         <v>380</v>
@@ -11044,13 +11044,13 @@
         <v>355</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="I74" s="11" t="s">
         <v>380</v>
@@ -11088,13 +11088,13 @@
         <v>356</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="I75" s="11" t="s">
         <v>380</v>
@@ -11132,13 +11132,13 @@
         <v>357</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="I76" s="11" t="s">
         <v>380</v>
@@ -11173,13 +11173,13 @@
         <v>358</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="I77" s="11" t="s">
         <v>380</v>
@@ -11214,13 +11214,13 @@
         <v>358</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="I78" s="11" t="s">
         <v>380</v>
@@ -11255,13 +11255,13 @@
         <v>358</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="G79" s="11" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="I79" s="11" t="s">
         <v>380</v>
@@ -11296,13 +11296,13 @@
         <v>358</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="I80" s="11" t="s">
         <v>380</v>
@@ -11337,13 +11337,13 @@
         <v>358</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="I81" s="11" t="s">
         <v>380</v>
@@ -11378,13 +11378,13 @@
         <v>358</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="G82" s="11" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="I82" s="11" t="s">
         <v>380</v>
@@ -11880,7 +11880,7 @@
         <v>583</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="F93" s="11" t="s">
         <v>1227</v>
@@ -11889,7 +11889,7 @@
         <v>1228</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I93" s="11" t="s">
         <v>380</v>
@@ -11907,7 +11907,7 @@
         <v>6</v>
       </c>
       <c r="P93" s="11" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="Q93" s="11">
         <v>1</v>
@@ -11948,7 +11948,7 @@
         <v>584</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="F94" s="11" t="s">
         <v>1229</v>
@@ -11957,7 +11957,7 @@
         <v>1230</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I94" s="11" t="s">
         <v>380</v>
@@ -11993,7 +11993,7 @@
         <v>161</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="F95" s="11" t="s">
         <v>274</v>
@@ -12002,7 +12002,7 @@
         <v>1228</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I95" s="11" t="s">
         <v>380</v>
@@ -12038,7 +12038,7 @@
         <v>162</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="F96" s="11" t="s">
         <v>274</v>
@@ -12047,7 +12047,7 @@
         <v>1228</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I96" s="11" t="s">
         <v>380</v>
@@ -12100,7 +12100,7 @@
         <v>163</v>
       </c>
       <c r="E97" s="11" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="F97" s="11" t="s">
         <v>270</v>
@@ -12109,7 +12109,7 @@
         <v>1228</v>
       </c>
       <c r="H97" s="11" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I97" s="11" t="s">
         <v>380</v>
@@ -12145,7 +12145,7 @@
         <v>163</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="F98" s="11" t="s">
         <v>198</v>
@@ -12154,7 +12154,7 @@
         <v>1228</v>
       </c>
       <c r="H98" s="11" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I98" s="11" t="s">
         <v>380</v>
@@ -12190,7 +12190,7 @@
         <v>163</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="F99" s="11" t="s">
         <v>197</v>
@@ -12199,7 +12199,7 @@
         <v>1228</v>
       </c>
       <c r="H99" s="11" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I99" s="11" t="s">
         <v>380</v>
@@ -12235,7 +12235,7 @@
         <v>167</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="F100" s="11" t="s">
         <v>270</v>
@@ -12244,7 +12244,7 @@
         <v>1228</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I100" s="11" t="s">
         <v>380</v>
@@ -12280,7 +12280,7 @@
         <v>167</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="F101" s="11" t="s">
         <v>198</v>
@@ -12289,7 +12289,7 @@
         <v>1228</v>
       </c>
       <c r="H101" s="11" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I101" s="11" t="s">
         <v>380</v>
@@ -12325,7 +12325,7 @@
         <v>167</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="F102" s="11" t="s">
         <v>197</v>
@@ -12334,7 +12334,7 @@
         <v>1228</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I102" s="11" t="s">
         <v>380</v>
@@ -12370,16 +12370,16 @@
         <v>585</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="G103" s="11" t="s">
         <v>1228</v>
       </c>
       <c r="H103" s="11" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I103" s="11" t="s">
         <v>380</v>
@@ -12432,16 +12432,16 @@
         <v>585</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="F104" s="11" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="G104" s="11" t="s">
         <v>1228</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I104" s="11" t="s">
         <v>380</v>
@@ -12476,16 +12476,16 @@
         <v>585</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="G105" s="11" t="s">
         <v>1228</v>
       </c>
       <c r="H105" s="11" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I105" s="11" t="s">
         <v>380</v>
@@ -12544,7 +12544,7 @@
         <v>172</v>
       </c>
       <c r="E106" s="11" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="F106" s="11" t="s">
         <v>271</v>
@@ -12553,7 +12553,7 @@
         <v>1230</v>
       </c>
       <c r="H106" s="11" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I106" s="11" t="s">
         <v>380</v>
@@ -12588,16 +12588,16 @@
         <v>586</v>
       </c>
       <c r="E107" s="11" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="G107" s="11" t="s">
         <v>1228</v>
       </c>
       <c r="H107" s="11" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I107" s="11" t="s">
         <v>380</v>
@@ -12665,7 +12665,7 @@
         <v>1231</v>
       </c>
       <c r="H108" s="11" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="I108" s="11" t="s">
         <v>380</v>
@@ -12715,19 +12715,19 @@
         <v>207</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="E109" s="11" t="s">
         <v>885</v>
       </c>
       <c r="F109" s="11" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="G109" s="11" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="H109" s="11" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="I109" s="11" t="s">
         <v>380</v>
@@ -12765,13 +12765,13 @@
         <v>359</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="G110" s="11" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="H110" s="11" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="I110" s="11" t="s">
         <v>380</v>
@@ -12800,22 +12800,22 @@
         <v>1177</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="E111" s="11" t="s">
         <v>360</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="G111" s="11" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="H111" s="11" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="I111" s="11" t="s">
         <v>380</v>
@@ -12844,22 +12844,22 @@
         <v>1177</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="E112" s="11" t="s">
         <v>360</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="G112" s="11" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="H112" s="11" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="I112" s="11" t="s">
         <v>380</v>
@@ -12891,19 +12891,19 @@
         <v>223</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="E113" s="11" t="s">
         <v>889</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="G113" s="11" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="H113" s="11" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="I113" s="11" t="s">
         <v>380</v>
@@ -12939,7 +12939,7 @@
         <v>1078</v>
       </c>
       <c r="X113" s="25" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="114" spans="1:24" ht="17.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -12959,13 +12959,13 @@
         <v>361</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="G114" s="11" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="H114" s="11" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="I114" s="11" t="s">
         <v>380</v>
@@ -13003,13 +13003,13 @@
         <v>361</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="G115" s="11" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="H115" s="11" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="I115" s="11" t="s">
         <v>380</v>
@@ -13038,22 +13038,22 @@
         <v>1178</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="E116" s="11" t="s">
         <v>362</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="G116" s="11" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="H116" s="11" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="I116" s="11" t="s">
         <v>380</v>
@@ -13082,22 +13082,22 @@
         <v>1178</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="E117" s="11" t="s">
         <v>362</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="G117" s="11" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="H117" s="11" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="I117" s="11" t="s">
         <v>380</v>
@@ -13129,19 +13129,19 @@
         <v>224</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="E118" s="11" t="s">
         <v>884</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="G118" s="11" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="H118" s="11" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="I118" s="11" t="s">
         <v>380</v>
@@ -13179,13 +13179,13 @@
         <v>363</v>
       </c>
       <c r="F119" s="11" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="G119" s="11" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="H119" s="11" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="I119" s="11" t="s">
         <v>380</v>
@@ -13214,22 +13214,22 @@
         <v>1179</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="E120" s="11" t="s">
         <v>364</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="G120" s="11" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="H120" s="11" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="I120" s="11" t="s">
         <v>380</v>
@@ -13258,22 +13258,22 @@
         <v>1179</v>
       </c>
       <c r="C121" s="36" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="E121" s="36" t="s">
         <v>364</v>
       </c>
       <c r="F121" s="11" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="G121" s="11" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="H121" s="11" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="I121" s="36" t="s">
         <v>380</v>
@@ -13311,13 +13311,13 @@
         <v>365</v>
       </c>
       <c r="F122" s="11" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="G122" s="11" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="H122" s="11" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="I122" s="36" t="s">
         <v>380</v>
@@ -13373,13 +13373,13 @@
         <v>528</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="G123" s="11" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="H123" s="11" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="I123" s="11" t="s">
         <v>380</v>
@@ -13417,13 +13417,13 @@
         <v>528</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="G124" s="11" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="H124" s="11" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="I124" s="11" t="s">
         <v>380</v>
@@ -13461,13 +13461,13 @@
         <v>1323</v>
       </c>
       <c r="F125" s="11" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="G125" s="11" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="H125" s="11" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="I125" s="11" t="s">
         <v>380</v>
@@ -13523,13 +13523,13 @@
         <v>1323</v>
       </c>
       <c r="F126" s="11" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="G126" s="11" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="H126" s="11" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="I126" s="11" t="s">
         <v>380</v>
@@ -13585,13 +13585,13 @@
         <v>1323</v>
       </c>
       <c r="F127" s="11" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="G127" s="11" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="H127" s="11" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="I127" s="11" t="s">
         <v>380</v>
@@ -13647,13 +13647,13 @@
         <v>1323</v>
       </c>
       <c r="F128" s="11" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="G128" s="11" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="H128" s="11" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="I128" s="11" t="s">
         <v>380</v>
@@ -13709,13 +13709,13 @@
         <v>1323</v>
       </c>
       <c r="F129" s="11" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="G129" s="11" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="H129" s="11" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="I129" s="11" t="s">
         <v>380</v>
@@ -13771,13 +13771,13 @@
         <v>1323</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="G130" s="11" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="H130" s="11" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="I130" s="11" t="s">
         <v>380</v>
@@ -13833,13 +13833,13 @@
         <v>1323</v>
       </c>
       <c r="F131" s="11" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="G131" s="11" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="H131" s="11" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="I131" s="11" t="s">
         <v>380</v>
@@ -13901,7 +13901,7 @@
         <v>1232</v>
       </c>
       <c r="H132" s="16" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I132" s="16" t="s">
         <v>380</v>
@@ -13952,7 +13952,7 @@
         <v>1162</v>
       </c>
       <c r="C133" s="16" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="D133" s="16" t="s">
         <v>533</v>
@@ -13964,10 +13964,10 @@
         <v>1233</v>
       </c>
       <c r="G133" s="16" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="H133" s="16" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="I133" s="16" t="s">
         <v>380</v>
@@ -14007,10 +14007,10 @@
         <v>892</v>
       </c>
       <c r="D134" s="16" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="E134" s="16" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="F134" s="16" t="s">
         <v>893</v>
@@ -14064,13 +14064,13 @@
         <v>897</v>
       </c>
       <c r="E135" s="16" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="F135" s="16" t="s">
         <v>1234</v>
       </c>
       <c r="G135" s="16" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="H135" s="16" t="s">
         <v>898</v>
@@ -14112,19 +14112,19 @@
         <v>1162</v>
       </c>
       <c r="C136" s="16" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="D136" s="16" t="s">
         <v>900</v>
       </c>
       <c r="E136" s="16" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="F136" s="16" t="s">
         <v>1235</v>
       </c>
       <c r="G136" s="16" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="H136" s="16" t="s">
         <v>901</v>
@@ -14166,19 +14166,19 @@
         <v>1162</v>
       </c>
       <c r="C137" s="16" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D137" s="16" t="s">
+        <v>1655</v>
+      </c>
+      <c r="E137" s="16" t="s">
         <v>1656</v>
-      </c>
-      <c r="D137" s="16" t="s">
-        <v>1657</v>
-      </c>
-      <c r="E137" s="16" t="s">
-        <v>1658</v>
       </c>
       <c r="F137" s="16" t="s">
         <v>1236</v>
       </c>
       <c r="G137" s="16" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="H137" s="16" t="s">
         <v>903</v>
@@ -14187,7 +14187,7 @@
         <v>380</v>
       </c>
       <c r="J137" s="16" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="K137" s="16" t="s">
         <v>1063</v>
@@ -14226,13 +14226,13 @@
         <v>905</v>
       </c>
       <c r="E138" s="16" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="F138" s="16" t="s">
         <v>1237</v>
       </c>
       <c r="G138" s="16" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="H138" s="16" t="s">
         <v>906</v>
@@ -14280,22 +14280,22 @@
         <v>909</v>
       </c>
       <c r="E139" s="16" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="F139" s="16" t="s">
         <v>1238</v>
       </c>
       <c r="G139" s="16" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="H139" s="16" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="I139" s="16" t="s">
         <v>380</v>
       </c>
       <c r="J139" s="16" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="K139" s="16" t="s">
         <v>1016</v>
@@ -14331,25 +14331,25 @@
         <v>910</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="E140" s="16" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="F140" s="16" t="s">
         <v>1239</v>
       </c>
       <c r="G140" s="16" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="H140" s="16" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="I140" s="16" t="s">
         <v>380</v>
       </c>
       <c r="J140" s="16" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="K140" s="16" t="s">
         <v>1016</v>
@@ -14382,28 +14382,28 @@
         <v>1162</v>
       </c>
       <c r="C141" s="16" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D141" s="16" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E141" s="16" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F141" s="16" t="s">
         <v>1666</v>
       </c>
-      <c r="D141" s="16" t="s">
-        <v>1663</v>
-      </c>
-      <c r="E141" s="16" t="s">
-        <v>1667</v>
-      </c>
-      <c r="F141" s="16" t="s">
-        <v>1668</v>
-      </c>
       <c r="G141" s="16" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
       <c r="H141" s="16" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="I141" s="16" t="s">
         <v>380</v>
       </c>
       <c r="J141" s="16" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="K141" s="16"/>
       <c r="L141" s="16"/>
@@ -14428,31 +14428,31 @@
         <v>1162</v>
       </c>
       <c r="C142" s="16" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D142" s="16" t="s">
+        <v>1669</v>
+      </c>
+      <c r="E142" s="16" t="s">
         <v>1670</v>
       </c>
-      <c r="D142" s="16" t="s">
-        <v>1671</v>
-      </c>
-      <c r="E142" s="16" t="s">
-        <v>1672</v>
-      </c>
       <c r="F142" s="16" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="G142" s="16" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="H142" s="16" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="I142" s="16" t="s">
         <v>380</v>
       </c>
       <c r="J142" s="16" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="K142" s="16" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="L142" s="16"/>
       <c r="M142" s="16" t="s">
@@ -14485,16 +14485,16 @@
         <v>911</v>
       </c>
       <c r="D143" s="16" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="E143" s="16" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="F143" s="16" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="G143" s="16" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="H143" s="16" t="s">
         <v>912</v>
@@ -14503,10 +14503,10 @@
         <v>380</v>
       </c>
       <c r="J143" s="16" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="K143" s="16" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="L143" s="16"/>
       <c r="M143" s="16" t="s">
@@ -14536,7 +14536,7 @@
         <v>1182</v>
       </c>
       <c r="C144" s="17" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="D144" s="17" t="s">
         <v>602</v>
@@ -14582,7 +14582,7 @@
         <v>1182</v>
       </c>
       <c r="C145" s="17" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="D145" s="17" t="s">
         <v>606</v>
@@ -14628,7 +14628,7 @@
         <v>1182</v>
       </c>
       <c r="C146" s="17" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="D146" s="17" t="s">
         <v>609</v>
@@ -14676,7 +14676,7 @@
         <v>1182</v>
       </c>
       <c r="C147" s="17" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="D147" s="17" t="s">
         <v>804</v>
@@ -14724,7 +14724,7 @@
         <v>1182</v>
       </c>
       <c r="C148" s="17" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="D148" s="17" t="s">
         <v>805</v>
@@ -14864,7 +14864,7 @@
         <v>1182</v>
       </c>
       <c r="C151" s="17" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="D151" s="17" t="s">
         <v>623</v>
@@ -14910,7 +14910,7 @@
         <v>1182</v>
       </c>
       <c r="C152" s="17" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="D152" s="17" t="s">
         <v>625</v>
@@ -15005,7 +15005,7 @@
         <v>913</v>
       </c>
       <c r="D154" s="28" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="E154" s="28" t="s">
         <v>1026</v>
@@ -15014,7 +15014,7 @@
         <v>1251</v>
       </c>
       <c r="G154" s="28" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="H154" s="28" t="s">
         <v>914</v>
@@ -15183,16 +15183,16 @@
         <v>922</v>
       </c>
       <c r="D157" s="28" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="E157" s="28" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="F157" s="28" t="s">
         <v>1253</v>
       </c>
       <c r="G157" s="28" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="H157" s="28" t="s">
         <v>923</v>
@@ -15201,7 +15201,7 @@
         <v>380</v>
       </c>
       <c r="J157" s="28" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="K157" s="28"/>
       <c r="L157" s="28"/>
@@ -15247,7 +15247,7 @@
         <v>924</v>
       </c>
       <c r="D158" s="28" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="E158" s="28" t="s">
         <v>1028</v>
@@ -15256,7 +15256,7 @@
         <v>1254</v>
       </c>
       <c r="G158" s="28" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="H158" s="28" t="s">
         <v>631</v>
@@ -15265,7 +15265,7 @@
         <v>380</v>
       </c>
       <c r="J158" s="28" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="K158" s="28" t="s">
         <v>1004</v>
@@ -15301,7 +15301,7 @@
         <v>925</v>
       </c>
       <c r="D159" s="28" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="E159" s="28" t="s">
         <v>1029</v>
@@ -15355,7 +15355,7 @@
         <v>1034</v>
       </c>
       <c r="D160" s="28" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="E160" s="28" t="s">
         <v>1030</v>
@@ -15373,7 +15373,7 @@
         <v>380</v>
       </c>
       <c r="J160" s="28" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="K160" s="28" t="s">
         <v>931</v>
@@ -15409,7 +15409,7 @@
         <v>1035</v>
       </c>
       <c r="D161" s="28" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="E161" s="28" t="s">
         <v>1031</v>
@@ -15418,7 +15418,7 @@
         <v>1257</v>
       </c>
       <c r="G161" s="28" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="H161" s="28" t="s">
         <v>932</v>
@@ -15461,7 +15461,7 @@
         <v>1036</v>
       </c>
       <c r="D162" s="28" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="E162" s="28" t="s">
         <v>1032</v>
@@ -15470,7 +15470,7 @@
         <v>1258</v>
       </c>
       <c r="G162" s="28" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="H162" s="28" t="s">
         <v>934</v>
@@ -15513,7 +15513,7 @@
         <v>1037</v>
       </c>
       <c r="D163" s="28" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="E163" s="28" t="s">
         <v>1033</v>
@@ -15522,7 +15522,7 @@
         <v>1259</v>
       </c>
       <c r="G163" s="28" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="H163" s="28" t="s">
         <v>936</v>
@@ -15800,7 +15800,7 @@
         <v>1184</v>
       </c>
       <c r="C169" s="33" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="D169" s="33" t="s">
         <v>938</v>
@@ -15852,7 +15852,7 @@
         <v>1184</v>
       </c>
       <c r="C170" s="33" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="D170" s="33" t="s">
         <v>941</v>
@@ -15904,7 +15904,7 @@
         <v>1184</v>
       </c>
       <c r="C171" s="33" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="D171" s="33" t="s">
         <v>944</v>
@@ -15956,7 +15956,7 @@
         <v>1184</v>
       </c>
       <c r="C172" s="33" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="D172" s="33" t="s">
         <v>947</v>
@@ -16008,7 +16008,7 @@
         <v>1184</v>
       </c>
       <c r="C173" s="33" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="D173" s="33" t="s">
         <v>950</v>
@@ -16060,10 +16060,10 @@
         <v>1184</v>
       </c>
       <c r="C174" s="33" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="D174" s="33" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="E174" s="33" t="s">
         <v>1045</v>
@@ -16112,7 +16112,7 @@
         <v>1185</v>
       </c>
       <c r="C175" s="32" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="D175" s="32" t="s">
         <v>955</v>
@@ -16124,7 +16124,7 @@
         <v>1278</v>
       </c>
       <c r="G175" s="32" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="H175" s="32" t="s">
         <v>956</v>
@@ -16166,7 +16166,7 @@
         <v>1185</v>
       </c>
       <c r="C176" s="32" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="D176" s="32" t="s">
         <v>958</v>
@@ -16178,7 +16178,7 @@
         <v>1279</v>
       </c>
       <c r="G176" s="32" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="H176" s="32" t="s">
         <v>959</v>
@@ -16232,7 +16232,7 @@
         <v>1280</v>
       </c>
       <c r="G177" s="32" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="H177" s="32" t="s">
         <v>962</v>
@@ -16286,7 +16286,7 @@
         <v>1281</v>
       </c>
       <c r="G178" s="32" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="H178" s="32" t="s">
         <v>966</v>
@@ -16338,7 +16338,7 @@
         <v>1282</v>
       </c>
       <c r="G179" s="32" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="H179" s="32" t="s">
         <v>970</v>
@@ -16390,7 +16390,7 @@
         <v>1283</v>
       </c>
       <c r="G180" s="32" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="H180" s="32" t="s">
         <v>974</v>
@@ -16444,7 +16444,7 @@
         <v>1284</v>
       </c>
       <c r="G181" s="32" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="H181" s="32" t="s">
         <v>978</v>
@@ -16498,7 +16498,7 @@
         <v>1285</v>
       </c>
       <c r="G182" s="32" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="H182" s="32" t="s">
         <v>982</v>
@@ -16552,7 +16552,7 @@
         <v>1286</v>
       </c>
       <c r="G183" s="32" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="H183" s="32" t="s">
         <v>986</v>
@@ -16606,7 +16606,7 @@
         <v>1287</v>
       </c>
       <c r="G184" s="32" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="H184" s="32" t="s">
         <v>989</v>
@@ -16660,7 +16660,7 @@
         <v>1288</v>
       </c>
       <c r="G185" s="32" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="H185" s="32" t="s">
         <v>993</v>
@@ -16714,7 +16714,7 @@
         <v>1289</v>
       </c>
       <c r="G186" s="32" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="H186" s="32" t="s">
         <v>996</v>
@@ -16768,7 +16768,7 @@
         <v>1290</v>
       </c>
       <c r="G187" s="32" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="H187" s="32" t="s">
         <v>1000</v>
@@ -17479,7 +17479,7 @@
         <v>1299</v>
       </c>
       <c r="H200" s="11" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="I200" s="11" t="s">
         <v>385</v>
@@ -17541,7 +17541,7 @@
         <v>1301</v>
       </c>
       <c r="H201" s="11" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="I201" s="11" t="s">
         <v>385</v>
@@ -17609,7 +17609,7 @@
         <v>1299</v>
       </c>
       <c r="H202" s="11" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="I202" s="11" t="s">
         <v>385</v>
@@ -17980,7 +17980,7 @@
         <v>6</v>
       </c>
       <c r="P208" s="11" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="Q208" s="11">
         <v>1</v>
@@ -18340,13 +18340,13 @@
         <v>1187</v>
       </c>
       <c r="C214" s="11" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="D214" s="11" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="E214" s="11" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="F214" s="11" t="s">
         <v>636</v>
@@ -18391,7 +18391,7 @@
         <v>1078</v>
       </c>
       <c r="X214" s="25" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="215" spans="1:24" ht="17.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -18402,13 +18402,13 @@
         <v>1187</v>
       </c>
       <c r="C215" s="11" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="D215" s="11" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="E215" s="11" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="F215" s="11" t="s">
         <v>1095</v>
@@ -18423,7 +18423,7 @@
         <v>384</v>
       </c>
       <c r="J215" s="11" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="K215" s="11" t="s">
         <v>1096</v>
@@ -18453,7 +18453,7 @@
         <v>1078</v>
       </c>
       <c r="X215" s="25" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="216" spans="1:24" ht="17.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -18561,7 +18561,7 @@
         <v>371</v>
       </c>
       <c r="F218" s="11" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="G218" s="11" t="s">
         <v>1311</v>
@@ -18620,7 +18620,7 @@
         <v>371</v>
       </c>
       <c r="F219" s="11" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="G219" s="11" t="s">
         <v>1311</v>
@@ -18679,7 +18679,7 @@
         <v>1105</v>
       </c>
       <c r="F220" s="11" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="G220" s="11" t="s">
         <v>1311</v>
@@ -18744,7 +18744,7 @@
         <v>1105</v>
       </c>
       <c r="F221" s="11" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="G221" s="11" t="s">
         <v>1311</v>
@@ -18927,7 +18927,7 @@
         <v>1104</v>
       </c>
       <c r="F224" s="11" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="G224" s="11" t="s">
         <v>1313</v>
@@ -18983,7 +18983,7 @@
         <v>640</v>
       </c>
       <c r="D225" s="11" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="E225" s="11" t="s">
         <v>641</v>
@@ -19028,13 +19028,13 @@
         <v>644</v>
       </c>
       <c r="D226" s="11" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="E226" s="11" t="s">
         <v>641</v>
       </c>
       <c r="F226" s="11" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="G226" s="11" t="s">
         <v>645</v>
@@ -19090,13 +19090,13 @@
         <v>647</v>
       </c>
       <c r="D227" s="11" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="E227" s="11" t="s">
         <v>641</v>
       </c>
       <c r="F227" s="11" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="G227" s="11" t="s">
         <v>642</v>
@@ -19149,13 +19149,13 @@
         <v>650</v>
       </c>
       <c r="D228" s="11" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="E228" s="11" t="s">
         <v>641</v>
       </c>
       <c r="F228" s="11" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="G228" s="11" t="s">
         <v>642</v>
@@ -19208,7 +19208,7 @@
         <v>652</v>
       </c>
       <c r="D229" s="11" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="E229" s="11" t="s">
         <v>653</v>
@@ -19253,13 +19253,13 @@
         <v>656</v>
       </c>
       <c r="D230" s="11" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="E230" s="11" t="s">
         <v>653</v>
       </c>
       <c r="F230" s="11" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="G230" s="11" t="s">
         <v>657</v>
@@ -19315,13 +19315,13 @@
         <v>659</v>
       </c>
       <c r="D231" s="11" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="E231" s="11" t="s">
         <v>653</v>
       </c>
       <c r="F231" s="11" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="G231" s="11" t="s">
         <v>654</v>
@@ -19374,13 +19374,13 @@
         <v>661</v>
       </c>
       <c r="D232" s="11" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="E232" s="11" t="s">
         <v>653</v>
       </c>
       <c r="F232" s="11" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="G232" s="11" t="s">
         <v>654</v>
@@ -19433,7 +19433,7 @@
         <v>663</v>
       </c>
       <c r="D233" s="11" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="E233" s="11" t="s">
         <v>664</v>
@@ -19478,13 +19478,13 @@
         <v>666</v>
       </c>
       <c r="D234" s="11" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="E234" s="11" t="s">
         <v>664</v>
       </c>
       <c r="F234" s="11" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="G234" s="11" t="s">
         <v>1316</v>
@@ -19540,13 +19540,13 @@
         <v>668</v>
       </c>
       <c r="D235" s="11" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="E235" s="11" t="s">
         <v>664</v>
       </c>
       <c r="F235" s="11" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="G235" s="11" t="s">
         <v>1315</v>
@@ -19599,13 +19599,13 @@
         <v>670</v>
       </c>
       <c r="D236" s="11" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="E236" s="11" t="s">
         <v>664</v>
       </c>
       <c r="F236" s="11" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="G236" s="11" t="s">
         <v>1315</v>
@@ -19643,7 +19643,7 @@
         <v>531</v>
       </c>
       <c r="E237" s="11" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="F237" s="11" t="s">
         <v>495</v>
@@ -19652,7 +19652,7 @@
         <v>497</v>
       </c>
       <c r="H237" s="15" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="I237" s="11" t="s">
         <v>384</v>
@@ -19705,16 +19705,16 @@
         <v>594</v>
       </c>
       <c r="E238" s="11" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="F238" s="11" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="G238" s="11" t="s">
         <v>784</v>
       </c>
       <c r="H238" s="15" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="I238" s="11" t="s">
         <v>384</v>
@@ -19729,7 +19729,7 @@
         <v>6</v>
       </c>
       <c r="P238" s="11" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="Q238" s="11">
         <v>1</v>
@@ -19770,16 +19770,16 @@
         <v>810</v>
       </c>
       <c r="E239" s="11" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="F239" s="11" t="s">
         <v>1317</v>
       </c>
       <c r="G239" s="11" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="H239" s="11" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="I239" s="11" t="s">
         <v>384</v>
@@ -19838,7 +19838,7 @@
         <v>1318</v>
       </c>
       <c r="H240" s="11" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="I240" s="11" t="s">
         <v>385</v>
@@ -19933,13 +19933,13 @@
         <v>1171</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="G3" s="39"/>
       <c r="H3" s="40"/>
@@ -19951,13 +19951,13 @@
         <v>1171</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="G4" s="39"/>
       <c r="H4" s="40"/>
@@ -19972,7 +19972,7 @@
         <v>405</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>627</v>
@@ -19990,7 +19990,7 @@
         <v>69</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>628</v>
@@ -20005,7 +20005,7 @@
         <v>15</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>882</v>
@@ -20041,7 +20041,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>880</v>
@@ -20059,13 +20059,13 @@
         <v>1175</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="G10" s="40"/>
       <c r="H10" s="40"/>
@@ -20152,7 +20152,7 @@
         <v>423</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>443</v>
@@ -20167,10 +20167,10 @@
         <v>435</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D17" s="46" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -20178,13 +20178,13 @@
         <v>110</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D18" s="46" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -20195,10 +20195,10 @@
         <v>695</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D19" s="46" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -20209,10 +20209,10 @@
         <v>696</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -20223,10 +20223,10 @@
         <v>697</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D21" s="46" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -20237,10 +20237,10 @@
         <v>744</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D22" s="51" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -20248,13 +20248,13 @@
         <v>110</v>
       </c>
       <c r="B23" s="50" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -20265,10 +20265,10 @@
         <v>745</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D24" s="51" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -20279,10 +20279,10 @@
         <v>746</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -20293,10 +20293,10 @@
         <v>747</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D26" s="51" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -20307,10 +20307,10 @@
         <v>403</v>
       </c>
       <c r="C27" s="11" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D27" s="12" t="s">
         <v>1606</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>1608</v>
       </c>
       <c r="F27" s="40"/>
     </row>
@@ -20320,10 +20320,10 @@
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="11" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D28" s="12" t="s">
         <v>1607</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>1609</v>
       </c>
       <c r="F28" s="40"/>
     </row>
@@ -20626,7 +20626,7 @@
         <v>567</v>
       </c>
       <c r="D46" s="46" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -20640,7 +20640,7 @@
         <v>569</v>
       </c>
       <c r="D47" s="46" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -20654,7 +20654,7 @@
         <v>571</v>
       </c>
       <c r="D48" s="46" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -20665,10 +20665,10 @@
         <v>437</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -20679,7 +20679,7 @@
         <v>438</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="D50" s="46" t="s">
         <v>448</v>
@@ -20693,7 +20693,7 @@
         <v>439</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="D51" s="46" t="s">
         <v>449</v>
@@ -20710,7 +20710,7 @@
         <v>500</v>
       </c>
       <c r="D52" s="53" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -20724,7 +20724,7 @@
         <v>630</v>
       </c>
       <c r="D53" s="55" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -20738,7 +20738,7 @@
         <v>631</v>
       </c>
       <c r="D54" s="55" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -20752,7 +20752,7 @@
         <v>632</v>
       </c>
       <c r="D55" s="55" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -20780,7 +20780,7 @@
         <v>1350</v>
       </c>
       <c r="D57" s="46" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
     </row>
   </sheetData>
@@ -20829,7 +20829,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="60" t="s">
-        <v>1369</v>
+        <v>1805</v>
       </c>
       <c r="C2" s="60" t="s">
         <v>459</v>
@@ -20850,7 +20850,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="60" t="s">
-        <v>1370</v>
+        <v>1806</v>
       </c>
       <c r="C3" s="60" t="s">
         <v>463</v>
@@ -20871,7 +20871,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="C4" s="60" t="s">
         <v>1365</v>
@@ -20976,7 +20976,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="60" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="C9" s="60" t="s">
         <v>1364</v>
@@ -21039,7 +21039,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="C12" s="59" t="s">
         <v>1351</v>

--- a/STEPS_data_analysis/data_input/ISO_input_matrix.xlsx
+++ b/STEPS_data_analysis/data_input/ISO_input_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasmalla/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF25AC27-C71A-5F4D-9100-398BCED22291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E724A3-5BD7-0243-B534-6B642759CFFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="400" yWindow="600" windowWidth="24520" windowHeight="15220" activeTab="2" xr2:uid="{56236E1D-2702-4F2C-A185-C8269303025C}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4056" uniqueCount="1807">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4061" uniqueCount="1812">
   <si>
     <t>Section</t>
   </si>
@@ -6383,6 +6383,21 @@
   </si>
   <si>
     <t>Women</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>étape</t>
+  </si>
+  <si>
+    <t>مرحلة</t>
+  </si>
+  <si>
+    <t>etapa</t>
+  </si>
+  <si>
+    <t>этап</t>
   </si>
 </sst>
 </file>
@@ -21077,20 +21092,29 @@
       <c r="G13" s="59"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="59" t="str">
-        <f t="shared" ref="A14:A42" si="0">IF(B14="","",A13+1)</f>
-        <v/>
-      </c>
-      <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
+      <c r="A14" s="59">
+        <v>13</v>
+      </c>
+      <c r="B14" s="59" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C14" s="59" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D14" s="62" t="s">
+        <v>1809</v>
+      </c>
+      <c r="E14" s="59" t="s">
+        <v>1810</v>
+      </c>
+      <c r="F14" s="59" t="s">
+        <v>1811</v>
+      </c>
       <c r="G14" s="59"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="59" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A14:A42" si="0">IF(B15="","",A14+1)</f>
         <v/>
       </c>
       <c r="B15" s="59"/>

--- a/STEPS_data_analysis/data_input/ISO_input_matrix.xlsx
+++ b/STEPS_data_analysis/data_input/ISO_input_matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\R\GitHub current\data_input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8AE740A-D77E-4520-AD20-1AD825D39E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2DB618-1F92-439B-982E-BC0B2227A2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29925" yWindow="90" windowWidth="21555" windowHeight="15480" activeTab="1" xr2:uid="{56236E1D-2702-4F2C-A185-C8269303025C}"/>
+    <workbookView xWindow="2835" yWindow="75" windowWidth="25185" windowHeight="15480" xr2:uid="{56236E1D-2702-4F2C-A185-C8269303025C}"/>
   </bookViews>
   <sheets>
     <sheet name="indicators" sheetId="1" r:id="rId1"/>
@@ -5023,9 +5023,6 @@
     <t>(t1==1 &amp; t2==1) | (t12==1 &amp; t13==1)</t>
   </si>
   <si>
-    <t>(t1==1&amp;t2==1)|(t13==1&amp;t12==1); (t1==1&amp;t2==2)|(t12==1&amp;t13==2); t1==2&amp;t12==2&amp;(t8==1|t15==1); t8==2&amp;t15==2</t>
-  </si>
-  <si>
     <t>t17==1</t>
   </si>
   <si>
@@ -6372,6 +6369,9 @@
                                 labels = c('Men 15 - 44','Men 45 - 69','Women 15 - 44','Women 45 - 69')),
                bin_age = case_when(age&gt;=18 &amp; age &lt; 45 ~ 1,age&gt;=45 &amp; age &lt; 70 ~ 2),
                bin_age = factor(bin_age,levels = 1:2, labels = c('18-44','45-69')))</t>
+  </si>
+  <si>
+    <t>(t1==1&amp;t2==1)|(t13==1&amp;t12==1);((is.na(t2) | t2!=1) &amp; (is.na(t13) | t13 != 1) &amp; ((t1==1 &amp; t2==2) | (t12 ==1 &amp; t13==2)));t1==2&amp;t12==2&amp;(t8==1|t15==1);t8==2&amp;t15==2</t>
   </si>
 </sst>
 </file>
@@ -7215,10 +7215,10 @@
         <v>372</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>1429</v>
@@ -7253,7 +7253,7 @@
         <v>373</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>315</v>
@@ -7297,7 +7297,7 @@
         <v>374</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>316</v>
@@ -7379,7 +7379,7 @@
         <v>376</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>317</v>
@@ -7431,7 +7431,7 @@
         <v>377</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>318</v>
@@ -7481,7 +7481,7 @@
         <v>1435</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>1434</v>
@@ -7601,7 +7601,7 @@
         <v>78</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>321</v>
@@ -7610,7 +7610,7 @@
         <v>1438</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>1368</v>
@@ -7666,10 +7666,10 @@
         <v>1166</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>322</v>
@@ -7678,10 +7678,10 @@
         <v>1439</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>379</v>
@@ -7749,7 +7749,7 @@
         <v>1440</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>1445</v>
@@ -7798,10 +7798,10 @@
         <v>67</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>379</v>
@@ -7851,7 +7851,7 @@
         <v>395</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>324</v>
@@ -7860,10 +7860,10 @@
         <v>68</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>379</v>
@@ -7910,10 +7910,10 @@
         <v>1441</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>379</v>
@@ -7965,10 +7965,10 @@
         <v>1441</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="I17" s="11" t="s">
         <v>379</v>
@@ -8015,10 +8015,10 @@
         <v>1442</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>379</v>
@@ -8069,10 +8069,10 @@
         <v>1443</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="I19" s="11" t="s">
         <v>379</v>
@@ -8123,10 +8123,10 @@
         <v>1444</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>379</v>
@@ -8179,7 +8179,7 @@
         <v>1447</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="H21" s="11" t="s">
         <v>1364</v>
@@ -8241,7 +8241,7 @@
         <v>492</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>1365</v>
@@ -8277,7 +8277,7 @@
         <v>85</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>348</v>
@@ -8286,7 +8286,7 @@
         <v>1448</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H23" s="11" t="s">
         <v>1366</v>
@@ -8322,7 +8322,7 @@
         <v>86</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>327</v>
@@ -8331,7 +8331,7 @@
         <v>1449</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="H24" s="11" t="s">
         <v>1367</v>
@@ -8367,7 +8367,7 @@
         <v>87</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>328</v>
@@ -8376,7 +8376,7 @@
         <v>69</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>1428</v>
@@ -8421,7 +8421,7 @@
         <v>1450</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H26" s="11" t="s">
         <v>1368</v>
@@ -8483,7 +8483,7 @@
         <v>1451</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="H27" s="11" t="s">
         <v>1369</v>
@@ -8492,7 +8492,7 @@
         <v>379</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>722</v>
@@ -8536,7 +8536,7 @@
         <v>90</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>331</v>
@@ -8545,7 +8545,7 @@
         <v>1452</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="H28" s="11" t="s">
         <v>1370</v>
@@ -8604,7 +8604,7 @@
         <v>91</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>332</v>
@@ -8613,7 +8613,7 @@
         <v>1453</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="H29" s="11" t="s">
         <v>1371</v>
@@ -8669,7 +8669,7 @@
         <v>92</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>333</v>
@@ -8678,7 +8678,7 @@
         <v>1454</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="H30" s="11" t="s">
         <v>1372</v>
@@ -8687,7 +8687,7 @@
         <v>379</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>720</v>
@@ -8714,7 +8714,7 @@
         <v>93</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>333</v>
@@ -8723,7 +8723,7 @@
         <v>1454</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>1373</v>
@@ -8768,10 +8768,10 @@
         <v>1455</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>379</v>
@@ -8780,7 +8780,7 @@
         <v>41</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="M32" s="11" t="s">
         <v>66</v>
@@ -8813,10 +8813,10 @@
         <v>1456</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="I33" s="11" t="s">
         <v>379</v>
@@ -8825,7 +8825,7 @@
         <v>70</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="M33" s="11" t="s">
         <v>66</v>
@@ -8866,7 +8866,7 @@
         <v>95</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>335</v>
@@ -8875,7 +8875,7 @@
         <v>1457</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="H34" s="11" t="s">
         <v>1374</v>
@@ -8911,7 +8911,7 @@
         <v>96</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>335</v>
@@ -8920,7 +8920,7 @@
         <v>1458</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="H35" s="11" t="s">
         <v>1375</v>
@@ -8956,16 +8956,16 @@
         <v>746</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>506</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>1459</v>
+        <v>1803</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="H36" s="11" t="s">
         <v>1376</v>
@@ -9027,10 +9027,10 @@
         <v>336</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H37" s="11" t="s">
         <v>1377</v>
@@ -9089,10 +9089,10 @@
         <v>337</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="H38" s="11" t="s">
         <v>1378</v>
@@ -9151,10 +9151,10 @@
         <v>338</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="H39" s="11" t="s">
         <v>1379</v>
@@ -9199,7 +9199,7 @@
         <v>831</v>
       </c>
       <c r="X39" s="25" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="40" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9219,10 +9219,10 @@
         <v>339</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="H40" s="11" t="s">
         <v>1380</v>
@@ -9231,10 +9231,10 @@
         <v>379</v>
       </c>
       <c r="J40" s="11" t="s">
+        <v>1545</v>
+      </c>
+      <c r="K40" s="11" t="s">
         <v>1546</v>
-      </c>
-      <c r="K40" s="11" t="s">
-        <v>1547</v>
       </c>
       <c r="M40" s="11" t="s">
         <v>66</v>
@@ -9264,10 +9264,10 @@
         <v>340</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="H41" s="11" t="s">
         <v>1381</v>
@@ -9308,10 +9308,10 @@
         <v>341</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="H42" s="11" t="s">
         <v>1382</v>
@@ -9353,10 +9353,10 @@
         <v>342</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="H43" s="11" t="s">
         <v>1383</v>
@@ -9395,7 +9395,7 @@
         <v>831</v>
       </c>
       <c r="X43" s="25" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="44" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9406,7 +9406,7 @@
         <v>1170</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>571</v>
@@ -9451,7 +9451,7 @@
         <v>1170</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>571</v>
@@ -9496,7 +9496,7 @@
         <v>1170</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>571</v>
@@ -9553,7 +9553,7 @@
         <v>1204</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="H47" s="11" t="s">
         <v>1446</v>
@@ -9598,7 +9598,7 @@
         <v>1205</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="H48" s="11" t="s">
         <v>1446</v>
@@ -9643,7 +9643,7 @@
         <v>1206</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="H49" s="11" t="s">
         <v>1446</v>
@@ -9685,13 +9685,13 @@
         <v>343</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="I50" s="11" t="s">
         <v>379</v>
@@ -9730,10 +9730,10 @@
         <v>770</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="H51" s="11" t="s">
         <v>1384</v>
@@ -9742,7 +9742,7 @@
         <v>379</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>59</v>
@@ -9801,7 +9801,7 @@
         <v>410</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="H52" s="11" t="s">
         <v>1384</v>
@@ -9850,10 +9850,10 @@
         <v>1311</v>
       </c>
       <c r="G53" s="11" t="s">
+        <v>1699</v>
+      </c>
+      <c r="H53" s="11" t="s">
         <v>1700</v>
-      </c>
-      <c r="H53" s="11" t="s">
-        <v>1701</v>
       </c>
       <c r="I53" s="11" t="s">
         <v>379</v>
@@ -9889,7 +9889,7 @@
         <v>831</v>
       </c>
       <c r="X53" s="25" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="54" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9912,10 +9912,10 @@
         <v>76</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="I54" s="11" t="s">
         <v>379</v>
@@ -9953,13 +9953,13 @@
         <v>773</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="I55" s="11" t="s">
         <v>379</v>
@@ -10003,7 +10003,7 @@
         <v>1207</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="I56" s="11" t="s">
         <v>379</v>
@@ -10110,7 +10110,7 @@
         <v>845</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H58" s="11" t="s">
         <v>846</v>
@@ -10163,10 +10163,10 @@
         <v>852</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="H59" s="11" t="s">
         <v>1385</v>
@@ -10217,10 +10217,10 @@
         <v>856</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H60" s="11" t="s">
         <v>1386</v>
@@ -10271,10 +10271,10 @@
         <v>860</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="H61" s="11" t="s">
         <v>1387</v>
@@ -10325,10 +10325,10 @@
         <v>863</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="H62" s="11" t="s">
         <v>1388</v>
@@ -10803,10 +10803,10 @@
         <v>351</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="H70" s="11" t="s">
         <v>1391</v>
@@ -10868,10 +10868,10 @@
         <v>352</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="H71" s="11" t="s">
         <v>1392</v>
@@ -10927,10 +10927,10 @@
         <v>353</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="G72" s="11" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="H72" s="11" t="s">
         <v>1393</v>
@@ -10992,10 +10992,10 @@
         <v>354</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H73" s="11" t="s">
         <v>1394</v>
@@ -11033,10 +11033,10 @@
         <v>354</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H74" s="11" t="s">
         <v>1394</v>
@@ -11077,10 +11077,10 @@
         <v>355</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="H75" s="11" t="s">
         <v>1395</v>
@@ -11121,10 +11121,10 @@
         <v>356</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="H76" s="11" t="s">
         <v>1396</v>
@@ -11162,10 +11162,10 @@
         <v>357</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H77" s="11" t="s">
         <v>1397</v>
@@ -11203,10 +11203,10 @@
         <v>357</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="H78" s="11" t="s">
         <v>1398</v>
@@ -11244,10 +11244,10 @@
         <v>357</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="G79" s="11" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="H79" s="11" t="s">
         <v>1399</v>
@@ -11285,10 +11285,10 @@
         <v>357</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="H80" s="11" t="s">
         <v>1400</v>
@@ -11326,10 +11326,10 @@
         <v>357</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="H81" s="11" t="s">
         <v>1401</v>
@@ -11367,10 +11367,10 @@
         <v>357</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="G82" s="11" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="H82" s="11" t="s">
         <v>1402</v>
@@ -11869,7 +11869,7 @@
         <v>580</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F93" s="11" t="s">
         <v>1221</v>
@@ -11878,7 +11878,7 @@
         <v>1222</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="I93" s="11" t="s">
         <v>379</v>
@@ -11896,7 +11896,7 @@
         <v>6</v>
       </c>
       <c r="P93" s="11" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="Q93" s="11">
         <v>1</v>
@@ -11937,7 +11937,7 @@
         <v>581</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F94" s="11" t="s">
         <v>1223</v>
@@ -11946,7 +11946,7 @@
         <v>1224</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="I94" s="11" t="s">
         <v>379</v>
@@ -11982,7 +11982,7 @@
         <v>160</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F95" s="11" t="s">
         <v>273</v>
@@ -11991,7 +11991,7 @@
         <v>1222</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="I95" s="11" t="s">
         <v>379</v>
@@ -12027,7 +12027,7 @@
         <v>161</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F96" s="11" t="s">
         <v>273</v>
@@ -12036,7 +12036,7 @@
         <v>1222</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="I96" s="11" t="s">
         <v>379</v>
@@ -12089,7 +12089,7 @@
         <v>162</v>
       </c>
       <c r="E97" s="11" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F97" s="11" t="s">
         <v>269</v>
@@ -12098,7 +12098,7 @@
         <v>1222</v>
       </c>
       <c r="H97" s="11" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="I97" s="11" t="s">
         <v>379</v>
@@ -12134,7 +12134,7 @@
         <v>162</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F98" s="11" t="s">
         <v>197</v>
@@ -12143,7 +12143,7 @@
         <v>1222</v>
       </c>
       <c r="H98" s="11" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="I98" s="11" t="s">
         <v>379</v>
@@ -12179,7 +12179,7 @@
         <v>162</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F99" s="11" t="s">
         <v>196</v>
@@ -12188,7 +12188,7 @@
         <v>1222</v>
       </c>
       <c r="H99" s="11" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="I99" s="11" t="s">
         <v>379</v>
@@ -12224,7 +12224,7 @@
         <v>166</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F100" s="11" t="s">
         <v>269</v>
@@ -12233,7 +12233,7 @@
         <v>1222</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="I100" s="11" t="s">
         <v>379</v>
@@ -12269,7 +12269,7 @@
         <v>166</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F101" s="11" t="s">
         <v>197</v>
@@ -12278,7 +12278,7 @@
         <v>1222</v>
       </c>
       <c r="H101" s="11" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="I101" s="11" t="s">
         <v>379</v>
@@ -12314,7 +12314,7 @@
         <v>166</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F102" s="11" t="s">
         <v>196</v>
@@ -12323,7 +12323,7 @@
         <v>1222</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="I102" s="11" t="s">
         <v>379</v>
@@ -12359,16 +12359,16 @@
         <v>582</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="G103" s="11" t="s">
         <v>1222</v>
       </c>
       <c r="H103" s="11" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="I103" s="11" t="s">
         <v>379</v>
@@ -12421,16 +12421,16 @@
         <v>582</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F104" s="11" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="G104" s="11" t="s">
         <v>1222</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="I104" s="11" t="s">
         <v>379</v>
@@ -12465,16 +12465,16 @@
         <v>582</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="G105" s="11" t="s">
         <v>1222</v>
       </c>
       <c r="H105" s="11" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="I105" s="11" t="s">
         <v>379</v>
@@ -12533,7 +12533,7 @@
         <v>171</v>
       </c>
       <c r="E106" s="11" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F106" s="11" t="s">
         <v>270</v>
@@ -12542,7 +12542,7 @@
         <v>1224</v>
       </c>
       <c r="H106" s="11" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="I106" s="11" t="s">
         <v>379</v>
@@ -12577,16 +12577,16 @@
         <v>583</v>
       </c>
       <c r="E107" s="11" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="G107" s="11" t="s">
         <v>1222</v>
       </c>
       <c r="H107" s="11" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="I107" s="11" t="s">
         <v>379</v>
@@ -12654,7 +12654,7 @@
         <v>1225</v>
       </c>
       <c r="H108" s="11" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="I108" s="11" t="s">
         <v>379</v>
@@ -12704,16 +12704,16 @@
         <v>206</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="E109" s="11" t="s">
         <v>880</v>
       </c>
       <c r="F109" s="11" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="G109" s="11" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="H109" s="11" t="s">
         <v>1403</v>
@@ -12754,10 +12754,10 @@
         <v>358</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="G110" s="11" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="H110" s="11" t="s">
         <v>1404</v>
@@ -12789,19 +12789,19 @@
         <v>1172</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="E111" s="11" t="s">
         <v>359</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="G111" s="11" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="H111" s="11" t="s">
         <v>1405</v>
@@ -12833,19 +12833,19 @@
         <v>1172</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="E112" s="11" t="s">
         <v>359</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="G112" s="11" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="H112" s="11" t="s">
         <v>1406</v>
@@ -12880,16 +12880,16 @@
         <v>222</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="E113" s="11" t="s">
         <v>884</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="G113" s="11" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="H113" s="11" t="s">
         <v>1407</v>
@@ -12928,7 +12928,7 @@
         <v>1073</v>
       </c>
       <c r="X113" s="25" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="114" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12948,10 +12948,10 @@
         <v>360</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G114" s="11" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="H114" s="11" t="s">
         <v>1408</v>
@@ -12992,10 +12992,10 @@
         <v>360</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="G115" s="11" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="H115" s="11" t="s">
         <v>1409</v>
@@ -13027,19 +13027,19 @@
         <v>1173</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="E116" s="11" t="s">
         <v>361</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="G116" s="11" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H116" s="11" t="s">
         <v>1410</v>
@@ -13071,19 +13071,19 @@
         <v>1173</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="E117" s="11" t="s">
         <v>361</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="G117" s="11" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H117" s="11" t="s">
         <v>1411</v>
@@ -13118,16 +13118,16 @@
         <v>223</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="E118" s="11" t="s">
         <v>879</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="G118" s="11" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H118" s="11" t="s">
         <v>1412</v>
@@ -13168,10 +13168,10 @@
         <v>362</v>
       </c>
       <c r="F119" s="11" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="G119" s="11" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H119" s="11" t="s">
         <v>1413</v>
@@ -13203,19 +13203,19 @@
         <v>1174</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="E120" s="11" t="s">
         <v>363</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="G120" s="11" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H120" s="11" t="s">
         <v>1414</v>
@@ -13247,19 +13247,19 @@
         <v>1174</v>
       </c>
       <c r="C121" s="36" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="E121" s="36" t="s">
         <v>363</v>
       </c>
       <c r="F121" s="11" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="G121" s="11" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H121" s="11" t="s">
         <v>1415</v>
@@ -13300,10 +13300,10 @@
         <v>364</v>
       </c>
       <c r="F122" s="11" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="G122" s="11" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="H122" s="11" t="s">
         <v>1416</v>
@@ -13362,10 +13362,10 @@
         <v>525</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="G123" s="11" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="H123" s="11" t="s">
         <v>1417</v>
@@ -13406,10 +13406,10 @@
         <v>525</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="G124" s="11" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H124" s="11" t="s">
         <v>1418</v>
@@ -13450,10 +13450,10 @@
         <v>1315</v>
       </c>
       <c r="F125" s="11" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="G125" s="11" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H125" s="11" t="s">
         <v>1419</v>
@@ -13512,10 +13512,10 @@
         <v>1315</v>
       </c>
       <c r="F126" s="11" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="G126" s="11" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H126" s="11" t="s">
         <v>1420</v>
@@ -13574,10 +13574,10 @@
         <v>1315</v>
       </c>
       <c r="F127" s="11" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="G127" s="11" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H127" s="11" t="s">
         <v>1421</v>
@@ -13636,10 +13636,10 @@
         <v>1315</v>
       </c>
       <c r="F128" s="11" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="G128" s="11" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="H128" s="11" t="s">
         <v>1422</v>
@@ -13698,10 +13698,10 @@
         <v>1315</v>
       </c>
       <c r="F129" s="11" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="G129" s="11" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="H129" s="11" t="s">
         <v>1423</v>
@@ -13760,10 +13760,10 @@
         <v>1315</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="G130" s="11" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="H130" s="11" t="s">
         <v>1424</v>
@@ -13822,10 +13822,10 @@
         <v>1315</v>
       </c>
       <c r="F131" s="11" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="G131" s="11" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="H131" s="11" t="s">
         <v>1425</v>
@@ -13941,7 +13941,7 @@
         <v>1157</v>
       </c>
       <c r="C133" s="16" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D133" s="16" t="s">
         <v>530</v>
@@ -13953,7 +13953,7 @@
         <v>1227</v>
       </c>
       <c r="G133" s="16" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H133" s="16" t="s">
         <v>1427</v>
@@ -13996,10 +13996,10 @@
         <v>887</v>
       </c>
       <c r="D134" s="16" t="s">
+        <v>1642</v>
+      </c>
+      <c r="E134" s="16" t="s">
         <v>1643</v>
-      </c>
-      <c r="E134" s="16" t="s">
-        <v>1644</v>
       </c>
       <c r="F134" s="16" t="s">
         <v>888</v>
@@ -14053,13 +14053,13 @@
         <v>892</v>
       </c>
       <c r="E135" s="16" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="F135" s="16" t="s">
         <v>1228</v>
       </c>
       <c r="G135" s="16" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H135" s="16" t="s">
         <v>893</v>
@@ -14101,19 +14101,19 @@
         <v>1157</v>
       </c>
       <c r="C136" s="16" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="D136" s="16" t="s">
         <v>895</v>
       </c>
       <c r="E136" s="16" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="F136" s="16" t="s">
         <v>1229</v>
       </c>
       <c r="G136" s="16" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="H136" s="16" t="s">
         <v>896</v>
@@ -14155,19 +14155,19 @@
         <v>1157</v>
       </c>
       <c r="C137" s="16" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D137" s="16" t="s">
         <v>1647</v>
       </c>
-      <c r="D137" s="16" t="s">
+      <c r="E137" s="16" t="s">
         <v>1648</v>
-      </c>
-      <c r="E137" s="16" t="s">
-        <v>1649</v>
       </c>
       <c r="F137" s="16" t="s">
         <v>1230</v>
       </c>
       <c r="G137" s="16" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="H137" s="16" t="s">
         <v>898</v>
@@ -14176,7 +14176,7 @@
         <v>379</v>
       </c>
       <c r="J137" s="16" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="K137" s="16" t="s">
         <v>1058</v>
@@ -14215,13 +14215,13 @@
         <v>900</v>
       </c>
       <c r="E138" s="16" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="F138" s="16" t="s">
         <v>1231</v>
       </c>
       <c r="G138" s="16" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="H138" s="16" t="s">
         <v>901</v>
@@ -14269,22 +14269,22 @@
         <v>904</v>
       </c>
       <c r="E139" s="16" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="F139" s="16" t="s">
         <v>1232</v>
       </c>
       <c r="G139" s="16" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="H139" s="16" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="I139" s="16" t="s">
         <v>379</v>
       </c>
       <c r="J139" s="16" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="K139" s="16" t="s">
         <v>1011</v>
@@ -14320,25 +14320,25 @@
         <v>905</v>
       </c>
       <c r="D140" s="16" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E140" s="16" t="s">
         <v>1654</v>
-      </c>
-      <c r="E140" s="16" t="s">
-        <v>1655</v>
       </c>
       <c r="F140" s="16" t="s">
         <v>1233</v>
       </c>
       <c r="G140" s="16" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="H140" s="16" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="I140" s="16" t="s">
         <v>379</v>
       </c>
       <c r="J140" s="16" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="K140" s="16" t="s">
         <v>1011</v>
@@ -14371,28 +14371,28 @@
         <v>1157</v>
       </c>
       <c r="C141" s="16" t="s">
+        <v>1656</v>
+      </c>
+      <c r="D141" s="16" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E141" s="16" t="s">
         <v>1657</v>
       </c>
-      <c r="D141" s="16" t="s">
-        <v>1654</v>
-      </c>
-      <c r="E141" s="16" t="s">
+      <c r="F141" s="16" t="s">
         <v>1658</v>
       </c>
-      <c r="F141" s="16" t="s">
-        <v>1659</v>
-      </c>
       <c r="G141" s="16" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="H141" s="16" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="I141" s="16" t="s">
         <v>379</v>
       </c>
       <c r="J141" s="16" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="K141" s="16"/>
       <c r="L141" s="16"/>
@@ -14417,31 +14417,31 @@
         <v>1157</v>
       </c>
       <c r="C142" s="16" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D142" s="16" t="s">
         <v>1661</v>
       </c>
-      <c r="D142" s="16" t="s">
+      <c r="E142" s="16" t="s">
         <v>1662</v>
       </c>
-      <c r="E142" s="16" t="s">
-        <v>1663</v>
-      </c>
       <c r="F142" s="16" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="G142" s="16" t="s">
+        <v>1768</v>
+      </c>
+      <c r="H142" s="16" t="s">
         <v>1769</v>
-      </c>
-      <c r="H142" s="16" t="s">
-        <v>1770</v>
       </c>
       <c r="I142" s="16" t="s">
         <v>379</v>
       </c>
       <c r="J142" s="16" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="K142" s="16" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="L142" s="16"/>
       <c r="M142" s="16" t="s">
@@ -14474,16 +14474,16 @@
         <v>906</v>
       </c>
       <c r="D143" s="16" t="s">
+        <v>1664</v>
+      </c>
+      <c r="E143" s="16" t="s">
         <v>1665</v>
       </c>
-      <c r="E143" s="16" t="s">
-        <v>1666</v>
-      </c>
       <c r="F143" s="16" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="G143" s="16" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="H143" s="16" t="s">
         <v>907</v>
@@ -14492,10 +14492,10 @@
         <v>379</v>
       </c>
       <c r="J143" s="16" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="K143" s="16" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="L143" s="16"/>
       <c r="M143" s="16" t="s">
@@ -14525,7 +14525,7 @@
         <v>1177</v>
       </c>
       <c r="C144" s="17" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="D144" s="17" t="s">
         <v>599</v>
@@ -14571,7 +14571,7 @@
         <v>1177</v>
       </c>
       <c r="C145" s="17" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="D145" s="17" t="s">
         <v>603</v>
@@ -14617,7 +14617,7 @@
         <v>1177</v>
       </c>
       <c r="C146" s="17" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="D146" s="17" t="s">
         <v>606</v>
@@ -14665,7 +14665,7 @@
         <v>1177</v>
       </c>
       <c r="C147" s="17" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="D147" s="17" t="s">
         <v>799</v>
@@ -14713,7 +14713,7 @@
         <v>1177</v>
       </c>
       <c r="C148" s="17" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="D148" s="17" t="s">
         <v>800</v>
@@ -14853,7 +14853,7 @@
         <v>1177</v>
       </c>
       <c r="C151" s="17" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="D151" s="17" t="s">
         <v>620</v>
@@ -14899,7 +14899,7 @@
         <v>1177</v>
       </c>
       <c r="C152" s="17" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="D152" s="17" t="s">
         <v>622</v>
@@ -14994,7 +14994,7 @@
         <v>908</v>
       </c>
       <c r="D154" s="28" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="E154" s="28" t="s">
         <v>1021</v>
@@ -15003,7 +15003,7 @@
         <v>1245</v>
       </c>
       <c r="G154" s="28" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H154" s="28" t="s">
         <v>909</v>
@@ -15172,16 +15172,16 @@
         <v>917</v>
       </c>
       <c r="D157" s="28" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="E157" s="28" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="F157" s="28" t="s">
         <v>1247</v>
       </c>
       <c r="G157" s="28" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="H157" s="28" t="s">
         <v>918</v>
@@ -15190,7 +15190,7 @@
         <v>379</v>
       </c>
       <c r="J157" s="28" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K157" s="28"/>
       <c r="L157" s="28"/>
@@ -15236,7 +15236,7 @@
         <v>919</v>
       </c>
       <c r="D158" s="28" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="E158" s="28" t="s">
         <v>1023</v>
@@ -15245,7 +15245,7 @@
         <v>1248</v>
       </c>
       <c r="G158" s="28" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="H158" s="28" t="s">
         <v>628</v>
@@ -15254,7 +15254,7 @@
         <v>379</v>
       </c>
       <c r="J158" s="28" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K158" s="28" t="s">
         <v>999</v>
@@ -15290,7 +15290,7 @@
         <v>920</v>
       </c>
       <c r="D159" s="28" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="E159" s="28" t="s">
         <v>1024</v>
@@ -15344,7 +15344,7 @@
         <v>1029</v>
       </c>
       <c r="D160" s="28" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="E160" s="28" t="s">
         <v>1025</v>
@@ -15362,7 +15362,7 @@
         <v>379</v>
       </c>
       <c r="J160" s="28" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="K160" s="28" t="s">
         <v>926</v>
@@ -15398,7 +15398,7 @@
         <v>1030</v>
       </c>
       <c r="D161" s="28" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="E161" s="28" t="s">
         <v>1026</v>
@@ -15407,7 +15407,7 @@
         <v>1251</v>
       </c>
       <c r="G161" s="28" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="H161" s="28" t="s">
         <v>927</v>
@@ -15450,7 +15450,7 @@
         <v>1031</v>
       </c>
       <c r="D162" s="28" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="E162" s="28" t="s">
         <v>1027</v>
@@ -15459,7 +15459,7 @@
         <v>1252</v>
       </c>
       <c r="G162" s="28" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="H162" s="28" t="s">
         <v>929</v>
@@ -15502,7 +15502,7 @@
         <v>1032</v>
       </c>
       <c r="D163" s="28" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="E163" s="28" t="s">
         <v>1028</v>
@@ -15511,7 +15511,7 @@
         <v>1253</v>
       </c>
       <c r="G163" s="28" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="H163" s="28" t="s">
         <v>931</v>
@@ -15789,7 +15789,7 @@
         <v>1179</v>
       </c>
       <c r="C169" s="33" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="D169" s="33" t="s">
         <v>933</v>
@@ -15841,7 +15841,7 @@
         <v>1179</v>
       </c>
       <c r="C170" s="33" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="D170" s="33" t="s">
         <v>936</v>
@@ -15893,7 +15893,7 @@
         <v>1179</v>
       </c>
       <c r="C171" s="33" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="D171" s="33" t="s">
         <v>939</v>
@@ -15945,7 +15945,7 @@
         <v>1179</v>
       </c>
       <c r="C172" s="33" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="D172" s="33" t="s">
         <v>942</v>
@@ -15997,7 +15997,7 @@
         <v>1179</v>
       </c>
       <c r="C173" s="33" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="D173" s="33" t="s">
         <v>945</v>
@@ -16049,10 +16049,10 @@
         <v>1179</v>
       </c>
       <c r="C174" s="33" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="D174" s="33" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="E174" s="33" t="s">
         <v>1040</v>
@@ -16101,7 +16101,7 @@
         <v>1180</v>
       </c>
       <c r="C175" s="32" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="D175" s="32" t="s">
         <v>950</v>
@@ -16113,7 +16113,7 @@
         <v>1272</v>
       </c>
       <c r="G175" s="32" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H175" s="32" t="s">
         <v>951</v>
@@ -16155,7 +16155,7 @@
         <v>1180</v>
       </c>
       <c r="C176" s="32" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="D176" s="32" t="s">
         <v>953</v>
@@ -16167,7 +16167,7 @@
         <v>1273</v>
       </c>
       <c r="G176" s="32" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H176" s="32" t="s">
         <v>954</v>
@@ -16221,7 +16221,7 @@
         <v>1274</v>
       </c>
       <c r="G177" s="32" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H177" s="32" t="s">
         <v>957</v>
@@ -16275,7 +16275,7 @@
         <v>1275</v>
       </c>
       <c r="G178" s="32" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="H178" s="32" t="s">
         <v>961</v>
@@ -16327,7 +16327,7 @@
         <v>1276</v>
       </c>
       <c r="G179" s="32" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="H179" s="32" t="s">
         <v>965</v>
@@ -16379,7 +16379,7 @@
         <v>1277</v>
       </c>
       <c r="G180" s="32" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="H180" s="32" t="s">
         <v>969</v>
@@ -16433,7 +16433,7 @@
         <v>1278</v>
       </c>
       <c r="G181" s="32" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="H181" s="32" t="s">
         <v>973</v>
@@ -16487,7 +16487,7 @@
         <v>1279</v>
       </c>
       <c r="G182" s="32" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="H182" s="32" t="s">
         <v>977</v>
@@ -16541,7 +16541,7 @@
         <v>1280</v>
       </c>
       <c r="G183" s="32" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H183" s="32" t="s">
         <v>981</v>
@@ -16595,7 +16595,7 @@
         <v>1281</v>
       </c>
       <c r="G184" s="32" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H184" s="32" t="s">
         <v>984</v>
@@ -16649,7 +16649,7 @@
         <v>1282</v>
       </c>
       <c r="G185" s="32" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="H185" s="32" t="s">
         <v>988</v>
@@ -16703,7 +16703,7 @@
         <v>1283</v>
       </c>
       <c r="G186" s="32" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="H186" s="32" t="s">
         <v>991</v>
@@ -16757,7 +16757,7 @@
         <v>1284</v>
       </c>
       <c r="G187" s="32" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H187" s="32" t="s">
         <v>995</v>
@@ -17969,7 +17969,7 @@
         <v>6</v>
       </c>
       <c r="P208" s="11" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="Q208" s="11">
         <v>1</v>
@@ -18329,13 +18329,13 @@
         <v>1182</v>
       </c>
       <c r="C214" s="11" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="D214" s="11" t="s">
+        <v>1588</v>
+      </c>
+      <c r="E214" s="11" t="s">
         <v>1589</v>
-      </c>
-      <c r="E214" s="11" t="s">
-        <v>1590</v>
       </c>
       <c r="F214" s="11" t="s">
         <v>633</v>
@@ -18380,7 +18380,7 @@
         <v>1073</v>
       </c>
       <c r="X214" s="25" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="215" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -18391,13 +18391,13 @@
         <v>1182</v>
       </c>
       <c r="C215" s="11" t="s">
+        <v>1592</v>
+      </c>
+      <c r="D215" s="11" t="s">
         <v>1593</v>
       </c>
-      <c r="D215" s="11" t="s">
-        <v>1594</v>
-      </c>
       <c r="E215" s="11" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="F215" s="11" t="s">
         <v>1090</v>
@@ -18412,7 +18412,7 @@
         <v>383</v>
       </c>
       <c r="J215" s="11" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="K215" s="11" t="s">
         <v>1091</v>
@@ -18442,7 +18442,7 @@
         <v>1073</v>
       </c>
       <c r="X215" s="25" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="216" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -18550,7 +18550,7 @@
         <v>370</v>
       </c>
       <c r="F218" s="11" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="G218" s="11" t="s">
         <v>1304</v>
@@ -18609,7 +18609,7 @@
         <v>370</v>
       </c>
       <c r="F219" s="11" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="G219" s="11" t="s">
         <v>1304</v>
@@ -18668,7 +18668,7 @@
         <v>1100</v>
       </c>
       <c r="F220" s="11" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="G220" s="11" t="s">
         <v>1304</v>
@@ -18733,7 +18733,7 @@
         <v>1100</v>
       </c>
       <c r="F221" s="11" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="G221" s="11" t="s">
         <v>1304</v>
@@ -18916,7 +18916,7 @@
         <v>1099</v>
       </c>
       <c r="F224" s="11" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="G224" s="11" t="s">
         <v>1306</v>
@@ -18972,7 +18972,7 @@
         <v>636</v>
       </c>
       <c r="D225" s="11" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="E225" s="11" t="s">
         <v>637</v>
@@ -19017,13 +19017,13 @@
         <v>640</v>
       </c>
       <c r="D226" s="11" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="E226" s="11" t="s">
         <v>637</v>
       </c>
       <c r="F226" s="11" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="G226" s="11" t="s">
         <v>641</v>
@@ -19079,13 +19079,13 @@
         <v>643</v>
       </c>
       <c r="D227" s="11" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="E227" s="11" t="s">
         <v>637</v>
       </c>
       <c r="F227" s="11" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="G227" s="11" t="s">
         <v>638</v>
@@ -19138,13 +19138,13 @@
         <v>646</v>
       </c>
       <c r="D228" s="11" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="E228" s="11" t="s">
         <v>637</v>
       </c>
       <c r="F228" s="11" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="G228" s="11" t="s">
         <v>638</v>
@@ -19197,7 +19197,7 @@
         <v>648</v>
       </c>
       <c r="D229" s="11" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="E229" s="11" t="s">
         <v>649</v>
@@ -19242,13 +19242,13 @@
         <v>652</v>
       </c>
       <c r="D230" s="11" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="E230" s="11" t="s">
         <v>649</v>
       </c>
       <c r="F230" s="11" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="G230" s="11" t="s">
         <v>653</v>
@@ -19304,13 +19304,13 @@
         <v>655</v>
       </c>
       <c r="D231" s="11" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="E231" s="11" t="s">
         <v>649</v>
       </c>
       <c r="F231" s="11" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="G231" s="11" t="s">
         <v>650</v>
@@ -19363,13 +19363,13 @@
         <v>657</v>
       </c>
       <c r="D232" s="11" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="E232" s="11" t="s">
         <v>649</v>
       </c>
       <c r="F232" s="11" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="G232" s="11" t="s">
         <v>650</v>
@@ -19422,7 +19422,7 @@
         <v>659</v>
       </c>
       <c r="D233" s="11" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="E233" s="11" t="s">
         <v>660</v>
@@ -19467,13 +19467,13 @@
         <v>662</v>
       </c>
       <c r="D234" s="11" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="E234" s="11" t="s">
         <v>660</v>
       </c>
       <c r="F234" s="11" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="G234" s="11" t="s">
         <v>1309</v>
@@ -19529,13 +19529,13 @@
         <v>664</v>
       </c>
       <c r="D235" s="11" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="E235" s="11" t="s">
         <v>660</v>
       </c>
       <c r="F235" s="11" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="G235" s="11" t="s">
         <v>1308</v>
@@ -19588,13 +19588,13 @@
         <v>666</v>
       </c>
       <c r="D236" s="11" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="E236" s="11" t="s">
         <v>660</v>
       </c>
       <c r="F236" s="11" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="G236" s="11" t="s">
         <v>1308</v>
@@ -19632,16 +19632,16 @@
         <v>528</v>
       </c>
       <c r="E237" s="11" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="F237" s="11" t="s">
         <v>493</v>
       </c>
       <c r="G237" s="11" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H237" s="15" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="I237" s="11" t="s">
         <v>383</v>
@@ -19694,16 +19694,16 @@
         <v>591</v>
       </c>
       <c r="E238" s="11" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="F238" s="11" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="G238" s="11" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H238" s="15" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="I238" s="11" t="s">
         <v>383</v>
@@ -19718,7 +19718,7 @@
         <v>6</v>
       </c>
       <c r="P238" s="11" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="Q238" s="11">
         <v>1</v>
@@ -19759,13 +19759,13 @@
         <v>805</v>
       </c>
       <c r="E239" s="11" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="F239" s="11" t="s">
         <v>1310</v>
       </c>
       <c r="G239" s="11" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H239" s="11" t="s">
         <v>1416</v>
@@ -19824,10 +19824,10 @@
         <v>1312</v>
       </c>
       <c r="G240" s="11" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H240" s="11" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="I240" s="11" t="s">
         <v>384</v>
@@ -19910,7 +19910,7 @@
         <v>403</v>
       </c>
       <c r="D2" s="46" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="G2" s="39"/>
       <c r="H2" s="40"/>
@@ -19922,13 +19922,13 @@
         <v>1166</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>1673</v>
       </c>
-      <c r="C3" s="15" t="s">
-        <v>1674</v>
-      </c>
       <c r="D3" s="46" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="G3" s="39"/>
       <c r="H3" s="40"/>
@@ -19940,13 +19940,13 @@
         <v>1166</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>1371</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="G4" s="39"/>
       <c r="H4" s="40"/>
@@ -19961,7 +19961,7 @@
         <v>404</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>624</v>
@@ -19979,7 +19979,7 @@
         <v>69</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>625</v>
@@ -20048,13 +20048,13 @@
         <v>1170</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>1676</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>1677</v>
-      </c>
       <c r="D10" s="46" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="G10" s="40"/>
       <c r="H10" s="40"/>
@@ -20072,7 +20072,7 @@
         <v>408</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20141,7 +20141,7 @@
         <v>422</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>441</v>
@@ -20156,10 +20156,10 @@
         <v>434</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="D17" s="46" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20167,13 +20167,13 @@
         <v>110</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="D18" s="46" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20184,10 +20184,10 @@
         <v>691</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="D19" s="46" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20198,10 +20198,10 @@
         <v>692</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20212,10 +20212,10 @@
         <v>693</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="D21" s="46" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20226,10 +20226,10 @@
         <v>740</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="D22" s="51" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20237,13 +20237,13 @@
         <v>110</v>
       </c>
       <c r="B23" s="50" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20254,10 +20254,10 @@
         <v>741</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="D24" s="51" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20268,10 +20268,10 @@
         <v>742</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20282,10 +20282,10 @@
         <v>743</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="D26" s="51" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20296,10 +20296,10 @@
         <v>402</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="F27" s="40"/>
     </row>
@@ -20308,13 +20308,13 @@
         <v>156</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="F28" s="40"/>
     </row>
@@ -20617,7 +20617,7 @@
         <v>564</v>
       </c>
       <c r="D46" s="46" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20631,7 +20631,7 @@
         <v>566</v>
       </c>
       <c r="D47" s="46" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20645,7 +20645,7 @@
         <v>568</v>
       </c>
       <c r="D48" s="46" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20656,10 +20656,10 @@
         <v>436</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20670,7 +20670,7 @@
         <v>437</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="D50" s="46" t="s">
         <v>446</v>
@@ -20684,7 +20684,7 @@
         <v>438</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="D51" s="46" t="s">
         <v>447</v>
@@ -20701,7 +20701,7 @@
         <v>497</v>
       </c>
       <c r="D52" s="53" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20715,7 +20715,7 @@
         <v>627</v>
       </c>
       <c r="D53" s="55" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20729,7 +20729,7 @@
         <v>628</v>
       </c>
       <c r="D54" s="55" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -20743,7 +20743,7 @@
         <v>629</v>
       </c>
       <c r="D55" s="55" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -20771,7 +20771,7 @@
         <v>1342</v>
       </c>
       <c r="D57" s="46" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
     </row>
   </sheetData>
@@ -20862,7 +20862,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="C4" s="60" t="s">
         <v>1357</v>
@@ -20967,7 +20967,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="60" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="C9" s="60" t="s">
         <v>1356</v>
@@ -21030,7 +21030,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="C12" s="59" t="s">
         <v>1343</v>

--- a/STEPS_data_analysis/data_input/ISO_input_matrix.xlsx
+++ b/STEPS_data_analysis/data_input/ISO_input_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\R\GitHub current\data_input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B3CD62-2C0F-43EB-9C89-10890F170DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A615D9F7-5F0B-43E2-AD2A-941C61770682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56236E1D-2702-4F2C-A185-C8269303025C}"/>
   </bookViews>
@@ -19839,7 +19839,7 @@
         <v>484</v>
       </c>
       <c r="N207" s="46" t="s">
-        <v>6</v>
+        <v>251</v>
       </c>
       <c r="O207" s="46"/>
       <c r="P207" s="46"/>

--- a/STEPS_data_analysis/data_input/ISO_input_matrix.xlsx
+++ b/STEPS_data_analysis/data_input/ISO_input_matrix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cowanm\OneDrive - World Health Organization\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\R\most recent from Lucas\data_input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68349EC-85CB-4264-86EE-02C89CDFC5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB165DC2-8D59-4658-BE4D-DEBCD604C0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56236E1D-2702-4F2C-A185-C8269303025C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{56236E1D-2702-4F2C-A185-C8269303025C}"/>
   </bookViews>
   <sheets>
     <sheet name="indicators" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="translations" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">indicators!$A$1:$X$277</definedName>
     <definedName name="_Toc450054825" localSheetId="0">indicators!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4608" uniqueCount="2075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4618" uniqueCount="2084">
   <si>
     <t>Section</t>
   </si>
@@ -5050,9 +5051,6 @@
     <t>Mean fasting triglycerides and percentage of the population with raised fasting triglycerides (non-fasting recipients excluded)</t>
   </si>
   <si>
-    <t>1.Percentage aged 40-69 years with a 10-year CVD risk ≥ 20%, or with existing CVD**</t>
-  </si>
-  <si>
     <t>t1;t2;t5a;t5aw</t>
   </si>
   <si>
@@ -5072,9 +5070,6 @@
   </si>
   <si>
     <t>Mean age of initiation and mean duration of smoking, in years, among daily smokers (no total age group for mean duration of smoking as age influences these values)</t>
-  </si>
-  <si>
-    <t>1. Percentage with insufficient physical activity (defined as &lt; 150 minutes of moderate-intensity activity per week, or equivalent)*</t>
   </si>
   <si>
     <t>mhs1:Considered suicide</t>
@@ -5273,9 +5268,6 @@
   </si>
   <si>
     <t>h6;h7a;t1;m4a;m5a;m6a;b8</t>
-  </si>
-  <si>
-    <t>m11;m12;m8;</t>
   </si>
   <si>
     <t>m11;m12;m8;b14;b15;b10</t>
@@ -7317,6 +7309,42 @@
   </si>
   <si>
     <t>mean number of servings</t>
+  </si>
+  <si>
+    <t>1.Percentage aged 40-69 years with a 10-year CVD risk ≥ 20%, or with existing CVD††</t>
+  </si>
+  <si>
+    <t>1. Percentage with insufficient physical activity (defined as &lt; 150 minutes of moderate-intensity activity per week, or equivalent)†</t>
+  </si>
+  <si>
+    <t>Results for men aged 18–69 years (incl. 95% CI)</t>
+  </si>
+  <si>
+    <t>Résultats pour les hommes âgés de 18 à 69 ans (y compris IC à 95 %)</t>
+  </si>
+  <si>
+    <t>النتائج للرجال الذين تتراوح أعمارهم بين 18 و69 عامًا (بما في ذلك فاصل الثقة 95%)</t>
+  </si>
+  <si>
+    <t>Resultados para hombres de 18 a 69 años (incl. IC del 95 %)</t>
+  </si>
+  <si>
+    <t>Результаты для мужчин в возрасте 18–69 лет (включая 95% доверительный интервал)</t>
+  </si>
+  <si>
+    <t>Results for women aged 18–69 years (incl. 95% CI)</t>
+  </si>
+  <si>
+    <t>Résultats pour les femmes âgées de 18 à 69 ans (y compris IC à 95 %)</t>
+  </si>
+  <si>
+    <t>النتائج للنساء اللواتي تتراوح أعمارهن بين 18 و69 عامًا (بما في ذلك فاصل الثقة 95%)</t>
+  </si>
+  <si>
+    <t>Resultados para mujeres de 18 a 69 años (incl. IC del 95 %)</t>
+  </si>
+  <si>
+    <t>Результаты для женщин в возрасте 18–69 лет (включая 95% доверительный интервал)</t>
   </si>
 </sst>
 </file>
@@ -8113,34 +8141,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8545CCE-7849-4608-BA53-0CA4FD51ED56}">
   <dimension ref="A1:X277"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.125" style="18" customWidth="1"/>
-    <col min="2" max="2" width="26.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="48.875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.08203125" style="18" customWidth="1"/>
+    <col min="2" max="2" width="26.08203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="48.83203125" style="2" customWidth="1"/>
     <col min="4" max="4" width="58" style="2" customWidth="1"/>
     <col min="5" max="5" width="64" style="2" customWidth="1"/>
-    <col min="6" max="6" width="21.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="30.625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="49.875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="23.125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="7.125" style="2" customWidth="1"/>
-    <col min="14" max="15" width="10.625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="26.5" style="2" customWidth="1"/>
-    <col min="17" max="17" width="12.125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="10.625" style="2"/>
-    <col min="19" max="20" width="20.375" style="2" customWidth="1"/>
-    <col min="21" max="21" width="15.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="22.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="10.625" style="2"/>
+    <col min="6" max="6" width="21.08203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="25.08203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="30.58203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.58203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="49.83203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="23.08203125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="10.58203125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="7.08203125" style="2" customWidth="1"/>
+    <col min="14" max="15" width="10.58203125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="68.33203125" style="2" customWidth="1"/>
+    <col min="17" max="17" width="12.08203125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="10.58203125" style="2"/>
+    <col min="19" max="20" width="20.33203125" style="2" customWidth="1"/>
+    <col min="21" max="21" width="15.08203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.58203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="22.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.08203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="10.58203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="15" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="15" customFormat="1" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="51" t="s">
         <v>492</v>
       </c>
@@ -8214,7 +8242,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
         <v>385</v>
       </c>
@@ -8225,10 +8253,10 @@
         <v>367</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
       <c r="F2" s="33" t="s">
         <v>1371</v>
@@ -8264,7 +8292,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="21" t="s">
         <v>385</v>
       </c>
@@ -8275,7 +8303,7 @@
         <v>368</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>1555</v>
+        <v>1552</v>
       </c>
       <c r="E3" s="33" t="s">
         <v>310</v>
@@ -8318,7 +8346,7 @@
       <c r="W3" s="33"/>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="21" t="s">
         <v>385</v>
       </c>
@@ -8329,7 +8357,7 @@
         <v>369</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
       <c r="E4" s="33" t="s">
         <v>311</v>
@@ -8370,7 +8398,7 @@
       <c r="W4" s="33"/>
       <c r="X4" s="33"/>
     </row>
-    <row r="5" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
         <v>385</v>
       </c>
@@ -8422,7 +8450,7 @@
       <c r="W5" s="33"/>
       <c r="X5" s="33"/>
     </row>
-    <row r="6" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="21" t="s">
         <v>385</v>
       </c>
@@ -8433,7 +8461,7 @@
         <v>371</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>1557</v>
+        <v>1554</v>
       </c>
       <c r="E6" s="33" t="s">
         <v>312</v>
@@ -8474,7 +8502,7 @@
       <c r="W6" s="33"/>
       <c r="X6" s="33"/>
     </row>
-    <row r="7" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
         <v>385</v>
       </c>
@@ -8485,7 +8513,7 @@
         <v>372</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>1558</v>
+        <v>1555</v>
       </c>
       <c r="E7" s="33" t="s">
         <v>313</v>
@@ -8526,7 +8554,7 @@
       <c r="W7" s="33"/>
       <c r="X7" s="33"/>
     </row>
-    <row r="8" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
         <v>385</v>
       </c>
@@ -8546,7 +8574,7 @@
         <v>1377</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>1732</v>
+        <v>1729</v>
       </c>
       <c r="H8" s="33" t="s">
         <v>1376</v>
@@ -8580,7 +8608,7 @@
       <c r="W8" s="33"/>
       <c r="X8" s="33"/>
     </row>
-    <row r="9" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="21" t="s">
         <v>385</v>
       </c>
@@ -8634,7 +8662,7 @@
       <c r="W9" s="33"/>
       <c r="X9" s="33"/>
     </row>
-    <row r="10" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="21" t="s">
         <v>385</v>
       </c>
@@ -8686,7 +8714,7 @@
       <c r="W10" s="33"/>
       <c r="X10" s="33"/>
     </row>
-    <row r="11" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="21" t="s">
         <v>385</v>
       </c>
@@ -8706,7 +8734,7 @@
         <v>1380</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="H11" s="33" t="s">
         <v>1310</v>
@@ -8756,7 +8784,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="21" t="s">
         <v>385</v>
       </c>
@@ -8764,7 +8792,7 @@
         <v>1122</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="D12" s="33" t="s">
         <v>1479</v>
@@ -8776,10 +8804,10 @@
         <v>1381</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="H12" s="33" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="I12" s="33" t="s">
         <v>374</v>
@@ -8828,7 +8856,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="21" t="s">
         <v>385</v>
       </c>
@@ -8848,7 +8876,7 @@
         <v>1382</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="H13" s="33" t="s">
         <v>1387</v>
@@ -8882,7 +8910,7 @@
       <c r="W13" s="27"/>
       <c r="X13" s="27"/>
     </row>
-    <row r="14" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="21" t="s">
         <v>385</v>
       </c>
@@ -8902,10 +8930,10 @@
         <v>65</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="I14" s="33" t="s">
         <v>374</v>
@@ -8948,7 +8976,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="21" t="s">
         <v>385</v>
       </c>
@@ -8959,7 +8987,7 @@
         <v>390</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="E15" s="33" t="s">
         <v>319</v>
@@ -8968,10 +8996,10 @@
         <v>66</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
       <c r="H15" s="33" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="I15" s="33" t="s">
         <v>374</v>
@@ -9002,7 +9030,7 @@
       <c r="W15" s="27"/>
       <c r="X15" s="27"/>
     </row>
-    <row r="16" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="21" t="s">
         <v>385</v>
       </c>
@@ -9022,10 +9050,10 @@
         <v>1383</v>
       </c>
       <c r="G16" s="33" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="H16" s="33" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="I16" s="33" t="s">
         <v>374</v>
@@ -9060,7 +9088,7 @@
       <c r="W16" s="27"/>
       <c r="X16" s="27"/>
     </row>
-    <row r="17" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="21" t="s">
         <v>385</v>
       </c>
@@ -9080,10 +9108,10 @@
         <v>1383</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="H17" s="33" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="I17" s="33" t="s">
         <v>374</v>
@@ -9114,7 +9142,7 @@
       <c r="W17" s="27"/>
       <c r="X17" s="27"/>
     </row>
-    <row r="18" spans="1:24" s="16" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="16" customFormat="1" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="21" t="s">
         <v>385</v>
       </c>
@@ -9134,10 +9162,10 @@
         <v>1384</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="H18" s="33" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="I18" s="33" t="s">
         <v>374</v>
@@ -9168,7 +9196,7 @@
       <c r="W18" s="27"/>
       <c r="X18" s="27"/>
     </row>
-    <row r="19" spans="1:24" s="16" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="16" customFormat="1" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="21" t="s">
         <v>385</v>
       </c>
@@ -9188,10 +9216,10 @@
         <v>1385</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="H19" s="33" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="I19" s="33" t="s">
         <v>374</v>
@@ -9222,7 +9250,7 @@
       <c r="W19" s="27"/>
       <c r="X19" s="27"/>
     </row>
-    <row r="20" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="21" t="s">
         <v>385</v>
       </c>
@@ -9242,10 +9270,10 @@
         <v>1386</v>
       </c>
       <c r="G20" s="33" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
       <c r="H20" s="33" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="I20" s="33" t="s">
         <v>374</v>
@@ -9280,7 +9308,7 @@
       <c r="W20" s="27"/>
       <c r="X20" s="27"/>
     </row>
-    <row r="21" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="21" t="s">
         <v>385</v>
       </c>
@@ -9300,7 +9328,7 @@
         <v>1389</v>
       </c>
       <c r="G21" s="33" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="H21" s="33" t="s">
         <v>1306</v>
@@ -9346,7 +9374,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="21" t="s">
         <v>385</v>
       </c>
@@ -9366,7 +9394,7 @@
         <v>486</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="H22" s="33" t="s">
         <v>1307</v>
@@ -9400,7 +9428,7 @@
       <c r="W22" s="33"/>
       <c r="X22" s="33"/>
     </row>
-    <row r="23" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="21" t="s">
         <v>385</v>
       </c>
@@ -9420,7 +9448,7 @@
         <v>1390</v>
       </c>
       <c r="G23" s="33" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="H23" s="33" t="s">
         <v>1308</v>
@@ -9454,7 +9482,7 @@
       <c r="W23" s="33"/>
       <c r="X23" s="33"/>
     </row>
-    <row r="24" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="21" t="s">
         <v>385</v>
       </c>
@@ -9474,7 +9502,7 @@
         <v>1391</v>
       </c>
       <c r="G24" s="33" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="H24" s="33" t="s">
         <v>1309</v>
@@ -9508,7 +9536,7 @@
       <c r="W24" s="33"/>
       <c r="X24" s="33"/>
     </row>
-    <row r="25" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="21" t="s">
         <v>385</v>
       </c>
@@ -9528,7 +9556,7 @@
         <v>67</v>
       </c>
       <c r="G25" s="33" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
       <c r="H25" s="33" t="s">
         <v>1370</v>
@@ -9562,7 +9590,7 @@
       <c r="W25" s="33"/>
       <c r="X25" s="33"/>
     </row>
-    <row r="26" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="21" t="s">
         <v>385</v>
       </c>
@@ -9582,7 +9610,7 @@
         <v>1392</v>
       </c>
       <c r="G26" s="33" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="H26" s="33" t="s">
         <v>1310</v>
@@ -9628,7 +9656,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="21" t="s">
         <v>385</v>
       </c>
@@ -9648,7 +9676,7 @@
         <v>1393</v>
       </c>
       <c r="G27" s="33" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="H27" s="33" t="s">
         <v>1311</v>
@@ -9657,7 +9685,7 @@
         <v>374</v>
       </c>
       <c r="J27" s="33" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
       <c r="K27" s="33" t="s">
         <v>704</v>
@@ -9694,7 +9722,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="21" t="s">
         <v>385</v>
       </c>
@@ -9714,7 +9742,7 @@
         <v>1394</v>
       </c>
       <c r="G28" s="33" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="H28" s="33" t="s">
         <v>1312</v>
@@ -9764,7 +9792,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="21" t="s">
         <v>385</v>
       </c>
@@ -9784,7 +9812,7 @@
         <v>1395</v>
       </c>
       <c r="G29" s="33" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="H29" s="33" t="s">
         <v>1313</v>
@@ -9832,7 +9860,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="21" t="s">
         <v>385</v>
       </c>
@@ -9852,7 +9880,7 @@
         <v>1396</v>
       </c>
       <c r="G30" s="33" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="H30" s="33" t="s">
         <v>1314</v>
@@ -9886,7 +9914,7 @@
       <c r="W30" s="33"/>
       <c r="X30" s="33"/>
     </row>
-    <row r="31" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="21" t="s">
         <v>385</v>
       </c>
@@ -9906,7 +9934,7 @@
         <v>1396</v>
       </c>
       <c r="G31" s="33" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="H31" s="33" t="s">
         <v>1315</v>
@@ -9940,7 +9968,7 @@
       <c r="W31" s="33"/>
       <c r="X31" s="33"/>
     </row>
-    <row r="32" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="21" t="s">
         <v>385</v>
       </c>
@@ -9960,10 +9988,10 @@
         <v>1397</v>
       </c>
       <c r="G32" s="33" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="H32" s="33" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="I32" s="33" t="s">
         <v>374</v>
@@ -9972,7 +10000,7 @@
         <v>40</v>
       </c>
       <c r="K32" s="33" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="L32" s="33"/>
       <c r="M32" s="33" t="s">
@@ -9994,7 +10022,7 @@
       <c r="W32" s="33"/>
       <c r="X32" s="33"/>
     </row>
-    <row r="33" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="21" t="s">
         <v>385</v>
       </c>
@@ -10014,10 +10042,10 @@
         <v>1398</v>
       </c>
       <c r="G33" s="33" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="H33" s="33" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="I33" s="33" t="s">
         <v>374</v>
@@ -10026,7 +10054,7 @@
         <v>68</v>
       </c>
       <c r="K33" s="33" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="L33" s="33"/>
       <c r="M33" s="33" t="s">
@@ -10060,7 +10088,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="34" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="21" t="s">
         <v>385</v>
       </c>
@@ -10080,7 +10108,7 @@
         <v>1399</v>
       </c>
       <c r="G34" s="33" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="H34" s="33" t="s">
         <v>1316</v>
@@ -10114,7 +10142,7 @@
       <c r="W34" s="33"/>
       <c r="X34" s="33"/>
     </row>
-    <row r="35" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="21" t="s">
         <v>385</v>
       </c>
@@ -10134,7 +10162,7 @@
         <v>1400</v>
       </c>
       <c r="G35" s="33" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="H35" s="33" t="s">
         <v>1317</v>
@@ -10168,7 +10196,7 @@
       <c r="W35" s="33"/>
       <c r="X35" s="33"/>
     </row>
-    <row r="36" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="21" t="s">
         <v>385</v>
       </c>
@@ -10185,10 +10213,10 @@
         <v>498</v>
       </c>
       <c r="F36" s="33" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
       <c r="G36" s="33" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="H36" s="33" t="s">
         <v>1318</v>
@@ -10236,7 +10264,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="37" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="21" t="s">
         <v>385</v>
       </c>
@@ -10256,7 +10284,7 @@
         <v>1401</v>
       </c>
       <c r="G37" s="33" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="H37" s="33" t="s">
         <v>1319</v>
@@ -10302,7 +10330,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="21" t="s">
         <v>385</v>
       </c>
@@ -10368,7 +10396,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="39" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="21" t="s">
         <v>385</v>
       </c>
@@ -10388,7 +10416,7 @@
         <v>1403</v>
       </c>
       <c r="G39" s="33" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="H39" s="33" t="s">
         <v>1321</v>
@@ -10438,7 +10466,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="40" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="21" t="s">
         <v>385</v>
       </c>
@@ -10458,7 +10486,7 @@
         <v>1404</v>
       </c>
       <c r="G40" s="33" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="H40" s="33" t="s">
         <v>1322</v>
@@ -10492,7 +10520,7 @@
       <c r="W40" s="33"/>
       <c r="X40" s="33"/>
     </row>
-    <row r="41" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="21" t="s">
         <v>385</v>
       </c>
@@ -10512,7 +10540,7 @@
         <v>1405</v>
       </c>
       <c r="G41" s="33" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="H41" s="33" t="s">
         <v>1323</v>
@@ -10546,7 +10574,7 @@
       <c r="W41" s="33"/>
       <c r="X41" s="33"/>
     </row>
-    <row r="42" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="21" t="s">
         <v>385</v>
       </c>
@@ -10566,7 +10594,7 @@
         <v>1406</v>
       </c>
       <c r="G42" s="33" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="H42" s="33" t="s">
         <v>1324</v>
@@ -10600,7 +10628,7 @@
       <c r="W42" s="33"/>
       <c r="X42" s="33"/>
     </row>
-    <row r="43" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="21" t="s">
         <v>385</v>
       </c>
@@ -10620,7 +10648,7 @@
         <v>1407</v>
       </c>
       <c r="G43" s="33" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="H43" s="33" t="s">
         <v>1325</v>
@@ -10666,7 +10694,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="44" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="21" t="s">
         <v>385</v>
       </c>
@@ -10720,7 +10748,7 @@
       <c r="W44" s="33"/>
       <c r="X44" s="33"/>
     </row>
-    <row r="45" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="21" t="s">
         <v>385</v>
       </c>
@@ -10774,7 +10802,7 @@
       <c r="W45" s="33"/>
       <c r="X45" s="33"/>
     </row>
-    <row r="46" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="21" t="s">
         <v>385</v>
       </c>
@@ -10828,7 +10856,7 @@
       <c r="W46" s="33"/>
       <c r="X46" s="33"/>
     </row>
-    <row r="47" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="21" t="s">
         <v>385</v>
       </c>
@@ -10848,7 +10876,7 @@
         <v>1159</v>
       </c>
       <c r="G47" s="33" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="H47" s="33" t="s">
         <v>1388</v>
@@ -10882,7 +10910,7 @@
       <c r="W47" s="33"/>
       <c r="X47" s="33"/>
     </row>
-    <row r="48" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="21" t="s">
         <v>385</v>
       </c>
@@ -10902,7 +10930,7 @@
         <v>1160</v>
       </c>
       <c r="G48" s="33" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="H48" s="33" t="s">
         <v>1388</v>
@@ -10936,7 +10964,7 @@
       <c r="W48" s="33"/>
       <c r="X48" s="33"/>
     </row>
-    <row r="49" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="21" t="s">
         <v>385</v>
       </c>
@@ -10956,7 +10984,7 @@
         <v>1161</v>
       </c>
       <c r="G49" s="33" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="H49" s="33" t="s">
         <v>1388</v>
@@ -10990,7 +11018,7 @@
       <c r="W49" s="33"/>
       <c r="X49" s="33"/>
     </row>
-    <row r="50" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="21" t="s">
         <v>385</v>
       </c>
@@ -11010,10 +11038,10 @@
         <v>1408</v>
       </c>
       <c r="G50" s="33" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="H50" s="33" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="I50" s="33" t="s">
         <v>374</v>
@@ -11044,7 +11072,7 @@
       <c r="W50" s="33"/>
       <c r="X50" s="33"/>
     </row>
-    <row r="51" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="21" t="s">
         <v>385</v>
       </c>
@@ -11064,7 +11092,7 @@
         <v>1409</v>
       </c>
       <c r="G51" s="33" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="H51" s="33" t="s">
         <v>1326</v>
@@ -11114,7 +11142,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="52" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="21" t="s">
         <v>385</v>
       </c>
@@ -11134,7 +11162,7 @@
         <v>405</v>
       </c>
       <c r="G52" s="33" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="H52" s="33" t="s">
         <v>1326</v>
@@ -11168,7 +11196,7 @@
       <c r="W52" s="27"/>
       <c r="X52" s="27"/>
     </row>
-    <row r="53" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="21" t="s">
         <v>385</v>
       </c>
@@ -11188,10 +11216,10 @@
         <v>1259</v>
       </c>
       <c r="G53" s="33" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
       <c r="H53" s="33" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
       <c r="I53" s="33" t="s">
         <v>374</v>
@@ -11234,7 +11262,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="54" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="21" t="s">
         <v>385</v>
       </c>
@@ -11254,10 +11282,10 @@
         <v>74</v>
       </c>
       <c r="G54" s="33" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="H54" s="33" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
       <c r="I54" s="33" t="s">
         <v>374</v>
@@ -11288,7 +11316,7 @@
       <c r="W54" s="33"/>
       <c r="X54" s="33"/>
     </row>
-    <row r="55" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="21" t="s">
         <v>385</v>
       </c>
@@ -11308,10 +11336,10 @@
         <v>1410</v>
       </c>
       <c r="G55" s="33" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="H55" s="33" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
       <c r="I55" s="33" t="s">
         <v>374</v>
@@ -11342,7 +11370,7 @@
       <c r="W55" s="33"/>
       <c r="X55" s="33"/>
     </row>
-    <row r="56" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="21" t="s">
         <v>385</v>
       </c>
@@ -11365,7 +11393,7 @@
         <v>1162</v>
       </c>
       <c r="H56" s="33" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="I56" s="33" t="s">
         <v>374</v>
@@ -11396,7 +11424,7 @@
       <c r="W56" s="33"/>
       <c r="X56" s="33"/>
     </row>
-    <row r="57" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="21" t="s">
         <v>385</v>
       </c>
@@ -11452,7 +11480,7 @@
       <c r="W57" s="33"/>
       <c r="X57" s="33"/>
     </row>
-    <row r="58" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="21" t="s">
         <v>385</v>
       </c>
@@ -11472,7 +11500,7 @@
         <v>827</v>
       </c>
       <c r="G58" s="33" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
       <c r="H58" s="33" t="s">
         <v>828</v>
@@ -11508,7 +11536,7 @@
       <c r="W58" s="33"/>
       <c r="X58" s="33"/>
     </row>
-    <row r="59" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="21" t="s">
         <v>385</v>
       </c>
@@ -11528,7 +11556,7 @@
         <v>1411</v>
       </c>
       <c r="G59" s="33" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="H59" s="33" t="s">
         <v>1327</v>
@@ -11562,7 +11590,7 @@
       <c r="W59" s="33"/>
       <c r="X59" s="33"/>
     </row>
-    <row r="60" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="21" t="s">
         <v>385</v>
       </c>
@@ -11582,7 +11610,7 @@
         <v>1412</v>
       </c>
       <c r="G60" s="33" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
       <c r="H60" s="33" t="s">
         <v>1328</v>
@@ -11616,7 +11644,7 @@
       <c r="W60" s="33"/>
       <c r="X60" s="33"/>
     </row>
-    <row r="61" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="21" t="s">
         <v>385</v>
       </c>
@@ -11636,7 +11664,7 @@
         <v>1413</v>
       </c>
       <c r="G61" s="33" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
       <c r="H61" s="33" t="s">
         <v>1329</v>
@@ -11670,7 +11698,7 @@
       <c r="W61" s="33"/>
       <c r="X61" s="33"/>
     </row>
-    <row r="62" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="21" t="s">
         <v>385</v>
       </c>
@@ -11690,7 +11718,7 @@
         <v>1414</v>
       </c>
       <c r="G62" s="33" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
       <c r="H62" s="33" t="s">
         <v>1330</v>
@@ -11724,7 +11752,7 @@
       <c r="W62" s="33"/>
       <c r="X62" s="33"/>
     </row>
-    <row r="63" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="21" t="s">
         <v>385</v>
       </c>
@@ -11790,7 +11818,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="64" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="21" t="s">
         <v>385</v>
       </c>
@@ -11856,7 +11884,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="65" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="21" t="s">
         <v>385</v>
       </c>
@@ -11888,7 +11916,7 @@
         <v>111</v>
       </c>
       <c r="K65" s="33" t="s">
-        <v>2074</v>
+        <v>2071</v>
       </c>
       <c r="L65" s="33"/>
       <c r="M65" s="33" t="s">
@@ -11922,7 +11950,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="66" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="21" t="s">
         <v>385</v>
       </c>
@@ -11954,7 +11982,7 @@
         <v>112</v>
       </c>
       <c r="K66" s="33" t="s">
-        <v>2074</v>
+        <v>2071</v>
       </c>
       <c r="L66" s="33"/>
       <c r="M66" s="33" t="s">
@@ -11988,7 +12016,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="67" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="21" t="s">
         <v>385</v>
       </c>
@@ -12020,7 +12048,7 @@
         <v>113</v>
       </c>
       <c r="K67" s="33" t="s">
-        <v>2074</v>
+        <v>2071</v>
       </c>
       <c r="L67" s="33"/>
       <c r="M67" s="33" t="s">
@@ -12042,7 +12070,7 @@
       <c r="W67" s="33"/>
       <c r="X67" s="63"/>
     </row>
-    <row r="68" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="21" t="s">
         <v>385</v>
       </c>
@@ -12108,7 +12136,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="69" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="21" t="s">
         <v>385</v>
       </c>
@@ -12178,7 +12206,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="70" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="21" t="s">
         <v>385</v>
       </c>
@@ -12246,7 +12274,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="71" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="21" t="s">
         <v>385</v>
       </c>
@@ -12310,7 +12338,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="72" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="21" t="s">
         <v>385</v>
       </c>
@@ -12378,7 +12406,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="73" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="21" t="s">
         <v>385</v>
       </c>
@@ -12430,7 +12458,7 @@
       <c r="W73" s="33"/>
       <c r="X73" s="33"/>
     </row>
-    <row r="74" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="21" t="s">
         <v>385</v>
       </c>
@@ -12484,7 +12512,7 @@
       <c r="W74" s="33"/>
       <c r="X74" s="33"/>
     </row>
-    <row r="75" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="21" t="s">
         <v>385</v>
       </c>
@@ -12504,7 +12532,7 @@
         <v>1420</v>
       </c>
       <c r="G75" s="33" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
       <c r="H75" s="33" t="s">
         <v>1337</v>
@@ -12538,7 +12566,7 @@
       <c r="W75" s="33"/>
       <c r="X75" s="33"/>
     </row>
-    <row r="76" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="21" t="s">
         <v>385</v>
       </c>
@@ -12558,7 +12586,7 @@
         <v>1421</v>
       </c>
       <c r="G76" s="33" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="H76" s="33" t="s">
         <v>1338</v>
@@ -12590,7 +12618,7 @@
       <c r="W76" s="33"/>
       <c r="X76" s="33"/>
     </row>
-    <row r="77" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="21" t="s">
         <v>385</v>
       </c>
@@ -12610,7 +12638,7 @@
         <v>1422</v>
       </c>
       <c r="G77" s="33" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
       <c r="H77" s="33" t="s">
         <v>1339</v>
@@ -12642,7 +12670,7 @@
       <c r="W77" s="33"/>
       <c r="X77" s="33"/>
     </row>
-    <row r="78" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="21" t="s">
         <v>385</v>
       </c>
@@ -12662,7 +12690,7 @@
         <v>1423</v>
       </c>
       <c r="G78" s="33" t="s">
-        <v>1651</v>
+        <v>1648</v>
       </c>
       <c r="H78" s="33" t="s">
         <v>1340</v>
@@ -12694,7 +12722,7 @@
       <c r="W78" s="33"/>
       <c r="X78" s="33"/>
     </row>
-    <row r="79" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="21" t="s">
         <v>385</v>
       </c>
@@ -12714,7 +12742,7 @@
         <v>1424</v>
       </c>
       <c r="G79" s="33" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
       <c r="H79" s="33" t="s">
         <v>1341</v>
@@ -12746,7 +12774,7 @@
       <c r="W79" s="33"/>
       <c r="X79" s="33"/>
     </row>
-    <row r="80" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="21" t="s">
         <v>385</v>
       </c>
@@ -12766,7 +12794,7 @@
         <v>1425</v>
       </c>
       <c r="G80" s="33" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
       <c r="H80" s="33" t="s">
         <v>1342</v>
@@ -12798,7 +12826,7 @@
       <c r="W80" s="33"/>
       <c r="X80" s="33"/>
     </row>
-    <row r="81" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="21" t="s">
         <v>385</v>
       </c>
@@ -12818,7 +12846,7 @@
         <v>1426</v>
       </c>
       <c r="G81" s="33" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
       <c r="H81" s="33" t="s">
         <v>1343</v>
@@ -12850,7 +12878,7 @@
       <c r="W81" s="33"/>
       <c r="X81" s="33"/>
     </row>
-    <row r="82" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="21" t="s">
         <v>385</v>
       </c>
@@ -12870,7 +12898,7 @@
         <v>1427</v>
       </c>
       <c r="G82" s="33" t="s">
-        <v>1655</v>
+        <v>1652</v>
       </c>
       <c r="H82" s="33" t="s">
         <v>1344</v>
@@ -12902,7 +12930,7 @@
       <c r="W82" s="33"/>
       <c r="X82" s="33"/>
     </row>
-    <row r="83" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="21" t="s">
         <v>385</v>
       </c>
@@ -12972,7 +13000,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="84" spans="1:24" s="1" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:24" s="1" customFormat="1" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="21" t="s">
         <v>385</v>
       </c>
@@ -13026,7 +13054,7 @@
       <c r="W84" s="28"/>
       <c r="X84" s="28"/>
     </row>
-    <row r="85" spans="1:24" s="1" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:24" s="1" customFormat="1" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="21" t="s">
         <v>385</v>
       </c>
@@ -13080,7 +13108,7 @@
       <c r="W85" s="28"/>
       <c r="X85" s="28"/>
     </row>
-    <row r="86" spans="1:24" s="1" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:24" s="1" customFormat="1" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="21" t="s">
         <v>385</v>
       </c>
@@ -13134,7 +13162,7 @@
       <c r="W86" s="28"/>
       <c r="X86" s="28"/>
     </row>
-    <row r="87" spans="1:24" s="1" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:24" s="1" customFormat="1" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="21" t="s">
         <v>385</v>
       </c>
@@ -13188,7 +13216,7 @@
       <c r="W87" s="28"/>
       <c r="X87" s="28"/>
     </row>
-    <row r="88" spans="1:24" s="1" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:24" s="1" customFormat="1" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="21" t="s">
         <v>385</v>
       </c>
@@ -13242,7 +13270,7 @@
       <c r="W88" s="28"/>
       <c r="X88" s="28"/>
     </row>
-    <row r="89" spans="1:24" s="1" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:24" s="1" customFormat="1" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="21" t="s">
         <v>385</v>
       </c>
@@ -13296,7 +13324,7 @@
       <c r="W89" s="28"/>
       <c r="X89" s="28"/>
     </row>
-    <row r="90" spans="1:24" s="1" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:24" s="1" customFormat="1" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="21" t="s">
         <v>385</v>
       </c>
@@ -13350,7 +13378,7 @@
       <c r="W90" s="28"/>
       <c r="X90" s="28"/>
     </row>
-    <row r="91" spans="1:24" s="1" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:24" s="1" customFormat="1" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="21" t="s">
         <v>385</v>
       </c>
@@ -13404,7 +13432,7 @@
       <c r="W91" s="28"/>
       <c r="X91" s="28"/>
     </row>
-    <row r="92" spans="1:24" s="1" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:24" s="1" customFormat="1" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="21" t="s">
         <v>385</v>
       </c>
@@ -13458,7 +13486,7 @@
       <c r="W92" s="28"/>
       <c r="X92" s="28"/>
     </row>
-    <row r="93" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="21" t="s">
         <v>385</v>
       </c>
@@ -13472,7 +13500,7 @@
         <v>566</v>
       </c>
       <c r="E93" s="33" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="F93" s="33" t="s">
         <v>1176</v>
@@ -13481,7 +13509,7 @@
         <v>1177</v>
       </c>
       <c r="H93" s="33" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="I93" s="33" t="s">
         <v>374</v>
@@ -13501,7 +13529,7 @@
       </c>
       <c r="O93" s="33"/>
       <c r="P93" s="33" t="s">
-        <v>1521</v>
+        <v>2073</v>
       </c>
       <c r="Q93" s="33">
         <v>1</v>
@@ -13528,7 +13556,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="94" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="21" t="s">
         <v>385</v>
       </c>
@@ -13542,7 +13570,7 @@
         <v>567</v>
       </c>
       <c r="E94" s="33" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="F94" s="33" t="s">
         <v>1178</v>
@@ -13551,7 +13579,7 @@
         <v>1179</v>
       </c>
       <c r="H94" s="33" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="I94" s="33" t="s">
         <v>374</v>
@@ -13582,7 +13610,7 @@
       <c r="W94" s="33"/>
       <c r="X94" s="33"/>
     </row>
-    <row r="95" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="21" t="s">
         <v>385</v>
       </c>
@@ -13596,7 +13624,7 @@
         <v>157</v>
       </c>
       <c r="E95" s="33" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="F95" s="33" t="s">
         <v>269</v>
@@ -13605,7 +13633,7 @@
         <v>1177</v>
       </c>
       <c r="H95" s="33" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="I95" s="33" t="s">
         <v>374</v>
@@ -13636,7 +13664,7 @@
       <c r="W95" s="33"/>
       <c r="X95" s="33"/>
     </row>
-    <row r="96" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="21" t="s">
         <v>385</v>
       </c>
@@ -13650,7 +13678,7 @@
         <v>158</v>
       </c>
       <c r="E96" s="33" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="F96" s="33" t="s">
         <v>269</v>
@@ -13659,7 +13687,7 @@
         <v>1177</v>
       </c>
       <c r="H96" s="33" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="I96" s="33" t="s">
         <v>374</v>
@@ -13702,7 +13730,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="97" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="21" t="s">
         <v>385</v>
       </c>
@@ -13716,7 +13744,7 @@
         <v>159</v>
       </c>
       <c r="E97" s="33" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="F97" s="33" t="s">
         <v>265</v>
@@ -13725,7 +13753,7 @@
         <v>1177</v>
       </c>
       <c r="H97" s="33" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="I97" s="33" t="s">
         <v>374</v>
@@ -13756,7 +13784,7 @@
       <c r="W97" s="33"/>
       <c r="X97" s="33"/>
     </row>
-    <row r="98" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="21" t="s">
         <v>385</v>
       </c>
@@ -13770,7 +13798,7 @@
         <v>159</v>
       </c>
       <c r="E98" s="33" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="F98" s="33" t="s">
         <v>194</v>
@@ -13779,7 +13807,7 @@
         <v>1177</v>
       </c>
       <c r="H98" s="33" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="I98" s="33" t="s">
         <v>374</v>
@@ -13810,7 +13838,7 @@
       <c r="W98" s="33"/>
       <c r="X98" s="33"/>
     </row>
-    <row r="99" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="21" t="s">
         <v>385</v>
       </c>
@@ -13824,7 +13852,7 @@
         <v>159</v>
       </c>
       <c r="E99" s="33" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="F99" s="33" t="s">
         <v>193</v>
@@ -13833,7 +13861,7 @@
         <v>1177</v>
       </c>
       <c r="H99" s="33" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="I99" s="33" t="s">
         <v>374</v>
@@ -13864,7 +13892,7 @@
       <c r="W99" s="33"/>
       <c r="X99" s="33"/>
     </row>
-    <row r="100" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="21" t="s">
         <v>385</v>
       </c>
@@ -13878,7 +13906,7 @@
         <v>163</v>
       </c>
       <c r="E100" s="33" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="F100" s="33" t="s">
         <v>265</v>
@@ -13887,7 +13915,7 @@
         <v>1177</v>
       </c>
       <c r="H100" s="33" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="I100" s="33" t="s">
         <v>374</v>
@@ -13918,7 +13946,7 @@
       <c r="W100" s="33"/>
       <c r="X100" s="33"/>
     </row>
-    <row r="101" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="21" t="s">
         <v>385</v>
       </c>
@@ -13932,7 +13960,7 @@
         <v>163</v>
       </c>
       <c r="E101" s="33" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="F101" s="33" t="s">
         <v>194</v>
@@ -13941,7 +13969,7 @@
         <v>1177</v>
       </c>
       <c r="H101" s="33" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="I101" s="33" t="s">
         <v>374</v>
@@ -13972,7 +14000,7 @@
       <c r="W101" s="33"/>
       <c r="X101" s="33"/>
     </row>
-    <row r="102" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="21" t="s">
         <v>385</v>
       </c>
@@ -13986,7 +14014,7 @@
         <v>163</v>
       </c>
       <c r="E102" s="33" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="F102" s="33" t="s">
         <v>193</v>
@@ -13995,7 +14023,7 @@
         <v>1177</v>
       </c>
       <c r="H102" s="33" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="I102" s="33" t="s">
         <v>374</v>
@@ -14026,7 +14054,7 @@
       <c r="W102" s="33"/>
       <c r="X102" s="33"/>
     </row>
-    <row r="103" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="21" t="s">
         <v>385</v>
       </c>
@@ -14040,7 +14068,7 @@
         <v>568</v>
       </c>
       <c r="E103" s="33" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="F103" s="33" t="s">
         <v>1428</v>
@@ -14049,7 +14077,7 @@
         <v>1177</v>
       </c>
       <c r="H103" s="33" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="I103" s="33" t="s">
         <v>374</v>
@@ -14092,7 +14120,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="104" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="21" t="s">
         <v>385</v>
       </c>
@@ -14106,7 +14134,7 @@
         <v>568</v>
       </c>
       <c r="E104" s="33" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="F104" s="33" t="s">
         <v>1429</v>
@@ -14115,7 +14143,7 @@
         <v>1177</v>
       </c>
       <c r="H104" s="33" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="I104" s="33" t="s">
         <v>374</v>
@@ -14146,7 +14174,7 @@
       <c r="W104" s="33"/>
       <c r="X104" s="33"/>
     </row>
-    <row r="105" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="21" t="s">
         <v>385</v>
       </c>
@@ -14160,7 +14188,7 @@
         <v>568</v>
       </c>
       <c r="E105" s="33" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="F105" s="33" t="s">
         <v>1430</v>
@@ -14169,7 +14197,7 @@
         <v>1177</v>
       </c>
       <c r="H105" s="33" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="I105" s="33" t="s">
         <v>374</v>
@@ -14216,7 +14244,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="106" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="21" t="s">
         <v>385</v>
       </c>
@@ -14230,7 +14258,7 @@
         <v>168</v>
       </c>
       <c r="E106" s="33" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="F106" s="33" t="s">
         <v>266</v>
@@ -14239,7 +14267,7 @@
         <v>1179</v>
       </c>
       <c r="H106" s="33" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="I106" s="33" t="s">
         <v>374</v>
@@ -14270,7 +14298,7 @@
       <c r="W106" s="33"/>
       <c r="X106" s="33"/>
     </row>
-    <row r="107" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="21" t="s">
         <v>385</v>
       </c>
@@ -14284,7 +14312,7 @@
         <v>569</v>
       </c>
       <c r="E107" s="33" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="F107" s="33" t="s">
         <v>1431</v>
@@ -14293,7 +14321,7 @@
         <v>1177</v>
       </c>
       <c r="H107" s="33" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="I107" s="33" t="s">
         <v>374</v>
@@ -14340,7 +14368,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="108" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="21" t="s">
         <v>385</v>
       </c>
@@ -14363,7 +14391,7 @@
         <v>1180</v>
       </c>
       <c r="H108" s="33" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="I108" s="33" t="s">
         <v>374</v>
@@ -14406,7 +14434,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="109" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="21" t="s">
         <v>385</v>
       </c>
@@ -14426,7 +14454,7 @@
         <v>1432</v>
       </c>
       <c r="G109" s="33" t="s">
-        <v>1657</v>
+        <v>1654</v>
       </c>
       <c r="H109" s="33" t="s">
         <v>1345</v>
@@ -14460,7 +14488,7 @@
       <c r="W109" s="33"/>
       <c r="X109" s="33"/>
     </row>
-    <row r="110" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="21" t="s">
         <v>385</v>
       </c>
@@ -14480,7 +14508,7 @@
         <v>1433</v>
       </c>
       <c r="G110" s="33" t="s">
-        <v>1658</v>
+        <v>1655</v>
       </c>
       <c r="H110" s="33" t="s">
         <v>1346</v>
@@ -14514,7 +14542,7 @@
       <c r="W110" s="33"/>
       <c r="X110" s="33"/>
     </row>
-    <row r="111" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="21" t="s">
         <v>385</v>
       </c>
@@ -14525,7 +14553,7 @@
         <v>1494</v>
       </c>
       <c r="D111" s="33" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="E111" s="33" t="s">
         <v>354</v>
@@ -14534,7 +14562,7 @@
         <v>1434</v>
       </c>
       <c r="G111" s="33" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
       <c r="H111" s="33" t="s">
         <v>1347</v>
@@ -14568,7 +14596,7 @@
       <c r="W111" s="33"/>
       <c r="X111" s="33"/>
     </row>
-    <row r="112" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="21" t="s">
         <v>385</v>
       </c>
@@ -14579,7 +14607,7 @@
         <v>1495</v>
       </c>
       <c r="D112" s="33" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="E112" s="33" t="s">
         <v>354</v>
@@ -14588,7 +14616,7 @@
         <v>1435</v>
       </c>
       <c r="G112" s="33" t="s">
-        <v>1660</v>
+        <v>1657</v>
       </c>
       <c r="H112" s="33" t="s">
         <v>1348</v>
@@ -14622,7 +14650,7 @@
       <c r="W112" s="33"/>
       <c r="X112" s="33"/>
     </row>
-    <row r="113" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="21" t="s">
         <v>385</v>
       </c>
@@ -14642,7 +14670,7 @@
         <v>1436</v>
       </c>
       <c r="G113" s="33" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
       <c r="H113" s="33" t="s">
         <v>1349</v>
@@ -14685,10 +14713,10 @@
         <v>1030</v>
       </c>
       <c r="X113" s="62" t="s">
-        <v>1549</v>
-      </c>
-    </row>
-    <row r="114" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="114" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="21" t="s">
         <v>385</v>
       </c>
@@ -14708,7 +14736,7 @@
         <v>1437</v>
       </c>
       <c r="G114" s="33" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
       <c r="H114" s="33" t="s">
         <v>1350</v>
@@ -14742,7 +14770,7 @@
       <c r="W114" s="33"/>
       <c r="X114" s="33"/>
     </row>
-    <row r="115" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="21" t="s">
         <v>385</v>
       </c>
@@ -14762,7 +14790,7 @@
         <v>1438</v>
       </c>
       <c r="G115" s="33" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="H115" s="33" t="s">
         <v>1351</v>
@@ -14796,7 +14824,7 @@
       <c r="W115" s="33"/>
       <c r="X115" s="33"/>
     </row>
-    <row r="116" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="21" t="s">
         <v>385</v>
       </c>
@@ -14807,7 +14835,7 @@
         <v>1497</v>
       </c>
       <c r="D116" s="33" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="E116" s="33" t="s">
         <v>356</v>
@@ -14816,7 +14844,7 @@
         <v>1439</v>
       </c>
       <c r="G116" s="33" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="H116" s="33" t="s">
         <v>1352</v>
@@ -14850,7 +14878,7 @@
       <c r="W116" s="33"/>
       <c r="X116" s="33"/>
     </row>
-    <row r="117" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="21" t="s">
         <v>385</v>
       </c>
@@ -14861,7 +14889,7 @@
         <v>1498</v>
       </c>
       <c r="D117" s="33" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="E117" s="33" t="s">
         <v>356</v>
@@ -14870,7 +14898,7 @@
         <v>1440</v>
       </c>
       <c r="G117" s="33" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="H117" s="33" t="s">
         <v>1353</v>
@@ -14904,7 +14932,7 @@
       <c r="W117" s="33"/>
       <c r="X117" s="33"/>
     </row>
-    <row r="118" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="21" t="s">
         <v>385</v>
       </c>
@@ -14924,7 +14952,7 @@
         <v>1441</v>
       </c>
       <c r="G118" s="33" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="H118" s="33" t="s">
         <v>1354</v>
@@ -14958,7 +14986,7 @@
       <c r="W118" s="33"/>
       <c r="X118" s="33"/>
     </row>
-    <row r="119" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="21" t="s">
         <v>385</v>
       </c>
@@ -14978,7 +15006,7 @@
         <v>1442</v>
       </c>
       <c r="G119" s="33" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="H119" s="33" t="s">
         <v>1355</v>
@@ -15012,7 +15040,7 @@
       <c r="W119" s="33"/>
       <c r="X119" s="33"/>
     </row>
-    <row r="120" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="21" t="s">
         <v>385</v>
       </c>
@@ -15023,7 +15051,7 @@
         <v>1500</v>
       </c>
       <c r="D120" s="33" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
       <c r="E120" s="33" t="s">
         <v>358</v>
@@ -15032,7 +15060,7 @@
         <v>1443</v>
       </c>
       <c r="G120" s="33" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="H120" s="33" t="s">
         <v>1356</v>
@@ -15066,7 +15094,7 @@
       <c r="W120" s="33"/>
       <c r="X120" s="33"/>
     </row>
-    <row r="121" spans="1:24" s="17" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:24" s="17" customFormat="1" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="21" t="s">
         <v>385</v>
       </c>
@@ -15077,7 +15105,7 @@
         <v>1501</v>
       </c>
       <c r="D121" s="33" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
       <c r="E121" s="64" t="s">
         <v>358</v>
@@ -15086,7 +15114,7 @@
         <v>1444</v>
       </c>
       <c r="G121" s="33" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="H121" s="33" t="s">
         <v>1357</v>
@@ -15120,7 +15148,7 @@
       <c r="W121" s="64"/>
       <c r="X121" s="64"/>
     </row>
-    <row r="122" spans="1:24" s="17" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:24" s="17" customFormat="1" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="21" t="s">
         <v>385</v>
       </c>
@@ -15140,7 +15168,7 @@
         <v>1445</v>
       </c>
       <c r="G122" s="33" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="H122" s="33" t="s">
         <v>1358</v>
@@ -15186,7 +15214,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="123" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="21" t="s">
         <v>385</v>
       </c>
@@ -15206,7 +15234,7 @@
         <v>1446</v>
       </c>
       <c r="G123" s="33" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="H123" s="33" t="s">
         <v>1359</v>
@@ -15240,7 +15268,7 @@
       <c r="W123" s="33"/>
       <c r="X123" s="33"/>
     </row>
-    <row r="124" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="21" t="s">
         <v>385</v>
       </c>
@@ -15260,7 +15288,7 @@
         <v>1447</v>
       </c>
       <c r="G124" s="33" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="H124" s="33" t="s">
         <v>1360</v>
@@ -15294,7 +15322,7 @@
       <c r="W124" s="33"/>
       <c r="X124" s="33"/>
     </row>
-    <row r="125" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="21" t="s">
         <v>385</v>
       </c>
@@ -15314,7 +15342,7 @@
         <v>1448</v>
       </c>
       <c r="G125" s="33" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="H125" s="33" t="s">
         <v>1361</v>
@@ -15360,7 +15388,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="126" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="21" t="s">
         <v>385</v>
       </c>
@@ -15380,7 +15408,7 @@
         <v>1449</v>
       </c>
       <c r="G126" s="33" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="H126" s="33" t="s">
         <v>1362</v>
@@ -15426,7 +15454,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="127" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="21" t="s">
         <v>385</v>
       </c>
@@ -15446,7 +15474,7 @@
         <v>1450</v>
       </c>
       <c r="G127" s="33" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="H127" s="33" t="s">
         <v>1363</v>
@@ -15492,7 +15520,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="128" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="21" t="s">
         <v>385</v>
       </c>
@@ -15512,7 +15540,7 @@
         <v>1451</v>
       </c>
       <c r="G128" s="33" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
       <c r="H128" s="33" t="s">
         <v>1364</v>
@@ -15558,7 +15586,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="129" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="21" t="s">
         <v>385</v>
       </c>
@@ -15578,7 +15606,7 @@
         <v>1452</v>
       </c>
       <c r="G129" s="33" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
       <c r="H129" s="33" t="s">
         <v>1365</v>
@@ -15624,7 +15652,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="130" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="21" t="s">
         <v>385</v>
       </c>
@@ -15644,7 +15672,7 @@
         <v>1453</v>
       </c>
       <c r="G130" s="33" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
       <c r="H130" s="33" t="s">
         <v>1366</v>
@@ -15690,7 +15718,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="131" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="21" t="s">
         <v>385</v>
       </c>
@@ -15710,7 +15738,7 @@
         <v>1454</v>
       </c>
       <c r="G131" s="33" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="H131" s="33" t="s">
         <v>1367</v>
@@ -15756,7 +15784,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="132" spans="1:24" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A132" s="21" t="s">
         <v>385</v>
       </c>
@@ -15822,7 +15850,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="133" spans="1:24" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A133" s="21" t="s">
         <v>385</v>
       </c>
@@ -15880,7 +15908,7 @@
       <c r="W133" s="33"/>
       <c r="X133" s="33"/>
     </row>
-    <row r="134" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="21" t="s">
         <v>385</v>
       </c>
@@ -15891,10 +15919,10 @@
         <v>869</v>
       </c>
       <c r="D134" s="67" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="E134" s="67" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="F134" s="67" t="s">
         <v>870</v>
@@ -15934,7 +15962,7 @@
       <c r="W134" s="33"/>
       <c r="X134" s="33"/>
     </row>
-    <row r="135" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="21" t="s">
         <v>385</v>
       </c>
@@ -15948,13 +15976,13 @@
         <v>874</v>
       </c>
       <c r="E135" s="67" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F135" s="67" t="s">
         <v>1183</v>
       </c>
       <c r="G135" s="67" t="s">
-        <v>1694</v>
+        <v>1691</v>
       </c>
       <c r="H135" s="67" t="s">
         <v>875</v>
@@ -15988,7 +16016,7 @@
       <c r="W135" s="33"/>
       <c r="X135" s="33"/>
     </row>
-    <row r="136" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="21" t="s">
         <v>385</v>
       </c>
@@ -15996,19 +16024,19 @@
         <v>1113</v>
       </c>
       <c r="C136" s="67" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="D136" s="67" t="s">
         <v>877</v>
       </c>
       <c r="E136" s="67" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="F136" s="67" t="s">
         <v>1184</v>
       </c>
       <c r="G136" s="67" t="s">
-        <v>1695</v>
+        <v>1692</v>
       </c>
       <c r="H136" s="67" t="s">
         <v>878</v>
@@ -16042,7 +16070,7 @@
       <c r="W136" s="33"/>
       <c r="X136" s="33"/>
     </row>
-    <row r="137" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="21" t="s">
         <v>385</v>
       </c>
@@ -16050,19 +16078,19 @@
         <v>1113</v>
       </c>
       <c r="C137" s="67" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="D137" s="67" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="E137" s="67" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
       <c r="F137" s="67" t="s">
         <v>1185</v>
       </c>
       <c r="G137" s="67" t="s">
-        <v>1696</v>
+        <v>1693</v>
       </c>
       <c r="H137" s="67" t="s">
         <v>880</v>
@@ -16071,7 +16099,7 @@
         <v>374</v>
       </c>
       <c r="J137" s="67" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="K137" s="67" t="s">
         <v>1015</v>
@@ -16096,7 +16124,7 @@
       <c r="W137" s="33"/>
       <c r="X137" s="33"/>
     </row>
-    <row r="138" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="21" t="s">
         <v>385</v>
       </c>
@@ -16110,13 +16138,13 @@
         <v>882</v>
       </c>
       <c r="E138" s="67" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
       <c r="F138" s="67" t="s">
         <v>1186</v>
       </c>
       <c r="G138" s="67" t="s">
-        <v>1697</v>
+        <v>1694</v>
       </c>
       <c r="H138" s="67" t="s">
         <v>883</v>
@@ -16150,7 +16178,7 @@
       <c r="W138" s="33"/>
       <c r="X138" s="33"/>
     </row>
-    <row r="139" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="21" t="s">
         <v>385</v>
       </c>
@@ -16164,22 +16192,22 @@
         <v>886</v>
       </c>
       <c r="E139" s="67" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="F139" s="67" t="s">
         <v>1187</v>
       </c>
       <c r="G139" s="67" t="s">
-        <v>1698</v>
+        <v>1695</v>
       </c>
       <c r="H139" s="67" t="s">
-        <v>1704</v>
+        <v>1701</v>
       </c>
       <c r="I139" s="67" t="s">
         <v>374</v>
       </c>
       <c r="J139" s="67" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="K139" s="67" t="s">
         <v>977</v>
@@ -16204,7 +16232,7 @@
       <c r="W139" s="33"/>
       <c r="X139" s="33"/>
     </row>
-    <row r="140" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="21" t="s">
         <v>385</v>
       </c>
@@ -16215,25 +16243,25 @@
         <v>887</v>
       </c>
       <c r="D140" s="67" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="E140" s="67" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="F140" s="67" t="s">
         <v>1188</v>
       </c>
       <c r="G140" s="67" t="s">
-        <v>1699</v>
+        <v>1696</v>
       </c>
       <c r="H140" s="67" t="s">
-        <v>1705</v>
+        <v>1702</v>
       </c>
       <c r="I140" s="67" t="s">
         <v>374</v>
       </c>
       <c r="J140" s="67" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="K140" s="67" t="s">
         <v>977</v>
@@ -16258,7 +16286,7 @@
       <c r="W140" s="33"/>
       <c r="X140" s="33"/>
     </row>
-    <row r="141" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="21" t="s">
         <v>385</v>
       </c>
@@ -16266,28 +16294,28 @@
         <v>1113</v>
       </c>
       <c r="C141" s="67" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="D141" s="67" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="E141" s="67" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="F141" s="67" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="G141" s="67" t="s">
-        <v>1700</v>
+        <v>1697</v>
       </c>
       <c r="H141" s="67" t="s">
-        <v>1706</v>
+        <v>1703</v>
       </c>
       <c r="I141" s="67" t="s">
         <v>374</v>
       </c>
       <c r="J141" s="67" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="K141" s="67"/>
       <c r="L141" s="67"/>
@@ -16310,7 +16338,7 @@
       <c r="W141" s="33"/>
       <c r="X141" s="33"/>
     </row>
-    <row r="142" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="21" t="s">
         <v>385</v>
       </c>
@@ -16318,31 +16346,31 @@
         <v>1113</v>
       </c>
       <c r="C142" s="67" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="D142" s="67" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="E142" s="67" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F142" s="67" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="G142" s="67" t="s">
-        <v>1702</v>
+        <v>1699</v>
       </c>
       <c r="H142" s="67" t="s">
-        <v>1703</v>
+        <v>1700</v>
       </c>
       <c r="I142" s="67" t="s">
         <v>374</v>
       </c>
       <c r="J142" s="67" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="K142" s="67" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="L142" s="67"/>
       <c r="M142" s="67" t="s">
@@ -16364,7 +16392,7 @@
       <c r="W142" s="33"/>
       <c r="X142" s="33"/>
     </row>
-    <row r="143" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="21" t="s">
         <v>385</v>
       </c>
@@ -16375,16 +16403,16 @@
         <v>888</v>
       </c>
       <c r="D143" s="67" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="E143" s="67" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="F143" s="67" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="G143" s="67" t="s">
-        <v>1701</v>
+        <v>1698</v>
       </c>
       <c r="H143" s="67" t="s">
         <v>889</v>
@@ -16393,10 +16421,10 @@
         <v>374</v>
       </c>
       <c r="J143" s="67" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="K143" s="67" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="L143" s="67"/>
       <c r="M143" s="67" t="s">
@@ -16418,7 +16446,7 @@
       <c r="W143" s="33"/>
       <c r="X143" s="33"/>
     </row>
-    <row r="144" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="21" t="s">
         <v>385</v>
       </c>
@@ -16426,7 +16454,7 @@
         <v>1133</v>
       </c>
       <c r="C144" s="40" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="D144" s="40" t="s">
         <v>585</v>
@@ -16470,7 +16498,7 @@
       <c r="W144" s="33"/>
       <c r="X144" s="33"/>
     </row>
-    <row r="145" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="21" t="s">
         <v>385</v>
       </c>
@@ -16478,7 +16506,7 @@
         <v>1133</v>
       </c>
       <c r="C145" s="40" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="D145" s="40" t="s">
         <v>589</v>
@@ -16522,7 +16550,7 @@
       <c r="W145" s="33"/>
       <c r="X145" s="33"/>
     </row>
-    <row r="146" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="21" t="s">
         <v>385</v>
       </c>
@@ -16530,7 +16558,7 @@
         <v>1133</v>
       </c>
       <c r="C146" s="40" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="D146" s="40" t="s">
         <v>592</v>
@@ -16576,7 +16604,7 @@
       <c r="W146" s="33"/>
       <c r="X146" s="33"/>
     </row>
-    <row r="147" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="21" t="s">
         <v>385</v>
       </c>
@@ -16584,7 +16612,7 @@
         <v>1133</v>
       </c>
       <c r="C147" s="40" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="D147" s="40" t="s">
         <v>781</v>
@@ -16630,7 +16658,7 @@
       <c r="W147" s="33"/>
       <c r="X147" s="33"/>
     </row>
-    <row r="148" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="21" t="s">
         <v>385</v>
       </c>
@@ -16638,7 +16666,7 @@
         <v>1133</v>
       </c>
       <c r="C148" s="40" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="D148" s="40" t="s">
         <v>782</v>
@@ -16684,7 +16712,7 @@
       <c r="W148" s="33"/>
       <c r="X148" s="33"/>
     </row>
-    <row r="149" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="21" t="s">
         <v>385</v>
       </c>
@@ -16736,7 +16764,7 @@
       <c r="W149" s="33"/>
       <c r="X149" s="33"/>
     </row>
-    <row r="150" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="21" t="s">
         <v>385</v>
       </c>
@@ -16788,7 +16816,7 @@
       <c r="W150" s="33"/>
       <c r="X150" s="33"/>
     </row>
-    <row r="151" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="21" t="s">
         <v>385</v>
       </c>
@@ -16796,7 +16824,7 @@
         <v>1133</v>
       </c>
       <c r="C151" s="40" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="D151" s="40" t="s">
         <v>606</v>
@@ -16840,7 +16868,7 @@
       <c r="W151" s="33"/>
       <c r="X151" s="33"/>
     </row>
-    <row r="152" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="21" t="s">
         <v>385</v>
       </c>
@@ -16848,7 +16876,7 @@
         <v>1133</v>
       </c>
       <c r="C152" s="40" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="D152" s="40" t="s">
         <v>608</v>
@@ -16892,7 +16920,7 @@
       <c r="W152" s="33"/>
       <c r="X152" s="33"/>
     </row>
-    <row r="153" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="21" t="s">
         <v>385</v>
       </c>
@@ -16944,7 +16972,7 @@
       <c r="W153" s="33"/>
       <c r="X153" s="33"/>
     </row>
-    <row r="154" spans="1:24" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:24" s="4" customFormat="1" ht="17.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="21" t="s">
         <v>385</v>
       </c>
@@ -16964,7 +16992,7 @@
         <v>1200</v>
       </c>
       <c r="G154" s="68" t="s">
-        <v>1680</v>
+        <v>1677</v>
       </c>
       <c r="H154" s="68" t="s">
         <v>891</v>
@@ -16998,7 +17026,7 @@
       <c r="W154" s="27"/>
       <c r="X154" s="27"/>
     </row>
-    <row r="155" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="21" t="s">
         <v>385</v>
       </c>
@@ -17064,7 +17092,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="156" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="21" t="s">
         <v>385</v>
       </c>
@@ -17128,7 +17156,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="157" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="21" t="s">
         <v>385</v>
       </c>
@@ -17139,7 +17167,7 @@
         <v>899</v>
       </c>
       <c r="D157" s="68" t="s">
-        <v>1561</v>
+        <v>1558</v>
       </c>
       <c r="E157" s="68" t="s">
         <v>1504</v>
@@ -17148,7 +17176,7 @@
         <v>1202</v>
       </c>
       <c r="G157" s="68" t="s">
-        <v>1681</v>
+        <v>1678</v>
       </c>
       <c r="H157" s="68" t="s">
         <v>900</v>
@@ -17192,7 +17220,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="158" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="21" t="s">
         <v>385</v>
       </c>
@@ -17203,7 +17231,7 @@
         <v>901</v>
       </c>
       <c r="D158" s="68" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
       <c r="E158" s="68" t="s">
         <v>989</v>
@@ -17212,7 +17240,7 @@
         <v>1203</v>
       </c>
       <c r="G158" s="68" t="s">
-        <v>1709</v>
+        <v>1706</v>
       </c>
       <c r="H158" s="68" t="s">
         <v>613</v>
@@ -17246,7 +17274,7 @@
       <c r="W158" s="69"/>
       <c r="X158" s="69"/>
     </row>
-    <row r="159" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="21" t="s">
         <v>385</v>
       </c>
@@ -17300,7 +17328,7 @@
       <c r="W159" s="69"/>
       <c r="X159" s="69"/>
     </row>
-    <row r="160" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="21" t="s">
         <v>385</v>
       </c>
@@ -17329,7 +17357,7 @@
         <v>374</v>
       </c>
       <c r="J160" s="68" t="s">
-        <v>1693</v>
+        <v>1690</v>
       </c>
       <c r="K160" s="68" t="s">
         <v>908</v>
@@ -17354,7 +17382,7 @@
       <c r="W160" s="69"/>
       <c r="X160" s="69"/>
     </row>
-    <row r="161" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="21" t="s">
         <v>385</v>
       </c>
@@ -17365,7 +17393,7 @@
         <v>996</v>
       </c>
       <c r="D161" s="68" t="s">
-        <v>1691</v>
+        <v>1688</v>
       </c>
       <c r="E161" s="68" t="s">
         <v>992</v>
@@ -17374,7 +17402,7 @@
         <v>1206</v>
       </c>
       <c r="G161" s="68" t="s">
-        <v>1707</v>
+        <v>1704</v>
       </c>
       <c r="H161" s="68" t="s">
         <v>909</v>
@@ -17406,7 +17434,7 @@
       <c r="W161" s="69"/>
       <c r="X161" s="69"/>
     </row>
-    <row r="162" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="21" t="s">
         <v>385</v>
       </c>
@@ -17417,7 +17445,7 @@
         <v>997</v>
       </c>
       <c r="D162" s="68" t="s">
-        <v>1692</v>
+        <v>1689</v>
       </c>
       <c r="E162" s="68" t="s">
         <v>993</v>
@@ -17426,7 +17454,7 @@
         <v>1207</v>
       </c>
       <c r="G162" s="68" t="s">
-        <v>1708</v>
+        <v>1705</v>
       </c>
       <c r="H162" s="68" t="s">
         <v>911</v>
@@ -17458,7 +17486,7 @@
       <c r="W162" s="69"/>
       <c r="X162" s="69"/>
     </row>
-    <row r="163" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="21" t="s">
         <v>385</v>
       </c>
@@ -17478,7 +17506,7 @@
         <v>1208</v>
       </c>
       <c r="G163" s="68" t="s">
-        <v>1690</v>
+        <v>1687</v>
       </c>
       <c r="H163" s="68" t="s">
         <v>913</v>
@@ -17510,7 +17538,7 @@
       <c r="W163" s="69"/>
       <c r="X163" s="69"/>
     </row>
-    <row r="164" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="21" t="s">
         <v>385</v>
       </c>
@@ -17518,13 +17546,13 @@
         <v>1134</v>
       </c>
       <c r="C164" s="71" t="s">
-        <v>1930</v>
+        <v>1927</v>
       </c>
       <c r="D164" s="71" t="s">
         <v>571</v>
       </c>
       <c r="E164" s="72" t="s">
-        <v>1927</v>
+        <v>1924</v>
       </c>
       <c r="F164" s="71" t="s">
         <v>1209</v>
@@ -17533,7 +17561,7 @@
         <v>1210</v>
       </c>
       <c r="H164" s="71" t="s">
-        <v>1931</v>
+        <v>1928</v>
       </c>
       <c r="I164" s="71" t="s">
         <v>374</v>
@@ -17562,7 +17590,7 @@
       <c r="W164" s="33"/>
       <c r="X164" s="33"/>
     </row>
-    <row r="165" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="21" t="s">
         <v>385</v>
       </c>
@@ -17570,22 +17598,22 @@
         <v>1134</v>
       </c>
       <c r="C165" s="71" t="s">
-        <v>1943</v>
+        <v>1940</v>
       </c>
       <c r="D165" s="71" t="s">
         <v>745</v>
       </c>
       <c r="E165" s="71" t="s">
-        <v>1928</v>
+        <v>1925</v>
       </c>
       <c r="F165" s="71" t="s">
-        <v>1932</v>
+        <v>1929</v>
       </c>
       <c r="G165" s="71" t="s">
-        <v>1933</v>
+        <v>1930</v>
       </c>
       <c r="H165" s="71" t="s">
-        <v>1934</v>
+        <v>1931</v>
       </c>
       <c r="I165" s="71" t="s">
         <v>374</v>
@@ -17616,7 +17644,7 @@
       <c r="W165" s="33"/>
       <c r="X165" s="33"/>
     </row>
-    <row r="166" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="21" t="s">
         <v>385</v>
       </c>
@@ -17624,22 +17652,22 @@
         <v>1134</v>
       </c>
       <c r="C166" s="71" t="s">
-        <v>1944</v>
+        <v>1941</v>
       </c>
       <c r="D166" s="71" t="s">
         <v>745</v>
       </c>
       <c r="E166" s="71" t="s">
-        <v>1928</v>
+        <v>1925</v>
       </c>
       <c r="F166" s="71" t="s">
-        <v>1935</v>
+        <v>1932</v>
       </c>
       <c r="G166" s="71" t="s">
-        <v>1936</v>
+        <v>1933</v>
       </c>
       <c r="H166" s="71" t="s">
-        <v>1934</v>
+        <v>1931</v>
       </c>
       <c r="I166" s="71" t="s">
         <v>374</v>
@@ -17670,7 +17698,7 @@
       <c r="W166" s="33"/>
       <c r="X166" s="33"/>
     </row>
-    <row r="167" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="21" t="s">
         <v>385</v>
       </c>
@@ -17678,22 +17706,22 @@
         <v>1134</v>
       </c>
       <c r="C167" s="71" t="s">
-        <v>1945</v>
+        <v>1942</v>
       </c>
       <c r="D167" s="71" t="s">
         <v>748</v>
       </c>
       <c r="E167" s="71" t="s">
-        <v>1929</v>
+        <v>1926</v>
       </c>
       <c r="F167" s="71" t="s">
-        <v>1937</v>
+        <v>1934</v>
       </c>
       <c r="G167" s="71" t="s">
-        <v>1938</v>
+        <v>1935</v>
       </c>
       <c r="H167" s="71" t="s">
-        <v>1939</v>
+        <v>1936</v>
       </c>
       <c r="I167" s="71" t="s">
         <v>374</v>
@@ -17724,7 +17752,7 @@
       <c r="W167" s="33"/>
       <c r="X167" s="33"/>
     </row>
-    <row r="168" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="21" t="s">
         <v>385</v>
       </c>
@@ -17732,22 +17760,22 @@
         <v>1134</v>
       </c>
       <c r="C168" s="71" t="s">
-        <v>1946</v>
+        <v>1943</v>
       </c>
       <c r="D168" s="71" t="s">
         <v>748</v>
       </c>
       <c r="E168" s="71" t="s">
-        <v>1929</v>
+        <v>1926</v>
       </c>
       <c r="F168" s="71" t="s">
-        <v>1940</v>
+        <v>1937</v>
       </c>
       <c r="G168" s="71" t="s">
-        <v>1941</v>
+        <v>1938</v>
       </c>
       <c r="H168" s="71" t="s">
-        <v>1939</v>
+        <v>1936</v>
       </c>
       <c r="I168" s="71" t="s">
         <v>374</v>
@@ -17778,7 +17806,7 @@
       <c r="W168" s="33"/>
       <c r="X168" s="33"/>
     </row>
-    <row r="169" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="21" t="s">
         <v>385</v>
       </c>
@@ -17786,7 +17814,7 @@
         <v>1135</v>
       </c>
       <c r="C169" s="73" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="D169" s="73" t="s">
         <v>915</v>
@@ -17830,7 +17858,7 @@
       <c r="W169" s="33"/>
       <c r="X169" s="33"/>
     </row>
-    <row r="170" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="21" t="s">
         <v>385</v>
       </c>
@@ -17838,7 +17866,7 @@
         <v>1135</v>
       </c>
       <c r="C170" s="73" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="D170" s="73" t="s">
         <v>918</v>
@@ -17850,7 +17878,7 @@
         <v>1213</v>
       </c>
       <c r="G170" s="73" t="s">
-        <v>1947</v>
+        <v>1944</v>
       </c>
       <c r="H170" s="73" t="s">
         <v>919</v>
@@ -17882,7 +17910,7 @@
       <c r="W170" s="33"/>
       <c r="X170" s="33"/>
     </row>
-    <row r="171" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="21" t="s">
         <v>385</v>
       </c>
@@ -17890,7 +17918,7 @@
         <v>1135</v>
       </c>
       <c r="C171" s="73" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="D171" s="73" t="s">
         <v>921</v>
@@ -17934,7 +17962,7 @@
       <c r="W171" s="33"/>
       <c r="X171" s="33"/>
     </row>
-    <row r="172" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="21" t="s">
         <v>385</v>
       </c>
@@ -17942,7 +17970,7 @@
         <v>1135</v>
       </c>
       <c r="C172" s="73" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="D172" s="73" t="s">
         <v>924</v>
@@ -17986,7 +18014,7 @@
       <c r="W172" s="33"/>
       <c r="X172" s="33"/>
     </row>
-    <row r="173" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="21" t="s">
         <v>385</v>
       </c>
@@ -17994,7 +18022,7 @@
         <v>1135</v>
       </c>
       <c r="C173" s="73" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="D173" s="73" t="s">
         <v>927</v>
@@ -18006,10 +18034,10 @@
         <v>1218</v>
       </c>
       <c r="G173" s="73" t="s">
+        <v>1945</v>
+      </c>
+      <c r="H173" s="73" t="s">
         <v>1948</v>
-      </c>
-      <c r="H173" s="73" t="s">
-        <v>1951</v>
       </c>
       <c r="I173" s="73" t="s">
         <v>374</v>
@@ -18038,7 +18066,7 @@
       <c r="W173" s="33"/>
       <c r="X173" s="33"/>
     </row>
-    <row r="174" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="21" t="s">
         <v>385</v>
       </c>
@@ -18046,22 +18074,22 @@
         <v>1135</v>
       </c>
       <c r="C174" s="73" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="D174" s="73" t="s">
-        <v>1949</v>
+        <v>1946</v>
       </c>
       <c r="E174" s="73" t="s">
-        <v>1950</v>
+        <v>1947</v>
       </c>
       <c r="F174" s="73" t="s">
         <v>1219</v>
       </c>
       <c r="G174" s="73" t="s">
-        <v>1953</v>
+        <v>1950</v>
       </c>
       <c r="H174" s="73" t="s">
-        <v>1952</v>
+        <v>1949</v>
       </c>
       <c r="I174" s="73" t="s">
         <v>374</v>
@@ -18090,7 +18118,7 @@
       <c r="W174" s="33"/>
       <c r="X174" s="33"/>
     </row>
-    <row r="175" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="21" t="s">
         <v>385</v>
       </c>
@@ -18098,7 +18126,7 @@
         <v>1136</v>
       </c>
       <c r="C175" s="74" t="s">
-        <v>1689</v>
+        <v>1686</v>
       </c>
       <c r="D175" s="74" t="s">
         <v>930</v>
@@ -18110,7 +18138,7 @@
         <v>1220</v>
       </c>
       <c r="G175" s="74" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
       <c r="H175" s="74" t="s">
         <v>931</v>
@@ -18144,7 +18172,7 @@
       <c r="W175" s="33"/>
       <c r="X175" s="33"/>
     </row>
-    <row r="176" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="21" t="s">
         <v>385</v>
       </c>
@@ -18152,10 +18180,10 @@
         <v>1136</v>
       </c>
       <c r="C176" s="74" t="s">
-        <v>1964</v>
+        <v>1961</v>
       </c>
       <c r="D176" s="74" t="s">
-        <v>1963</v>
+        <v>1960</v>
       </c>
       <c r="E176" s="74" t="s">
         <v>1005</v>
@@ -18164,7 +18192,7 @@
         <v>1221</v>
       </c>
       <c r="G176" s="74" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
       <c r="H176" s="74" t="s">
         <v>933</v>
@@ -18198,7 +18226,7 @@
       <c r="W176" s="33"/>
       <c r="X176" s="33"/>
     </row>
-    <row r="177" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="21" t="s">
         <v>385</v>
       </c>
@@ -18218,7 +18246,7 @@
         <v>1222</v>
       </c>
       <c r="G177" s="74" t="s">
-        <v>1684</v>
+        <v>1681</v>
       </c>
       <c r="H177" s="74" t="s">
         <v>936</v>
@@ -18230,7 +18258,7 @@
         <v>937</v>
       </c>
       <c r="K177" s="74" t="s">
-        <v>1959</v>
+        <v>1956</v>
       </c>
       <c r="L177" s="74"/>
       <c r="M177" s="74" t="s">
@@ -18252,7 +18280,7 @@
       <c r="W177" s="33"/>
       <c r="X177" s="33"/>
     </row>
-    <row r="178" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="21" t="s">
         <v>385</v>
       </c>
@@ -18263,7 +18291,7 @@
         <v>938</v>
       </c>
       <c r="D178" s="74" t="s">
-        <v>1954</v>
+        <v>1951</v>
       </c>
       <c r="E178" s="74" t="s">
         <v>1007</v>
@@ -18272,7 +18300,7 @@
         <v>1223</v>
       </c>
       <c r="G178" s="74" t="s">
-        <v>1960</v>
+        <v>1957</v>
       </c>
       <c r="H178" s="74" t="s">
         <v>939</v>
@@ -18304,7 +18332,7 @@
       <c r="W178" s="33"/>
       <c r="X178" s="33"/>
     </row>
-    <row r="179" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="21" t="s">
         <v>385</v>
       </c>
@@ -18315,7 +18343,7 @@
         <v>941</v>
       </c>
       <c r="D179" s="74" t="s">
-        <v>1955</v>
+        <v>1952</v>
       </c>
       <c r="E179" s="74" t="s">
         <v>1008</v>
@@ -18324,7 +18352,7 @@
         <v>1224</v>
       </c>
       <c r="G179" s="74" t="s">
-        <v>1685</v>
+        <v>1682</v>
       </c>
       <c r="H179" s="74" t="s">
         <v>942</v>
@@ -18356,7 +18384,7 @@
       <c r="W179" s="33"/>
       <c r="X179" s="33"/>
     </row>
-    <row r="180" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="21" t="s">
         <v>385</v>
       </c>
@@ -18364,10 +18392,10 @@
         <v>1136</v>
       </c>
       <c r="C180" s="74" t="s">
-        <v>1980</v>
+        <v>1977</v>
       </c>
       <c r="D180" s="74" t="s">
-        <v>1956</v>
+        <v>1953</v>
       </c>
       <c r="E180" s="74" t="s">
         <v>1009</v>
@@ -18376,7 +18404,7 @@
         <v>1225</v>
       </c>
       <c r="G180" s="74" t="s">
-        <v>1957</v>
+        <v>1954</v>
       </c>
       <c r="H180" s="74" t="s">
         <v>944</v>
@@ -18410,7 +18438,7 @@
       <c r="W180" s="33"/>
       <c r="X180" s="33"/>
     </row>
-    <row r="181" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="21" t="s">
         <v>385</v>
       </c>
@@ -18418,10 +18446,10 @@
         <v>1136</v>
       </c>
       <c r="C181" s="74" t="s">
-        <v>1981</v>
+        <v>1978</v>
       </c>
       <c r="D181" s="74" t="s">
-        <v>1958</v>
+        <v>1955</v>
       </c>
       <c r="E181" s="74" t="s">
         <v>1010</v>
@@ -18430,7 +18458,7 @@
         <v>1226</v>
       </c>
       <c r="G181" s="74" t="s">
-        <v>1961</v>
+        <v>1958</v>
       </c>
       <c r="H181" s="74" t="s">
         <v>946</v>
@@ -18464,7 +18492,7 @@
       <c r="W181" s="33"/>
       <c r="X181" s="33"/>
     </row>
-    <row r="182" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="21" t="s">
         <v>385</v>
       </c>
@@ -18472,31 +18500,31 @@
         <v>1136</v>
       </c>
       <c r="C182" s="74" t="s">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="D182" s="74" t="s">
+        <v>1959</v>
+      </c>
+      <c r="E182" s="74" t="s">
         <v>1962</v>
       </c>
-      <c r="E182" s="74" t="s">
+      <c r="F182" s="74" t="s">
+        <v>1964</v>
+      </c>
+      <c r="G182" s="74" t="s">
         <v>1965</v>
       </c>
-      <c r="F182" s="74" t="s">
-        <v>1967</v>
-      </c>
-      <c r="G182" s="74" t="s">
-        <v>1968</v>
-      </c>
       <c r="H182" s="74" t="s">
-        <v>1966</v>
+        <v>1963</v>
       </c>
       <c r="I182" s="74" t="s">
         <v>374</v>
       </c>
       <c r="J182" s="74" t="s">
-        <v>1969</v>
+        <v>1966</v>
       </c>
       <c r="K182" s="74" t="s">
-        <v>1970</v>
+        <v>1967</v>
       </c>
       <c r="L182" s="74"/>
       <c r="M182" s="74" t="s">
@@ -18518,7 +18546,7 @@
       <c r="W182" s="33"/>
       <c r="X182" s="33"/>
     </row>
-    <row r="183" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="21" t="s">
         <v>385</v>
       </c>
@@ -18526,28 +18554,28 @@
         <v>1136</v>
       </c>
       <c r="C183" s="74" t="s">
-        <v>1971</v>
+        <v>1968</v>
       </c>
       <c r="D183" s="74" t="s">
-        <v>1977</v>
+        <v>1974</v>
       </c>
       <c r="E183" s="74" t="s">
-        <v>1978</v>
+        <v>1975</v>
       </c>
       <c r="F183" s="74" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="G183" s="74" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
       <c r="H183" s="74" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="I183" s="74" t="s">
         <v>374</v>
       </c>
       <c r="J183" s="74" t="s">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="K183" s="74" t="s">
         <v>251</v>
@@ -18572,7 +18600,7 @@
       <c r="W183" s="33"/>
       <c r="X183" s="33"/>
     </row>
-    <row r="184" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" s="21" t="s">
         <v>385</v>
       </c>
@@ -18580,28 +18608,28 @@
         <v>1136</v>
       </c>
       <c r="C184" s="74" t="s">
-        <v>1976</v>
+        <v>1973</v>
       </c>
       <c r="D184" s="74" t="s">
-        <v>1977</v>
+        <v>1974</v>
       </c>
       <c r="E184" s="74" t="s">
-        <v>1978</v>
+        <v>1975</v>
       </c>
       <c r="F184" s="74" t="s">
-        <v>1975</v>
+        <v>1972</v>
       </c>
       <c r="G184" s="74" t="s">
-        <v>1983</v>
+        <v>1980</v>
       </c>
       <c r="H184" s="74" t="s">
-        <v>1975</v>
+        <v>1972</v>
       </c>
       <c r="I184" s="74" t="s">
         <v>374</v>
       </c>
       <c r="J184" s="74" t="s">
-        <v>1974</v>
+        <v>1971</v>
       </c>
       <c r="K184" s="74" t="s">
         <v>251</v>
@@ -18626,7 +18654,7 @@
       <c r="W184" s="33"/>
       <c r="X184" s="33"/>
     </row>
-    <row r="185" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" s="21" t="s">
         <v>385</v>
       </c>
@@ -18634,7 +18662,7 @@
         <v>1136</v>
       </c>
       <c r="C185" s="74" t="s">
-        <v>1984</v>
+        <v>1981</v>
       </c>
       <c r="D185" s="74" t="s">
         <v>948</v>
@@ -18646,7 +18674,7 @@
         <v>1227</v>
       </c>
       <c r="G185" s="74" t="s">
-        <v>1686</v>
+        <v>1683</v>
       </c>
       <c r="H185" s="74" t="s">
         <v>949</v>
@@ -18680,7 +18708,7 @@
       <c r="W185" s="33"/>
       <c r="X185" s="33"/>
     </row>
-    <row r="186" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" s="21" t="s">
         <v>385</v>
       </c>
@@ -18694,13 +18722,13 @@
         <v>952</v>
       </c>
       <c r="E186" s="74" t="s">
-        <v>1989</v>
+        <v>1986</v>
       </c>
       <c r="F186" s="74" t="s">
         <v>1228</v>
       </c>
       <c r="G186" s="74" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="H186" s="74" t="s">
         <v>953</v>
@@ -18734,7 +18762,7 @@
       <c r="W186" s="33"/>
       <c r="X186" s="33"/>
     </row>
-    <row r="187" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="21" t="s">
         <v>385</v>
       </c>
@@ -18742,19 +18770,19 @@
         <v>1136</v>
       </c>
       <c r="C187" s="74" t="s">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="D187" s="74" t="s">
         <v>965</v>
       </c>
       <c r="E187" s="74" t="s">
-        <v>1990</v>
+        <v>1987</v>
       </c>
       <c r="F187" s="74" t="s">
         <v>1229</v>
       </c>
       <c r="G187" s="74" t="s">
-        <v>1986</v>
+        <v>1983</v>
       </c>
       <c r="H187" s="74" t="s">
         <v>955</v>
@@ -18766,7 +18794,7 @@
         <v>956</v>
       </c>
       <c r="K187" s="74" t="s">
-        <v>1987</v>
+        <v>1984</v>
       </c>
       <c r="L187" s="74"/>
       <c r="M187" s="74" t="s">
@@ -18788,7 +18816,7 @@
       <c r="W187" s="33"/>
       <c r="X187" s="33"/>
     </row>
-    <row r="188" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="21" t="s">
         <v>385</v>
       </c>
@@ -18796,31 +18824,31 @@
         <v>1136</v>
       </c>
       <c r="C188" s="74" t="s">
-        <v>1994</v>
+        <v>1991</v>
       </c>
       <c r="D188" s="74" t="s">
-        <v>1996</v>
+        <v>1993</v>
       </c>
       <c r="E188" s="74" t="s">
-        <v>1991</v>
+        <v>1988</v>
       </c>
       <c r="F188" s="74" t="s">
+        <v>1995</v>
+      </c>
+      <c r="G188" s="74" t="s">
         <v>1998</v>
       </c>
-      <c r="G188" s="74" t="s">
-        <v>2001</v>
-      </c>
       <c r="H188" s="74" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="I188" s="74" t="s">
         <v>374</v>
       </c>
       <c r="J188" s="74" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="K188" s="74" t="s">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="L188" s="74"/>
       <c r="M188" s="74" t="s">
@@ -18842,7 +18870,7 @@
       <c r="W188" s="33"/>
       <c r="X188" s="33"/>
     </row>
-    <row r="189" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" s="21" t="s">
         <v>385</v>
       </c>
@@ -18850,28 +18878,28 @@
         <v>1136</v>
       </c>
       <c r="C189" s="74" t="s">
-        <v>1995</v>
+        <v>1992</v>
       </c>
       <c r="D189" s="74" t="s">
-        <v>1997</v>
+        <v>1994</v>
       </c>
       <c r="E189" s="74" t="s">
-        <v>1992</v>
+        <v>1989</v>
       </c>
       <c r="F189" s="74" t="s">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="G189" s="74" t="s">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="H189" s="74" t="s">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="I189" s="74" t="s">
         <v>374</v>
       </c>
       <c r="J189" s="74" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="K189" s="74" t="s">
         <v>977</v>
@@ -18896,7 +18924,7 @@
       <c r="W189" s="33"/>
       <c r="X189" s="33"/>
     </row>
-    <row r="190" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" s="21" t="s">
         <v>385</v>
       </c>
@@ -18904,19 +18932,19 @@
         <v>1136</v>
       </c>
       <c r="C190" s="74" t="s">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="D190" s="74" t="s">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="E190" s="74" t="s">
-        <v>1993</v>
+        <v>1990</v>
       </c>
       <c r="F190" s="74" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="G190" s="74" t="s">
-        <v>1687</v>
+        <v>1684</v>
       </c>
       <c r="H190" s="74" t="s">
         <v>958</v>
@@ -18925,10 +18953,10 @@
         <v>374</v>
       </c>
       <c r="J190" s="74" t="s">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="K190" s="74" t="s">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="L190" s="74"/>
       <c r="M190" s="74" t="s">
@@ -18950,7 +18978,7 @@
       <c r="W190" s="33"/>
       <c r="X190" s="33"/>
     </row>
-    <row r="191" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" s="21" t="s">
         <v>385</v>
       </c>
@@ -18961,16 +18989,16 @@
         <v>957</v>
       </c>
       <c r="D191" s="74" t="s">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="E191" s="74" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="F191" s="74" t="s">
         <v>1230</v>
       </c>
       <c r="G191" s="74" t="s">
-        <v>1687</v>
+        <v>1684</v>
       </c>
       <c r="H191" s="74" t="s">
         <v>958</v>
@@ -19004,7 +19032,7 @@
       <c r="W191" s="33"/>
       <c r="X191" s="33"/>
     </row>
-    <row r="192" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" s="21" t="s">
         <v>385</v>
       </c>
@@ -19012,19 +19040,19 @@
         <v>1136</v>
       </c>
       <c r="C192" s="74" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="D192" s="74" t="s">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="E192" s="74" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="F192" s="74" t="s">
         <v>1231</v>
       </c>
       <c r="G192" s="74" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="H192" s="74" t="s">
         <v>960</v>
@@ -19033,7 +19061,7 @@
         <v>374</v>
       </c>
       <c r="J192" s="74" t="s">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="K192" s="74" t="s">
         <v>976</v>
@@ -19058,7 +19086,7 @@
       <c r="W192" s="33"/>
       <c r="X192" s="33"/>
     </row>
-    <row r="193" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" s="21" t="s">
         <v>385</v>
       </c>
@@ -19069,7 +19097,7 @@
         <v>961</v>
       </c>
       <c r="D193" s="74" t="s">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="E193" s="74" t="s">
         <v>1012</v>
@@ -19078,7 +19106,7 @@
         <v>1232</v>
       </c>
       <c r="G193" s="74" t="s">
-        <v>1688</v>
+        <v>1685</v>
       </c>
       <c r="H193" s="74" t="s">
         <v>962</v>
@@ -19112,36 +19140,36 @@
       <c r="W193" s="33"/>
       <c r="X193" s="33"/>
     </row>
-    <row r="194" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="75" t="s">
         <v>385</v>
       </c>
       <c r="B194" s="76" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C194" s="46" t="s">
+        <v>1735</v>
+      </c>
+      <c r="D194" s="46" t="s">
+        <v>1736</v>
+      </c>
+      <c r="E194" s="50" t="s">
         <v>1737</v>
       </c>
-      <c r="C194" s="46" t="s">
+      <c r="F194" s="46" t="s">
         <v>1738</v>
       </c>
-      <c r="D194" s="46" t="s">
+      <c r="G194" s="46" t="s">
         <v>1739</v>
       </c>
-      <c r="E194" s="50" t="s">
+      <c r="H194" s="46" t="s">
         <v>1740</v>
-      </c>
-      <c r="F194" s="46" t="s">
-        <v>1741</v>
-      </c>
-      <c r="G194" s="46" t="s">
-        <v>1742</v>
-      </c>
-      <c r="H194" s="46" t="s">
-        <v>1743</v>
       </c>
       <c r="I194" s="46" t="s">
         <v>374</v>
       </c>
       <c r="J194" s="46" t="s">
-        <v>1744</v>
+        <v>1741</v>
       </c>
       <c r="K194" s="46"/>
       <c r="L194" s="46"/>
@@ -19164,36 +19192,36 @@
       <c r="W194" s="69"/>
       <c r="X194" s="69"/>
     </row>
-    <row r="195" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="75" t="s">
         <v>385</v>
       </c>
       <c r="B195" s="76" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="C195" s="46" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D195" s="46" t="s">
+        <v>1743</v>
+      </c>
+      <c r="E195" s="50" t="s">
+        <v>1744</v>
+      </c>
+      <c r="F195" s="46" t="s">
         <v>1745</v>
       </c>
-      <c r="D195" s="46" t="s">
+      <c r="G195" s="46" t="s">
         <v>1746</v>
       </c>
-      <c r="E195" s="50" t="s">
+      <c r="H195" s="46" t="s">
         <v>1747</v>
-      </c>
-      <c r="F195" s="46" t="s">
-        <v>1748</v>
-      </c>
-      <c r="G195" s="46" t="s">
-        <v>1749</v>
-      </c>
-      <c r="H195" s="46" t="s">
-        <v>1750</v>
       </c>
       <c r="I195" s="46" t="s">
         <v>374</v>
       </c>
       <c r="J195" s="46" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
       <c r="K195" s="46"/>
       <c r="L195" s="46"/>
@@ -19216,36 +19244,36 @@
       <c r="W195" s="69"/>
       <c r="X195" s="69"/>
     </row>
-    <row r="196" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="75" t="s">
         <v>385</v>
       </c>
       <c r="B196" s="76" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="C196" s="46" t="s">
+        <v>1749</v>
+      </c>
+      <c r="D196" s="46" t="s">
+        <v>1750</v>
+      </c>
+      <c r="E196" s="50" t="s">
+        <v>1751</v>
+      </c>
+      <c r="F196" s="46" t="s">
         <v>1752</v>
       </c>
-      <c r="D196" s="46" t="s">
+      <c r="G196" s="46" t="s">
         <v>1753</v>
       </c>
-      <c r="E196" s="50" t="s">
+      <c r="H196" s="46" t="s">
         <v>1754</v>
-      </c>
-      <c r="F196" s="46" t="s">
-        <v>1755</v>
-      </c>
-      <c r="G196" s="46" t="s">
-        <v>1756</v>
-      </c>
-      <c r="H196" s="46" t="s">
-        <v>1757</v>
       </c>
       <c r="I196" s="46" t="s">
         <v>374</v>
       </c>
       <c r="J196" s="46" t="s">
-        <v>1758</v>
+        <v>1755</v>
       </c>
       <c r="K196" s="46"/>
       <c r="L196" s="46"/>
@@ -19268,39 +19296,39 @@
       <c r="W196" s="69"/>
       <c r="X196" s="69"/>
     </row>
-    <row r="197" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="75" t="s">
         <v>385</v>
       </c>
       <c r="B197" s="76" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="C197" s="46" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D197" s="46" t="s">
+        <v>1757</v>
+      </c>
+      <c r="E197" s="50" t="s">
+        <v>1758</v>
+      </c>
+      <c r="F197" s="46" t="s">
         <v>1759</v>
       </c>
-      <c r="D197" s="46" t="s">
+      <c r="G197" s="46" t="s">
         <v>1760</v>
       </c>
-      <c r="E197" s="50" t="s">
+      <c r="H197" s="46" t="s">
         <v>1761</v>
-      </c>
-      <c r="F197" s="46" t="s">
-        <v>1762</v>
-      </c>
-      <c r="G197" s="46" t="s">
-        <v>1763</v>
-      </c>
-      <c r="H197" s="46" t="s">
-        <v>1764</v>
       </c>
       <c r="I197" s="46" t="s">
         <v>374</v>
       </c>
       <c r="J197" s="46" t="s">
-        <v>1765</v>
+        <v>1762</v>
       </c>
       <c r="K197" s="46" t="s">
-        <v>1766</v>
+        <v>1763</v>
       </c>
       <c r="L197" s="46"/>
       <c r="M197" s="46" t="s">
@@ -19322,39 +19350,39 @@
       <c r="W197" s="69"/>
       <c r="X197" s="69"/>
     </row>
-    <row r="198" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="75" t="s">
         <v>385</v>
       </c>
       <c r="B198" s="76" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="C198" s="46" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D198" s="46" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E198" s="50" t="s">
+        <v>1766</v>
+      </c>
+      <c r="F198" s="46" t="s">
         <v>1767</v>
       </c>
-      <c r="D198" s="46" t="s">
+      <c r="G198" s="46" t="s">
         <v>1768</v>
       </c>
-      <c r="E198" s="50" t="s">
+      <c r="H198" s="46" t="s">
         <v>1769</v>
-      </c>
-      <c r="F198" s="46" t="s">
-        <v>1770</v>
-      </c>
-      <c r="G198" s="46" t="s">
-        <v>1771</v>
-      </c>
-      <c r="H198" s="46" t="s">
-        <v>1772</v>
       </c>
       <c r="I198" s="46" t="s">
         <v>374</v>
       </c>
       <c r="J198" s="46" t="s">
-        <v>1773</v>
+        <v>1770</v>
       </c>
       <c r="K198" s="46" t="s">
-        <v>1774</v>
+        <v>1771</v>
       </c>
       <c r="L198" s="46"/>
       <c r="M198" s="46" t="s">
@@ -19376,36 +19404,36 @@
       <c r="W198" s="69"/>
       <c r="X198" s="69"/>
     </row>
-    <row r="199" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="75" t="s">
         <v>385</v>
       </c>
       <c r="B199" s="76" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="C199" s="46" t="s">
+        <v>1772</v>
+      </c>
+      <c r="D199" s="46" t="s">
+        <v>1773</v>
+      </c>
+      <c r="E199" s="50" t="s">
+        <v>1774</v>
+      </c>
+      <c r="F199" s="46" t="s">
         <v>1775</v>
       </c>
-      <c r="D199" s="46" t="s">
+      <c r="G199" s="46" t="s">
         <v>1776</v>
       </c>
-      <c r="E199" s="50" t="s">
+      <c r="H199" s="46" t="s">
         <v>1777</v>
-      </c>
-      <c r="F199" s="46" t="s">
-        <v>1778</v>
-      </c>
-      <c r="G199" s="46" t="s">
-        <v>1779</v>
-      </c>
-      <c r="H199" s="46" t="s">
-        <v>1780</v>
       </c>
       <c r="I199" s="46" t="s">
         <v>374</v>
       </c>
       <c r="J199" s="46" t="s">
-        <v>1781</v>
+        <v>1778</v>
       </c>
       <c r="K199" s="46"/>
       <c r="L199" s="46"/>
@@ -19428,36 +19456,36 @@
       <c r="W199" s="69"/>
       <c r="X199" s="69"/>
     </row>
-    <row r="200" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="75" t="s">
         <v>385</v>
       </c>
       <c r="B200" s="76" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="C200" s="46" t="s">
+        <v>1779</v>
+      </c>
+      <c r="D200" s="46" t="s">
+        <v>1780</v>
+      </c>
+      <c r="E200" s="50" t="s">
+        <v>1781</v>
+      </c>
+      <c r="F200" s="46" t="s">
         <v>1782</v>
       </c>
-      <c r="D200" s="46" t="s">
+      <c r="G200" s="46" t="s">
         <v>1783</v>
       </c>
-      <c r="E200" s="50" t="s">
+      <c r="H200" s="46" t="s">
         <v>1784</v>
-      </c>
-      <c r="F200" s="46" t="s">
-        <v>1785</v>
-      </c>
-      <c r="G200" s="46" t="s">
-        <v>1786</v>
-      </c>
-      <c r="H200" s="46" t="s">
-        <v>1787</v>
       </c>
       <c r="I200" s="46" t="s">
         <v>374</v>
       </c>
       <c r="J200" s="46" t="s">
-        <v>1788</v>
+        <v>1785</v>
       </c>
       <c r="K200" s="46"/>
       <c r="L200" s="46"/>
@@ -19480,39 +19508,39 @@
       <c r="W200" s="69"/>
       <c r="X200" s="69"/>
     </row>
-    <row r="201" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="75" t="s">
         <v>385</v>
       </c>
       <c r="B201" s="76" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="C201" s="46" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D201" s="46" t="s">
+        <v>1787</v>
+      </c>
+      <c r="E201" s="50" t="s">
+        <v>1788</v>
+      </c>
+      <c r="F201" s="46" t="s">
         <v>1789</v>
       </c>
-      <c r="D201" s="46" t="s">
+      <c r="G201" s="46" t="s">
         <v>1790</v>
       </c>
-      <c r="E201" s="50" t="s">
+      <c r="H201" s="46" t="s">
         <v>1791</v>
-      </c>
-      <c r="F201" s="46" t="s">
-        <v>1792</v>
-      </c>
-      <c r="G201" s="46" t="s">
-        <v>1793</v>
-      </c>
-      <c r="H201" s="46" t="s">
-        <v>1794</v>
       </c>
       <c r="I201" s="46" t="s">
         <v>374</v>
       </c>
       <c r="J201" s="46" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="K201" s="46" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="L201" s="46"/>
       <c r="M201" s="46" t="s">
@@ -19534,39 +19562,39 @@
       <c r="W201" s="69"/>
       <c r="X201" s="69"/>
     </row>
-    <row r="202" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="75" t="s">
         <v>385</v>
       </c>
       <c r="B202" s="76" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="C202" s="46" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D202" s="46" t="s">
+        <v>1795</v>
+      </c>
+      <c r="E202" s="50" t="s">
+        <v>1796</v>
+      </c>
+      <c r="F202" s="46" t="s">
         <v>1797</v>
       </c>
-      <c r="D202" s="46" t="s">
+      <c r="G202" s="46" t="s">
         <v>1798</v>
       </c>
-      <c r="E202" s="50" t="s">
+      <c r="H202" s="46" t="s">
         <v>1799</v>
-      </c>
-      <c r="F202" s="46" t="s">
-        <v>1800</v>
-      </c>
-      <c r="G202" s="46" t="s">
-        <v>1801</v>
-      </c>
-      <c r="H202" s="46" t="s">
-        <v>1802</v>
       </c>
       <c r="I202" s="46" t="s">
         <v>374</v>
       </c>
       <c r="J202" s="46" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="K202" s="46" t="s">
-        <v>1804</v>
+        <v>1801</v>
       </c>
       <c r="L202" s="46"/>
       <c r="M202" s="46" t="s">
@@ -19588,36 +19616,36 @@
       <c r="W202" s="69"/>
       <c r="X202" s="69"/>
     </row>
-    <row r="203" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="75" t="s">
         <v>385</v>
       </c>
       <c r="B203" s="76" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="C203" s="46" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D203" s="46" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E203" s="50" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F203" s="46" t="s">
         <v>1805</v>
       </c>
-      <c r="D203" s="46" t="s">
+      <c r="G203" s="46" t="s">
         <v>1806</v>
       </c>
-      <c r="E203" s="50" t="s">
+      <c r="H203" s="46" t="s">
         <v>1807</v>
-      </c>
-      <c r="F203" s="46" t="s">
-        <v>1808</v>
-      </c>
-      <c r="G203" s="46" t="s">
-        <v>1809</v>
-      </c>
-      <c r="H203" s="46" t="s">
-        <v>1810</v>
       </c>
       <c r="I203" s="46" t="s">
         <v>374</v>
       </c>
       <c r="J203" s="46" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="K203" s="46"/>
       <c r="L203" s="46"/>
@@ -19640,39 +19668,39 @@
       <c r="W203" s="69"/>
       <c r="X203" s="69"/>
     </row>
-    <row r="204" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="75" t="s">
         <v>385</v>
       </c>
       <c r="B204" s="76" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="C204" s="46" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D204" s="46" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E204" s="50" t="s">
+        <v>1811</v>
+      </c>
+      <c r="F204" s="46" t="s">
         <v>1812</v>
       </c>
-      <c r="D204" s="46" t="s">
+      <c r="G204" s="46" t="s">
         <v>1813</v>
       </c>
-      <c r="E204" s="50" t="s">
+      <c r="H204" s="46" t="s">
         <v>1814</v>
-      </c>
-      <c r="F204" s="46" t="s">
-        <v>1815</v>
-      </c>
-      <c r="G204" s="46" t="s">
-        <v>1816</v>
-      </c>
-      <c r="H204" s="46" t="s">
-        <v>1817</v>
       </c>
       <c r="I204" s="46" t="s">
         <v>374</v>
       </c>
       <c r="J204" s="46" t="s">
-        <v>1818</v>
+        <v>1815</v>
       </c>
       <c r="K204" s="46" t="s">
-        <v>1774</v>
+        <v>1771</v>
       </c>
       <c r="L204" s="46"/>
       <c r="M204" s="46" t="s">
@@ -19694,36 +19722,36 @@
       <c r="W204" s="69"/>
       <c r="X204" s="69"/>
     </row>
-    <row r="205" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="75" t="s">
         <v>385</v>
       </c>
       <c r="B205" s="76" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="C205" s="46" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D205" s="46" t="s">
+        <v>1817</v>
+      </c>
+      <c r="E205" s="50" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F205" s="46" t="s">
         <v>1819</v>
       </c>
-      <c r="D205" s="46" t="s">
+      <c r="G205" s="46" t="s">
         <v>1820</v>
       </c>
-      <c r="E205" s="50" t="s">
+      <c r="H205" s="46" t="s">
         <v>1821</v>
-      </c>
-      <c r="F205" s="46" t="s">
-        <v>1822</v>
-      </c>
-      <c r="G205" s="46" t="s">
-        <v>1823</v>
-      </c>
-      <c r="H205" s="46" t="s">
-        <v>1824</v>
       </c>
       <c r="I205" s="46" t="s">
         <v>374</v>
       </c>
       <c r="J205" s="46" t="s">
-        <v>1825</v>
+        <v>1822</v>
       </c>
       <c r="K205" s="46"/>
       <c r="L205" s="46"/>
@@ -19746,39 +19774,39 @@
       <c r="W205" s="69"/>
       <c r="X205" s="69"/>
     </row>
-    <row r="206" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="75" t="s">
         <v>385</v>
       </c>
       <c r="B206" s="76" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="C206" s="46" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D206" s="46" t="s">
+        <v>1817</v>
+      </c>
+      <c r="E206" s="50" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F206" s="46" t="s">
+        <v>1824</v>
+      </c>
+      <c r="G206" s="46" t="s">
+        <v>1825</v>
+      </c>
+      <c r="H206" s="46" t="s">
         <v>1826</v>
-      </c>
-      <c r="D206" s="46" t="s">
-        <v>1820</v>
-      </c>
-      <c r="E206" s="50" t="s">
-        <v>1821</v>
-      </c>
-      <c r="F206" s="46" t="s">
-        <v>1827</v>
-      </c>
-      <c r="G206" s="46" t="s">
-        <v>1828</v>
-      </c>
-      <c r="H206" s="46" t="s">
-        <v>1829</v>
       </c>
       <c r="I206" s="46" t="s">
         <v>374</v>
       </c>
       <c r="J206" s="46" t="s">
-        <v>1830</v>
+        <v>1827</v>
       </c>
       <c r="K206" s="46" t="s">
-        <v>1831</v>
+        <v>1828</v>
       </c>
       <c r="L206" s="46"/>
       <c r="M206" s="46" t="s">
@@ -19800,39 +19828,39 @@
       <c r="W206" s="69"/>
       <c r="X206" s="69"/>
     </row>
-    <row r="207" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:24" s="6" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="75" t="s">
         <v>385</v>
       </c>
       <c r="B207" s="76" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="C207" s="46" t="s">
-        <v>1832</v>
+        <v>1829</v>
       </c>
       <c r="D207" s="46" t="s">
-        <v>1820</v>
+        <v>1817</v>
       </c>
       <c r="E207" s="50" t="s">
-        <v>1821</v>
+        <v>1818</v>
       </c>
       <c r="F207" s="46" t="s">
-        <v>1833</v>
+        <v>1830</v>
       </c>
       <c r="G207" s="46" t="s">
-        <v>1822</v>
+        <v>1819</v>
       </c>
       <c r="H207" s="46" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="I207" s="46" t="s">
         <v>374</v>
       </c>
       <c r="J207" s="46" t="s">
-        <v>1835</v>
+        <v>1832</v>
       </c>
       <c r="K207" s="46" t="s">
-        <v>1774</v>
+        <v>1771</v>
       </c>
       <c r="L207" s="46"/>
       <c r="M207" s="46" t="s">
@@ -19854,39 +19882,39 @@
       <c r="W207" s="69"/>
       <c r="X207" s="69"/>
     </row>
-    <row r="208" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="21" t="s">
         <v>385</v>
       </c>
       <c r="B208" s="47" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C208" s="47" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D208" s="47" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E208" s="77" t="s">
         <v>1836</v>
       </c>
-      <c r="C208" s="47" t="s">
+      <c r="F208" s="47" t="s">
         <v>1837</v>
       </c>
-      <c r="D208" s="47" t="s">
+      <c r="G208" s="47" t="s">
         <v>1838</v>
       </c>
-      <c r="E208" s="77" t="s">
+      <c r="H208" s="47" t="s">
         <v>1839</v>
-      </c>
-      <c r="F208" s="47" t="s">
-        <v>1840</v>
-      </c>
-      <c r="G208" s="47" t="s">
-        <v>1841</v>
-      </c>
-      <c r="H208" s="47" t="s">
-        <v>1842</v>
       </c>
       <c r="I208" s="47" t="s">
         <v>374</v>
       </c>
       <c r="J208" s="47" t="s">
-        <v>1843</v>
+        <v>1840</v>
       </c>
       <c r="K208" s="47" t="s">
-        <v>1844</v>
+        <v>1841</v>
       </c>
       <c r="L208" s="47"/>
       <c r="M208" s="47" t="s">
@@ -19908,36 +19936,36 @@
       <c r="W208" s="33"/>
       <c r="X208" s="33"/>
     </row>
-    <row r="209" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="21" t="s">
         <v>385</v>
       </c>
       <c r="B209" s="47" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
       <c r="C209" s="47" t="s">
+        <v>1842</v>
+      </c>
+      <c r="D209" s="47" t="s">
+        <v>1843</v>
+      </c>
+      <c r="E209" s="77" t="s">
+        <v>1844</v>
+      </c>
+      <c r="F209" s="47" t="s">
         <v>1845</v>
       </c>
-      <c r="D209" s="47" t="s">
+      <c r="G209" s="47" t="s">
         <v>1846</v>
       </c>
-      <c r="E209" s="77" t="s">
+      <c r="H209" s="47" t="s">
         <v>1847</v>
-      </c>
-      <c r="F209" s="47" t="s">
-        <v>1848</v>
-      </c>
-      <c r="G209" s="47" t="s">
-        <v>1849</v>
-      </c>
-      <c r="H209" s="47" t="s">
-        <v>1850</v>
       </c>
       <c r="I209" s="47" t="s">
         <v>374</v>
       </c>
       <c r="J209" s="47" t="s">
-        <v>1851</v>
+        <v>1848</v>
       </c>
       <c r="K209" s="47"/>
       <c r="L209" s="47"/>
@@ -19960,39 +19988,39 @@
       <c r="W209" s="33"/>
       <c r="X209" s="33"/>
     </row>
-    <row r="210" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="21" t="s">
         <v>385</v>
       </c>
       <c r="B210" s="47" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
       <c r="C210" s="47" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D210" s="47" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E210" s="77" t="s">
+        <v>1851</v>
+      </c>
+      <c r="F210" s="47" t="s">
         <v>1852</v>
       </c>
-      <c r="D210" s="47" t="s">
+      <c r="G210" s="47" t="s">
         <v>1853</v>
       </c>
-      <c r="E210" s="77" t="s">
+      <c r="H210" s="47" t="s">
         <v>1854</v>
-      </c>
-      <c r="F210" s="47" t="s">
-        <v>1855</v>
-      </c>
-      <c r="G210" s="47" t="s">
-        <v>1856</v>
-      </c>
-      <c r="H210" s="47" t="s">
-        <v>1857</v>
       </c>
       <c r="I210" s="47" t="s">
         <v>374</v>
       </c>
       <c r="J210" s="47" t="s">
-        <v>1858</v>
+        <v>1855</v>
       </c>
       <c r="K210" s="47" t="s">
-        <v>1774</v>
+        <v>1771</v>
       </c>
       <c r="L210" s="47"/>
       <c r="M210" s="47" t="s">
@@ -20014,36 +20042,36 @@
       <c r="W210" s="33"/>
       <c r="X210" s="33"/>
     </row>
-    <row r="211" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="21" t="s">
         <v>385</v>
       </c>
       <c r="B211" s="47" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
       <c r="C211" s="47" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D211" s="47" t="s">
+        <v>1857</v>
+      </c>
+      <c r="E211" s="77" t="s">
+        <v>1858</v>
+      </c>
+      <c r="F211" s="47" t="s">
         <v>1859</v>
       </c>
-      <c r="D211" s="47" t="s">
+      <c r="G211" s="47" t="s">
         <v>1860</v>
       </c>
-      <c r="E211" s="77" t="s">
+      <c r="H211" s="47" t="s">
         <v>1861</v>
-      </c>
-      <c r="F211" s="47" t="s">
-        <v>1862</v>
-      </c>
-      <c r="G211" s="47" t="s">
-        <v>1863</v>
-      </c>
-      <c r="H211" s="47" t="s">
-        <v>1864</v>
       </c>
       <c r="I211" s="47" t="s">
         <v>374</v>
       </c>
       <c r="J211" s="47" t="s">
-        <v>1865</v>
+        <v>1862</v>
       </c>
       <c r="K211" s="47"/>
       <c r="L211" s="47"/>
@@ -20066,39 +20094,39 @@
       <c r="W211" s="33"/>
       <c r="X211" s="33"/>
     </row>
-    <row r="212" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="21" t="s">
         <v>385</v>
       </c>
       <c r="B212" s="47" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
       <c r="C212" s="47" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D212" s="47" t="s">
+        <v>1864</v>
+      </c>
+      <c r="E212" s="77" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F212" s="47" t="s">
         <v>1866</v>
       </c>
-      <c r="D212" s="47" t="s">
+      <c r="G212" s="47" t="s">
         <v>1867</v>
       </c>
-      <c r="E212" s="77" t="s">
+      <c r="H212" s="47" t="s">
         <v>1868</v>
-      </c>
-      <c r="F212" s="47" t="s">
-        <v>1869</v>
-      </c>
-      <c r="G212" s="47" t="s">
-        <v>1870</v>
-      </c>
-      <c r="H212" s="47" t="s">
-        <v>1871</v>
       </c>
       <c r="I212" s="47" t="s">
         <v>374</v>
       </c>
       <c r="J212" s="47" t="s">
-        <v>1872</v>
+        <v>1869</v>
       </c>
       <c r="K212" s="47" t="s">
-        <v>1873</v>
+        <v>1870</v>
       </c>
       <c r="L212" s="47"/>
       <c r="M212" s="47" t="s">
@@ -20120,36 +20148,36 @@
       <c r="W212" s="33"/>
       <c r="X212" s="33"/>
     </row>
-    <row r="213" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="21" t="s">
         <v>385</v>
       </c>
       <c r="B213" s="47" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
       <c r="C213" s="47" t="s">
+        <v>1871</v>
+      </c>
+      <c r="D213" s="47" t="s">
+        <v>1872</v>
+      </c>
+      <c r="E213" s="77" t="s">
+        <v>1873</v>
+      </c>
+      <c r="F213" s="47" t="s">
         <v>1874</v>
       </c>
-      <c r="D213" s="47" t="s">
+      <c r="G213" s="47" t="s">
         <v>1875</v>
       </c>
-      <c r="E213" s="77" t="s">
+      <c r="H213" s="47" t="s">
         <v>1876</v>
-      </c>
-      <c r="F213" s="47" t="s">
-        <v>1877</v>
-      </c>
-      <c r="G213" s="47" t="s">
-        <v>1878</v>
-      </c>
-      <c r="H213" s="47" t="s">
-        <v>1879</v>
       </c>
       <c r="I213" s="47" t="s">
         <v>374</v>
       </c>
       <c r="J213" s="47" t="s">
-        <v>1880</v>
+        <v>1877</v>
       </c>
       <c r="K213" s="47"/>
       <c r="L213" s="47"/>
@@ -20172,39 +20200,39 @@
       <c r="W213" s="33"/>
       <c r="X213" s="33"/>
     </row>
-    <row r="214" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="21" t="s">
         <v>385</v>
       </c>
       <c r="B214" s="47" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
       <c r="C214" s="47" t="s">
+        <v>1878</v>
+      </c>
+      <c r="D214" s="47" t="s">
+        <v>1879</v>
+      </c>
+      <c r="E214" s="77" t="s">
+        <v>1880</v>
+      </c>
+      <c r="F214" s="47" t="s">
         <v>1881</v>
       </c>
-      <c r="D214" s="47" t="s">
+      <c r="G214" s="47" t="s">
         <v>1882</v>
       </c>
-      <c r="E214" s="77" t="s">
+      <c r="H214" s="47" t="s">
         <v>1883</v>
-      </c>
-      <c r="F214" s="47" t="s">
-        <v>1884</v>
-      </c>
-      <c r="G214" s="47" t="s">
-        <v>1885</v>
-      </c>
-      <c r="H214" s="47" t="s">
-        <v>1886</v>
       </c>
       <c r="I214" s="47" t="s">
         <v>374</v>
       </c>
       <c r="J214" s="47" t="s">
-        <v>1887</v>
+        <v>1884</v>
       </c>
       <c r="K214" s="47" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
       <c r="L214" s="47"/>
       <c r="M214" s="47" t="s">
@@ -20226,39 +20254,39 @@
       <c r="W214" s="33"/>
       <c r="X214" s="33"/>
     </row>
-    <row r="215" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="21" t="s">
         <v>385</v>
       </c>
       <c r="B215" s="47" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
       <c r="C215" s="47" t="s">
+        <v>1886</v>
+      </c>
+      <c r="D215" s="47" t="s">
+        <v>1887</v>
+      </c>
+      <c r="E215" s="77" t="s">
+        <v>1888</v>
+      </c>
+      <c r="F215" s="47" t="s">
         <v>1889</v>
       </c>
-      <c r="D215" s="47" t="s">
+      <c r="G215" s="47" t="s">
         <v>1890</v>
       </c>
-      <c r="E215" s="77" t="s">
+      <c r="H215" s="47" t="s">
         <v>1891</v>
-      </c>
-      <c r="F215" s="47" t="s">
-        <v>1892</v>
-      </c>
-      <c r="G215" s="47" t="s">
-        <v>1893</v>
-      </c>
-      <c r="H215" s="47" t="s">
-        <v>1894</v>
       </c>
       <c r="I215" s="47" t="s">
         <v>374</v>
       </c>
       <c r="J215" s="47" t="s">
-        <v>1895</v>
+        <v>1892</v>
       </c>
       <c r="K215" s="47" t="s">
-        <v>1896</v>
+        <v>1893</v>
       </c>
       <c r="L215" s="47"/>
       <c r="M215" s="47" t="s">
@@ -20280,39 +20308,39 @@
       <c r="W215" s="33"/>
       <c r="X215" s="33"/>
     </row>
-    <row r="216" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="21" t="s">
         <v>385</v>
       </c>
       <c r="B216" s="47" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
       <c r="C216" s="47" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D216" s="47" t="s">
+        <v>1887</v>
+      </c>
+      <c r="E216" s="77" t="s">
+        <v>1888</v>
+      </c>
+      <c r="F216" s="47" t="s">
+        <v>1895</v>
+      </c>
+      <c r="G216" s="47" t="s">
+        <v>1896</v>
+      </c>
+      <c r="H216" s="47" t="s">
         <v>1897</v>
-      </c>
-      <c r="D216" s="47" t="s">
-        <v>1890</v>
-      </c>
-      <c r="E216" s="77" t="s">
-        <v>1891</v>
-      </c>
-      <c r="F216" s="47" t="s">
-        <v>1898</v>
-      </c>
-      <c r="G216" s="47" t="s">
-        <v>1899</v>
-      </c>
-      <c r="H216" s="47" t="s">
-        <v>1900</v>
       </c>
       <c r="I216" s="47" t="s">
         <v>374</v>
       </c>
       <c r="J216" s="47" t="s">
-        <v>1901</v>
+        <v>1898</v>
       </c>
       <c r="K216" s="47" t="s">
-        <v>1831</v>
+        <v>1828</v>
       </c>
       <c r="L216" s="47"/>
       <c r="M216" s="47" t="s">
@@ -20334,39 +20362,39 @@
       <c r="W216" s="33"/>
       <c r="X216" s="33"/>
     </row>
-    <row r="217" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="21" t="s">
         <v>385</v>
       </c>
       <c r="B217" s="47" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
       <c r="C217" s="47" t="s">
+        <v>1899</v>
+      </c>
+      <c r="D217" s="47" t="s">
+        <v>1900</v>
+      </c>
+      <c r="E217" s="77" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F217" s="47" t="s">
         <v>1902</v>
       </c>
-      <c r="D217" s="47" t="s">
+      <c r="G217" s="47" t="s">
         <v>1903</v>
       </c>
-      <c r="E217" s="77" t="s">
+      <c r="H217" s="47" t="s">
         <v>1904</v>
-      </c>
-      <c r="F217" s="47" t="s">
-        <v>1905</v>
-      </c>
-      <c r="G217" s="47" t="s">
-        <v>1906</v>
-      </c>
-      <c r="H217" s="47" t="s">
-        <v>1907</v>
       </c>
       <c r="I217" s="47" t="s">
         <v>374</v>
       </c>
       <c r="J217" s="47" t="s">
-        <v>1818</v>
+        <v>1815</v>
       </c>
       <c r="K217" s="47" t="s">
-        <v>1774</v>
+        <v>1771</v>
       </c>
       <c r="L217" s="47"/>
       <c r="M217" s="47" t="s">
@@ -20388,39 +20416,39 @@
       <c r="W217" s="33"/>
       <c r="X217" s="33"/>
     </row>
-    <row r="218" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:24" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="21" t="s">
         <v>385</v>
       </c>
       <c r="B218" s="47" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
       <c r="C218" s="47" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D218" s="47" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E218" s="77" t="s">
+        <v>1906</v>
+      </c>
+      <c r="F218" s="47" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G218" s="47" t="s">
         <v>1908</v>
       </c>
-      <c r="D218" s="47" t="s">
-        <v>2027</v>
-      </c>
-      <c r="E218" s="77" t="s">
+      <c r="H218" s="47" t="s">
         <v>1909</v>
-      </c>
-      <c r="F218" s="47" t="s">
-        <v>1910</v>
-      </c>
-      <c r="G218" s="47" t="s">
-        <v>1911</v>
-      </c>
-      <c r="H218" s="47" t="s">
-        <v>1912</v>
       </c>
       <c r="I218" s="47" t="s">
         <v>374</v>
       </c>
       <c r="J218" s="47" t="s">
-        <v>1913</v>
+        <v>1910</v>
       </c>
       <c r="K218" s="47" t="s">
-        <v>1914</v>
+        <v>1911</v>
       </c>
       <c r="L218" s="47"/>
       <c r="M218" s="47" t="s">
@@ -20442,7 +20470,7 @@
       <c r="W218" s="33"/>
       <c r="X218" s="33"/>
     </row>
-    <row r="219" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="21" t="s">
         <v>385</v>
       </c>
@@ -20505,10 +20533,10 @@
         <v>1035</v>
       </c>
       <c r="X219" s="62" t="s">
-        <v>2073</v>
-      </c>
-    </row>
-    <row r="220" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="220" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="21" t="s">
         <v>385</v>
       </c>
@@ -20571,10 +20599,10 @@
         <v>1035</v>
       </c>
       <c r="X220" s="62" t="s">
-        <v>2073</v>
-      </c>
-    </row>
-    <row r="221" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="221" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="21" t="s">
         <v>385</v>
       </c>
@@ -20630,7 +20658,7 @@
       <c r="W221" s="33"/>
       <c r="X221" s="33"/>
     </row>
-    <row r="222" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="21" t="s">
         <v>385</v>
       </c>
@@ -20682,7 +20710,7 @@
       <c r="W222" s="33"/>
       <c r="X222" s="33"/>
     </row>
-    <row r="223" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="21" t="s">
         <v>385</v>
       </c>
@@ -20747,10 +20775,10 @@
         <v>1035</v>
       </c>
       <c r="X223" s="62" t="s">
-        <v>2073</v>
-      </c>
-    </row>
-    <row r="224" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="224" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="21" t="s">
         <v>385</v>
       </c>
@@ -20802,7 +20830,7 @@
       <c r="W224" s="33"/>
       <c r="X224" s="33"/>
     </row>
-    <row r="225" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="21" t="s">
         <v>385</v>
       </c>
@@ -20872,7 +20900,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="226" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="21" t="s">
         <v>385</v>
       </c>
@@ -20942,7 +20970,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="227" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="21" t="s">
         <v>385</v>
       </c>
@@ -21012,7 +21040,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="228" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="21" t="s">
         <v>385</v>
       </c>
@@ -21066,7 +21094,7 @@
       <c r="W228" s="33"/>
       <c r="X228" s="33"/>
     </row>
-    <row r="229" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="21" t="s">
         <v>385</v>
       </c>
@@ -21120,7 +21148,7 @@
       <c r="W229" s="33"/>
       <c r="X229" s="33"/>
     </row>
-    <row r="230" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="21" t="s">
         <v>385</v>
       </c>
@@ -21174,7 +21202,7 @@
       <c r="W230" s="33"/>
       <c r="X230" s="33"/>
     </row>
-    <row r="231" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="21" t="s">
         <v>385</v>
       </c>
@@ -21240,7 +21268,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="232" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="21" t="s">
         <v>385</v>
       </c>
@@ -21310,7 +21338,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="233" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="21" t="s">
         <v>385</v>
       </c>
@@ -21380,7 +21408,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="234" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="21" t="s">
         <v>385</v>
       </c>
@@ -21446,7 +21474,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="235" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" s="21" t="s">
         <v>385</v>
       </c>
@@ -21500,7 +21528,7 @@
       <c r="W235" s="33"/>
       <c r="X235" s="33"/>
     </row>
-    <row r="236" spans="1:24" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:24" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" s="21" t="s">
         <v>385</v>
       </c>
@@ -21566,39 +21594,39 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="237" spans="1:24" s="27" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:24" s="27" customFormat="1" ht="16" x14ac:dyDescent="0.4">
       <c r="A237" s="21" t="s">
         <v>385</v>
       </c>
       <c r="B237" s="22" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C237" s="22" t="s">
+        <v>2028</v>
+      </c>
+      <c r="D237" s="23" t="s">
+        <v>2029</v>
+      </c>
+      <c r="E237" s="23" t="s">
         <v>2030</v>
       </c>
-      <c r="C237" s="22" t="s">
+      <c r="F237" s="23" t="s">
         <v>2031</v>
       </c>
-      <c r="D237" s="23" t="s">
+      <c r="G237" s="23" t="s">
         <v>2032</v>
       </c>
-      <c r="E237" s="23" t="s">
+      <c r="H237" s="23" t="s">
         <v>2033</v>
-      </c>
-      <c r="F237" s="23" t="s">
-        <v>2034</v>
-      </c>
-      <c r="G237" s="23" t="s">
-        <v>2035</v>
-      </c>
-      <c r="H237" s="23" t="s">
-        <v>2036</v>
       </c>
       <c r="I237" s="23" t="s">
         <v>379</v>
       </c>
       <c r="J237" s="23" t="s">
-        <v>2037</v>
+        <v>2034</v>
       </c>
       <c r="K237" s="23" t="s">
-        <v>2038</v>
+        <v>2035</v>
       </c>
       <c r="L237" s="23"/>
       <c r="M237" s="23" t="s">
@@ -21614,36 +21642,36 @@
         <v>581</v>
       </c>
     </row>
-    <row r="238" spans="1:24" s="27" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:24" s="27" customFormat="1" ht="16" x14ac:dyDescent="0.4">
       <c r="A238" s="21" t="s">
         <v>385</v>
       </c>
       <c r="B238" s="22" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C238" s="22" t="s">
+        <v>2036</v>
+      </c>
+      <c r="D238" s="23" t="s">
+        <v>2029</v>
+      </c>
+      <c r="E238" s="23" t="s">
         <v>2030</v>
       </c>
-      <c r="C238" s="22" t="s">
-        <v>2039</v>
-      </c>
-      <c r="D238" s="23" t="s">
+      <c r="F238" s="23" t="s">
+        <v>2037</v>
+      </c>
+      <c r="G238" s="23" t="s">
         <v>2032</v>
       </c>
-      <c r="E238" s="23" t="s">
+      <c r="H238" s="23" t="s">
         <v>2033</v>
-      </c>
-      <c r="F238" s="23" t="s">
-        <v>2040</v>
-      </c>
-      <c r="G238" s="23" t="s">
-        <v>2035</v>
-      </c>
-      <c r="H238" s="23" t="s">
-        <v>2036</v>
       </c>
       <c r="I238" s="23" t="s">
         <v>379</v>
       </c>
       <c r="J238" s="23" t="s">
-        <v>2041</v>
+        <v>2038</v>
       </c>
       <c r="K238" s="23"/>
       <c r="L238" s="23"/>
@@ -21660,36 +21688,36 @@
         <v>581</v>
       </c>
     </row>
-    <row r="239" spans="1:24" s="27" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:24" s="27" customFormat="1" ht="16" x14ac:dyDescent="0.4">
       <c r="A239" s="21" t="s">
         <v>385</v>
       </c>
       <c r="B239" s="22" t="s">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="C239" s="22" t="s">
+        <v>2039</v>
+      </c>
+      <c r="D239" s="23" t="s">
+        <v>2040</v>
+      </c>
+      <c r="E239" s="23" t="s">
+        <v>2041</v>
+      </c>
+      <c r="F239" s="23" t="s">
         <v>2042</v>
       </c>
-      <c r="D239" s="23" t="s">
+      <c r="G239" s="23" t="s">
         <v>2043</v>
       </c>
-      <c r="E239" s="23" t="s">
-        <v>2044</v>
-      </c>
-      <c r="F239" s="23" t="s">
-        <v>2045</v>
-      </c>
-      <c r="G239" s="23" t="s">
-        <v>2046</v>
-      </c>
       <c r="H239" s="23" t="s">
-        <v>2036</v>
+        <v>2033</v>
       </c>
       <c r="I239" s="23" t="s">
         <v>379</v>
       </c>
       <c r="J239" s="23" t="s">
-        <v>2047</v>
+        <v>2044</v>
       </c>
       <c r="K239" s="23"/>
       <c r="L239" s="23"/>
@@ -21706,36 +21734,36 @@
         <v>581</v>
       </c>
     </row>
-    <row r="240" spans="1:24" s="27" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:24" s="27" customFormat="1" ht="16" x14ac:dyDescent="0.4">
       <c r="A240" s="21" t="s">
         <v>385</v>
       </c>
       <c r="B240" s="22" t="s">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="C240" s="22" t="s">
+        <v>2045</v>
+      </c>
+      <c r="D240" s="23" t="s">
+        <v>2046</v>
+      </c>
+      <c r="E240" s="23" t="s">
+        <v>2047</v>
+      </c>
+      <c r="F240" s="23" t="s">
         <v>2048</v>
       </c>
-      <c r="D240" s="23" t="s">
+      <c r="G240" s="23" t="s">
         <v>2049</v>
       </c>
-      <c r="E240" s="23" t="s">
+      <c r="H240" s="23" t="s">
         <v>2050</v>
-      </c>
-      <c r="F240" s="23" t="s">
-        <v>2051</v>
-      </c>
-      <c r="G240" s="23" t="s">
-        <v>2052</v>
-      </c>
-      <c r="H240" s="23" t="s">
-        <v>2053</v>
       </c>
       <c r="I240" s="23" t="s">
         <v>379</v>
       </c>
       <c r="J240" s="23" t="s">
-        <v>2054</v>
+        <v>2051</v>
       </c>
       <c r="K240" s="23"/>
       <c r="L240" s="23"/>
@@ -21749,39 +21777,39 @@
       <c r="P240" s="23"/>
       <c r="Q240" s="23"/>
       <c r="R240" s="23" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="241" spans="1:24" s="27" customFormat="1" ht="16" x14ac:dyDescent="0.4">
+      <c r="A241" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="B241" s="22" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C241" s="22" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D241" s="23" t="s">
+        <v>2054</v>
+      </c>
+      <c r="E241" s="23" t="s">
         <v>2055</v>
       </c>
-    </row>
-    <row r="241" spans="1:24" s="27" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A241" s="21" t="s">
-        <v>385</v>
-      </c>
-      <c r="B241" s="22" t="s">
-        <v>2030</v>
-      </c>
-      <c r="C241" s="22" t="s">
+      <c r="F241" s="23" t="s">
         <v>2056</v>
       </c>
-      <c r="D241" s="23" t="s">
+      <c r="G241" s="23" t="s">
         <v>2057</v>
       </c>
-      <c r="E241" s="23" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F241" s="23" t="s">
-        <v>2059</v>
-      </c>
-      <c r="G241" s="23" t="s">
-        <v>2060</v>
-      </c>
       <c r="H241" s="23" t="s">
-        <v>2036</v>
+        <v>2033</v>
       </c>
       <c r="I241" s="23" t="s">
         <v>379</v>
       </c>
       <c r="J241" s="23" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="K241" s="23"/>
       <c r="L241" s="23"/>
@@ -21798,36 +21826,36 @@
         <v>581</v>
       </c>
     </row>
-    <row r="242" spans="1:24" s="19" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:24" s="19" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="21" t="s">
         <v>385</v>
       </c>
       <c r="B242" s="78" t="s">
+        <v>2015</v>
+      </c>
+      <c r="C242" s="78" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D242" s="78" t="s">
+        <v>2017</v>
+      </c>
+      <c r="E242" s="79" t="s">
         <v>2018</v>
       </c>
-      <c r="C242" s="78" t="s">
+      <c r="F242" s="78" t="s">
         <v>2019</v>
       </c>
-      <c r="D242" s="78" t="s">
+      <c r="G242" s="78" t="s">
         <v>2020</v>
       </c>
-      <c r="E242" s="79" t="s">
+      <c r="H242" s="78" t="s">
         <v>2021</v>
-      </c>
-      <c r="F242" s="78" t="s">
-        <v>2022</v>
-      </c>
-      <c r="G242" s="78" t="s">
-        <v>2023</v>
-      </c>
-      <c r="H242" s="78" t="s">
-        <v>2024</v>
       </c>
       <c r="I242" s="78" t="s">
         <v>374</v>
       </c>
       <c r="J242" s="78" t="s">
-        <v>1865</v>
+        <v>1862</v>
       </c>
       <c r="K242" s="78"/>
       <c r="L242" s="78"/>
@@ -21850,7 +21878,7 @@
       <c r="W242" s="33"/>
       <c r="X242" s="33"/>
     </row>
-    <row r="243" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="21" t="s">
         <v>385</v>
       </c>
@@ -21904,7 +21932,7 @@
       <c r="W243" s="33"/>
       <c r="X243" s="33"/>
     </row>
-    <row r="244" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="21" t="s">
         <v>385</v>
       </c>
@@ -21970,7 +21998,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="245" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="21" t="s">
         <v>385</v>
       </c>
@@ -22011,7 +22039,7 @@
       </c>
       <c r="O245" s="33"/>
       <c r="P245" s="33" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="Q245" s="33">
         <v>1</v>
@@ -22038,7 +22066,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="246" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="21" t="s">
         <v>385</v>
       </c>
@@ -22106,7 +22134,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="247" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="21" t="s">
         <v>385</v>
       </c>
@@ -22129,7 +22157,7 @@
         <v>1248</v>
       </c>
       <c r="H247" s="33" t="s">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="I247" s="33" t="s">
         <v>378</v>
@@ -22176,7 +22204,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="248" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="21" t="s">
         <v>385</v>
       </c>
@@ -22199,7 +22227,7 @@
         <v>1248</v>
       </c>
       <c r="H248" s="33" t="s">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="I248" s="33" t="s">
         <v>378</v>
@@ -22246,7 +22274,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="249" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="21" t="s">
         <v>385</v>
       </c>
@@ -22316,7 +22344,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="250" spans="1:24" s="1" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:24" s="1" customFormat="1" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="21" t="s">
         <v>385</v>
       </c>
@@ -22374,7 +22402,7 @@
       <c r="W250" s="33"/>
       <c r="X250" s="33"/>
     </row>
-    <row r="251" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="21" t="s">
         <v>385</v>
       </c>
@@ -22382,13 +22410,13 @@
         <v>1138</v>
       </c>
       <c r="C251" s="33" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="D251" s="33" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="E251" s="33" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="F251" s="33" t="s">
         <v>618</v>
@@ -22437,10 +22465,10 @@
         <v>1030</v>
       </c>
       <c r="X251" s="62" t="s">
-        <v>1549</v>
-      </c>
-    </row>
-    <row r="252" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="252" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="21" t="s">
         <v>385</v>
       </c>
@@ -22448,13 +22476,13 @@
         <v>1138</v>
       </c>
       <c r="C252" s="33" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="D252" s="33" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="E252" s="33" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="F252" s="33" t="s">
         <v>1047</v>
@@ -22469,7 +22497,7 @@
         <v>378</v>
       </c>
       <c r="J252" s="33" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="K252" s="33" t="s">
         <v>1048</v>
@@ -22503,10 +22531,10 @@
         <v>1030</v>
       </c>
       <c r="X252" s="62" t="s">
-        <v>1549</v>
-      </c>
-    </row>
-    <row r="253" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="253" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="21" t="s">
         <v>385</v>
       </c>
@@ -22560,7 +22588,7 @@
       <c r="W253" s="33"/>
       <c r="X253" s="33"/>
     </row>
-    <row r="254" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="21" t="s">
         <v>385</v>
       </c>
@@ -22614,7 +22642,7 @@
       <c r="W254" s="33"/>
       <c r="X254" s="33"/>
     </row>
-    <row r="255" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="21" t="s">
         <v>385</v>
       </c>
@@ -22678,7 +22706,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="256" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="21" t="s">
         <v>385</v>
       </c>
@@ -22742,7 +22770,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="257" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="21" t="s">
         <v>385</v>
       </c>
@@ -22810,7 +22838,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="258" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="21" t="s">
         <v>385</v>
       </c>
@@ -22874,7 +22902,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="259" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="21" t="s">
         <v>385</v>
       </c>
@@ -22940,7 +22968,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="260" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="21" t="s">
         <v>385</v>
       </c>
@@ -23006,7 +23034,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="261" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="21" t="s">
         <v>385</v>
       </c>
@@ -23072,7 +23100,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="262" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="21" t="s">
         <v>385</v>
       </c>
@@ -23126,7 +23154,7 @@
       <c r="W262" s="33"/>
       <c r="X262" s="33"/>
     </row>
-    <row r="263" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A263" s="21" t="s">
         <v>385</v>
       </c>
@@ -23192,7 +23220,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="264" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A264" s="21" t="s">
         <v>385</v>
       </c>
@@ -23256,7 +23284,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="265" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A265" s="21" t="s">
         <v>385</v>
       </c>
@@ -23320,7 +23348,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="266" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="21" t="s">
         <v>385</v>
       </c>
@@ -23374,7 +23402,7 @@
       <c r="W266" s="33"/>
       <c r="X266" s="33"/>
     </row>
-    <row r="267" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A267" s="21" t="s">
         <v>385</v>
       </c>
@@ -23440,7 +23468,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="268" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A268" s="21" t="s">
         <v>385</v>
       </c>
@@ -23504,7 +23532,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="269" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A269" s="21" t="s">
         <v>385</v>
       </c>
@@ -23568,7 +23596,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="270" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="21" t="s">
         <v>385</v>
       </c>
@@ -23622,7 +23650,7 @@
       <c r="W270" s="33"/>
       <c r="X270" s="33"/>
     </row>
-    <row r="271" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A271" s="21" t="s">
         <v>385</v>
       </c>
@@ -23688,7 +23716,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="272" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A272" s="21" t="s">
         <v>385</v>
       </c>
@@ -23752,7 +23780,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="273" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="21" t="s">
         <v>385</v>
       </c>
@@ -23804,7 +23832,7 @@
       <c r="W273" s="33"/>
       <c r="X273" s="33"/>
     </row>
-    <row r="274" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A274" s="21" t="s">
         <v>385</v>
       </c>
@@ -23818,16 +23846,16 @@
         <v>519</v>
       </c>
       <c r="E274" s="33" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="F274" s="33" t="s">
         <v>487</v>
       </c>
       <c r="G274" s="33" t="s">
-        <v>1730</v>
+        <v>1727</v>
       </c>
       <c r="H274" s="28" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="I274" s="33" t="s">
         <v>378</v>
@@ -23870,7 +23898,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="275" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A275" s="21" t="s">
         <v>385</v>
       </c>
@@ -23884,16 +23912,16 @@
         <v>577</v>
       </c>
       <c r="E275" s="33" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="F275" s="33" t="s">
         <v>1469</v>
       </c>
       <c r="G275" s="33" t="s">
-        <v>1730</v>
+        <v>1727</v>
       </c>
       <c r="H275" s="28" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="I275" s="33" t="s">
         <v>378</v>
@@ -23911,7 +23939,7 @@
       </c>
       <c r="O275" s="33"/>
       <c r="P275" s="33" t="s">
-        <v>1513</v>
+        <v>2072</v>
       </c>
       <c r="Q275" s="33">
         <v>1</v>
@@ -23938,7 +23966,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="276" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A276" s="21" t="s">
         <v>385</v>
       </c>
@@ -23952,7 +23980,7 @@
         <v>787</v>
       </c>
       <c r="E276" s="33" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="F276" s="33" t="s">
         <v>1258</v>
@@ -24002,7 +24030,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="277" spans="1:24" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:24" ht="17.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A277" s="21" t="s">
         <v>385</v>
       </c>
@@ -24022,10 +24050,10 @@
         <v>1260</v>
       </c>
       <c r="G277" s="33" t="s">
-        <v>1731</v>
+        <v>1728</v>
       </c>
       <c r="H277" s="33" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="I277" s="33" t="s">
         <v>379</v>
@@ -24078,16 +24106,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B1E54B1-94C7-420D-B742-577FC698418F}">
   <dimension ref="A1:L69"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="33" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="33" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="89.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="89.08203125" style="1" customWidth="1"/>
     <col min="5" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>393</v>
       </c>
@@ -24101,7 +24129,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="48" x14ac:dyDescent="0.35">
       <c r="A2" s="33" t="s">
         <v>726</v>
       </c>
@@ -24112,47 +24140,47 @@
         <v>398</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>1736</v>
+        <v>1733</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="33" t="s">
         <v>1122</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>1721</v>
+        <v>1718</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="33" t="s">
         <v>1122</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="C4" s="28" t="s">
         <v>1313</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>1720</v>
+        <v>1717</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="33" t="s">
         <v>1122</v>
       </c>
@@ -24160,7 +24188,7 @@
         <v>399</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="D5" s="34" t="s">
         <v>610</v>
@@ -24170,7 +24198,7 @@
       <c r="I5" s="2"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="33" t="s">
         <v>1122</v>
       </c>
@@ -24178,7 +24206,7 @@
         <v>67</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
       <c r="D6" s="34" t="s">
         <v>611</v>
@@ -24188,7 +24216,7 @@
       <c r="I6" s="2"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="33" t="s">
         <v>1122</v>
       </c>
@@ -24206,7 +24234,7 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="33" t="s">
         <v>1122</v>
       </c>
@@ -24224,7 +24252,7 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="33" t="s">
         <v>1122</v>
       </c>
@@ -24242,25 +24270,25 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="33" t="s">
         <v>1126</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>1722</v>
+        <v>1719</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" s="7" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" s="7" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="33" t="s">
         <v>1126</v>
       </c>
@@ -24271,10 +24299,10 @@
         <v>403</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>1733</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="7" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="7" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="33" t="s">
         <v>1126</v>
       </c>
@@ -24289,7 +24317,7 @@
       </c>
       <c r="I12" s="8"/>
     </row>
-    <row r="13" spans="1:10" s="7" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" s="7" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="33" t="s">
         <v>1126</v>
       </c>
@@ -24303,7 +24331,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="4" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" s="4" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="33" t="s">
         <v>1126</v>
       </c>
@@ -24317,7 +24345,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="28" t="s">
         <v>108</v>
       </c>
@@ -24332,7 +24360,7 @@
       </c>
       <c r="F15" s="5"/>
     </row>
-    <row r="16" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="35" t="s">
         <v>1137</v>
       </c>
@@ -24340,14 +24368,14 @@
         <v>417</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>1544</v>
+        <v>1305</v>
       </c>
       <c r="D16" s="28" t="s">
         <v>435</v>
       </c>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="36" t="s">
         <v>108</v>
       </c>
@@ -24355,27 +24383,27 @@
         <v>428</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="33" t="s">
         <v>108</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>1711</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="33" t="s">
         <v>108</v>
       </c>
@@ -24383,13 +24411,13 @@
         <v>674</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>1712</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="33" t="s">
         <v>108</v>
       </c>
@@ -24397,13 +24425,13 @@
         <v>675</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>1713</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="33" t="s">
         <v>108</v>
       </c>
@@ -24411,13 +24439,13 @@
         <v>676</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>1714</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="37" t="s">
         <v>108</v>
       </c>
@@ -24425,27 +24453,27 @@
         <v>722</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>1715</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="40" t="s">
         <v>108</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>1716</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="40" t="s">
         <v>108</v>
       </c>
@@ -24453,13 +24481,13 @@
         <v>723</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>1717</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="40" t="s">
         <v>108</v>
       </c>
@@ -24467,13 +24495,13 @@
         <v>724</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>1718</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="40" t="s">
         <v>108</v>
       </c>
@@ -24481,13 +24509,13 @@
         <v>725</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>1719</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="28" t="s">
         <v>1127</v>
       </c>
@@ -24495,29 +24523,29 @@
         <v>397</v>
       </c>
       <c r="C27" s="33" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D27" s="34" t="s">
         <v>1537</v>
       </c>
-      <c r="D27" s="34" t="s">
-        <v>1539</v>
-      </c>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="28" t="s">
         <v>1127</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>1729</v>
+        <v>1726</v>
       </c>
       <c r="C28" s="33" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D28" s="34" t="s">
         <v>1538</v>
       </c>
-      <c r="D28" s="34" t="s">
-        <v>1540</v>
-      </c>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="28" t="s">
         <v>1132</v>
       </c>
@@ -24529,7 +24557,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="35" t="s">
         <v>1137</v>
       </c>
@@ -24545,7 +24573,7 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
     </row>
-    <row r="31" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="35" t="s">
         <v>1137</v>
       </c>
@@ -24561,7 +24589,7 @@
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
     </row>
-    <row r="32" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="35" t="s">
         <v>1137</v>
       </c>
@@ -24578,7 +24606,7 @@
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
     </row>
-    <row r="33" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="35" t="s">
         <v>1137</v>
       </c>
@@ -24595,7 +24623,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="35" t="s">
         <v>1137</v>
       </c>
@@ -24612,7 +24640,7 @@
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
     </row>
-    <row r="35" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="35" t="s">
         <v>1137</v>
       </c>
@@ -24629,7 +24657,7 @@
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
     </row>
-    <row r="36" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="36" t="s">
         <v>1138</v>
       </c>
@@ -24646,7 +24674,7 @@
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
     </row>
-    <row r="37" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="36" t="s">
         <v>1138</v>
       </c>
@@ -24663,7 +24691,7 @@
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
     </row>
-    <row r="38" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="36" t="s">
         <v>1138</v>
       </c>
@@ -24680,7 +24708,7 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="36" t="s">
         <v>1138</v>
       </c>
@@ -24697,7 +24725,7 @@
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
     </row>
-    <row r="40" spans="1:12" s="6" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" s="6" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="36" t="s">
         <v>1138</v>
       </c>
@@ -24712,7 +24740,7 @@
       </c>
       <c r="L40" s="1"/>
     </row>
-    <row r="41" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="36" t="s">
         <v>1138</v>
       </c>
@@ -24732,7 +24760,7 @@
       <c r="J41" s="6"/>
       <c r="K41" s="6"/>
     </row>
-    <row r="42" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="36" t="s">
         <v>1138</v>
       </c>
@@ -24740,7 +24768,7 @@
         <v>425</v>
       </c>
       <c r="C42" s="28" t="s">
-        <v>2028</v>
+        <v>2025</v>
       </c>
       <c r="D42" s="29" t="s">
         <v>439</v>
@@ -24752,7 +24780,7 @@
       <c r="J42" s="6"/>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="36" t="s">
         <v>1138</v>
       </c>
@@ -24772,7 +24800,7 @@
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
     </row>
-    <row r="44" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="36" t="s">
         <v>1138</v>
       </c>
@@ -24786,7 +24814,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="36" t="s">
         <v>1138</v>
       </c>
@@ -24800,7 +24828,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="36" t="s">
         <v>1138</v>
       </c>
@@ -24811,10 +24839,10 @@
         <v>550</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>1723</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="36" t="s">
         <v>1138</v>
       </c>
@@ -24825,10 +24853,10 @@
         <v>552</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>1724</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="36" t="s">
         <v>1138</v>
       </c>
@@ -24839,10 +24867,10 @@
         <v>554</v>
       </c>
       <c r="D48" s="29" t="s">
-        <v>1725</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="36" t="s">
         <v>303</v>
       </c>
@@ -24850,13 +24878,13 @@
         <v>430</v>
       </c>
       <c r="C49" s="28" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="D49" s="34" t="s">
-        <v>1542</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="36" t="s">
         <v>303</v>
       </c>
@@ -24864,13 +24892,13 @@
         <v>431</v>
       </c>
       <c r="C50" s="28" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
       <c r="D50" s="29" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="36" t="s">
         <v>1139</v>
       </c>
@@ -24878,27 +24906,27 @@
         <v>432</v>
       </c>
       <c r="C51" s="28" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
       <c r="D51" s="29" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="41" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
       <c r="B52" s="41" t="s">
         <v>489</v>
       </c>
       <c r="C52" s="41" t="s">
-        <v>1931</v>
+        <v>1928</v>
       </c>
       <c r="D52" s="42" t="s">
-        <v>1942</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="43" t="s">
         <v>1114</v>
       </c>
@@ -24909,10 +24937,10 @@
         <v>612</v>
       </c>
       <c r="D53" s="44" t="s">
-        <v>1726</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="43" t="s">
         <v>1114</v>
       </c>
@@ -24923,10 +24951,10 @@
         <v>613</v>
       </c>
       <c r="D54" s="44" t="s">
-        <v>1727</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="43" t="s">
         <v>1114</v>
       </c>
@@ -24937,10 +24965,10 @@
         <v>614</v>
       </c>
       <c r="D55" s="44" t="s">
-        <v>1728</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="40" t="s">
         <v>1133</v>
       </c>
@@ -24954,187 +24982,187 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A57" s="46" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="B57" s="46" t="s">
-        <v>1770</v>
+        <v>1767</v>
       </c>
       <c r="C57" s="46" t="s">
-        <v>1772</v>
+        <v>1769</v>
       </c>
       <c r="D57" s="46" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="46" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B58" s="46" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C58" s="46" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D58" s="46" t="s">
         <v>1915</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A58" s="46" t="s">
-        <v>1737</v>
-      </c>
-      <c r="B58" s="46" t="s">
+      <c r="E58" s="6"/>
+    </row>
+    <row r="59" spans="1:5" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="46" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B59" s="46" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C59" s="46" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D59" s="46" t="s">
         <v>1916</v>
       </c>
-      <c r="C58" s="46" t="s">
+    </row>
+    <row r="60" spans="1:5" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="46" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B60" s="46" t="s">
         <v>1917</v>
       </c>
-      <c r="D58" s="46" t="s">
+      <c r="C60" s="46" t="s">
         <v>1918</v>
       </c>
-      <c r="E58" s="6"/>
-    </row>
-    <row r="59" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A59" s="46" t="s">
-        <v>1737</v>
-      </c>
-      <c r="B59" s="46" t="s">
-        <v>1815</v>
-      </c>
-      <c r="C59" s="46" t="s">
-        <v>1817</v>
-      </c>
-      <c r="D59" s="46" t="s">
+      <c r="D60" s="46" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="47" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B61" s="48" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C61" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D61" s="48" t="s">
         <v>1919</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A60" s="46" t="s">
-        <v>1737</v>
-      </c>
-      <c r="B60" s="46" t="s">
+    <row r="62" spans="1:5" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="48" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B62" s="48" t="s">
         <v>1920</v>
       </c>
-      <c r="C60" s="46" t="s">
+      <c r="C62" s="48" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D62" s="48" t="s">
         <v>1921</v>
       </c>
-      <c r="D60" s="46" t="s">
-        <v>2072</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A61" s="47" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B61" s="48" t="s">
-        <v>1855</v>
-      </c>
-      <c r="C61" s="48" t="s">
-        <v>1857</v>
-      </c>
-      <c r="D61" s="48" t="s">
+    </row>
+    <row r="63" spans="1:5" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="48" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B63" s="48" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C63" s="48" t="s">
         <v>1922</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A62" s="48" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B62" s="48" t="s">
+      <c r="D63" s="48" t="s">
         <v>1923</v>
       </c>
-      <c r="C62" s="48" t="s">
-        <v>1879</v>
-      </c>
-      <c r="D62" s="48" t="s">
-        <v>1924</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A63" s="48" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B63" s="48" t="s">
-        <v>1905</v>
-      </c>
-      <c r="C63" s="48" t="s">
-        <v>1925</v>
-      </c>
-      <c r="D63" s="48" t="s">
-        <v>1926</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" s="20" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:5" s="20" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="49" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="B64" s="49" t="s">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="C64" s="49" t="s">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D64" s="49" t="s">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" s="30" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" s="30" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="28" t="s">
         <v>1283</v>
       </c>
       <c r="B65" s="28" t="s">
-        <v>2062</v>
+        <v>2059</v>
       </c>
       <c r="C65" s="28" t="s">
         <v>1284</v>
       </c>
       <c r="D65" s="29" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" s="30" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="22" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B66" s="22" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C66" s="22" t="s">
+        <v>2033</v>
+      </c>
+      <c r="D66" s="31" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" s="30" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="22" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B67" s="22" t="s">
         <v>2063</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" s="30" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="22" t="s">
-        <v>2030</v>
-      </c>
-      <c r="B66" s="22" t="s">
+      <c r="C67" s="22" t="s">
+        <v>2033</v>
+      </c>
+      <c r="D67" s="31" t="s">
         <v>2064</v>
       </c>
-      <c r="C66" s="22" t="s">
-        <v>2036</v>
-      </c>
-      <c r="D66" s="31" t="s">
+    </row>
+    <row r="68" spans="1:4" s="30" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="22" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B68" s="22" t="s">
         <v>2065</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" s="30" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="22" t="s">
-        <v>2030</v>
-      </c>
-      <c r="B67" s="22" t="s">
+      <c r="C68" s="22" t="s">
+        <v>2050</v>
+      </c>
+      <c r="D68" s="31" t="s">
         <v>2066</v>
       </c>
-      <c r="C67" s="22" t="s">
-        <v>2036</v>
-      </c>
-      <c r="D67" s="31" t="s">
+    </row>
+    <row r="69" spans="1:4" s="30" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="22" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B69" s="22" t="s">
         <v>2067</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" s="30" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="22" t="s">
-        <v>2030</v>
-      </c>
-      <c r="B68" s="22" t="s">
+      <c r="C69" s="22" t="s">
+        <v>2033</v>
+      </c>
+      <c r="D69" s="31" t="s">
         <v>2068</v>
-      </c>
-      <c r="C68" s="22" t="s">
-        <v>2053</v>
-      </c>
-      <c r="D68" s="31" t="s">
-        <v>2069</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" s="30" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="22" t="s">
-        <v>2030</v>
-      </c>
-      <c r="B69" s="22" t="s">
-        <v>2070</v>
-      </c>
-      <c r="C69" s="22" t="s">
-        <v>2036</v>
-      </c>
-      <c r="D69" s="31" t="s">
-        <v>2071</v>
       </c>
     </row>
   </sheetData>
@@ -25145,17 +25173,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08E8E7EE-C276-4674-AE4F-1A0C8C62512A}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.25" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="5.625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="5.58203125" style="11" customWidth="1"/>
     <col min="2" max="2" width="29.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.875" style="14" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" style="14" customWidth="1"/>
     <col min="5" max="16384" width="11" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="9" t="s">
         <v>444</v>
       </c>
@@ -25178,7 +25206,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="11">
         <v>1</v>
       </c>
@@ -25199,7 +25227,7 @@
       </c>
       <c r="G2" s="12"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="11">
         <v>2</v>
       </c>
@@ -25220,12 +25248,12 @@
       </c>
       <c r="G3" s="12"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="11">
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>1299</v>
@@ -25241,7 +25269,7 @@
       </c>
       <c r="G4" s="12"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="11">
         <v>4</v>
       </c>
@@ -25262,7 +25290,7 @@
       </c>
       <c r="G5" s="12"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="11">
         <v>5</v>
       </c>
@@ -25283,7 +25311,7 @@
       </c>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="11">
         <v>6</v>
       </c>
@@ -25304,7 +25332,7 @@
       </c>
       <c r="G7" s="12"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="11">
         <v>7</v>
       </c>
@@ -25325,12 +25353,12 @@
       </c>
       <c r="G8" s="12"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="11">
         <v>8</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>1298</v>
@@ -25346,7 +25374,7 @@
       </c>
       <c r="G9" s="12"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="11">
         <v>9</v>
       </c>
@@ -25367,7 +25395,7 @@
       </c>
       <c r="G10" s="12"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="11">
         <v>10</v>
       </c>
@@ -25388,12 +25416,12 @@
       </c>
       <c r="G11" s="12"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="11">
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>1285</v>
@@ -25408,7 +25436,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="11">
         <v>12</v>
       </c>
@@ -25426,6 +25454,46 @@
       </c>
       <c r="F13" s="11" t="s">
         <v>1293</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="11">
+        <v>13</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>2075</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>2076</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>2077</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="11">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>2080</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>2081</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>2082</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>2083</v>
       </c>
     </row>
   </sheetData>
